--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1267320.01</v>
+        <v>1312204.01</v>
       </c>
       <c r="D2" t="n">
-        <v>3280</v>
+        <v>3535</v>
       </c>
       <c r="E2" t="n">
-        <v>1095430.01</v>
+        <v>1125034.01</v>
       </c>
       <c r="F2" t="n">
-        <v>171890</v>
+        <v>187170</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1170610</v>
+        <v>1206450</v>
       </c>
       <c r="D3" t="n">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="E3" t="n">
-        <v>1001990</v>
+        <v>1022950</v>
       </c>
       <c r="F3" t="n">
-        <v>168620</v>
+        <v>183500</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>96710.00999999999</v>
+        <v>105754.01</v>
       </c>
       <c r="D4" t="n">
-        <v>3047</v>
+        <v>3294</v>
       </c>
       <c r="E4" t="n">
-        <v>93440.00999999999</v>
+        <v>102084.01</v>
       </c>
       <c r="F4" t="n">
-        <v>3270</v>
+        <v>3670</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2248799.91</v>
+        <v>2352273.91</v>
       </c>
       <c r="D5" t="n">
-        <v>463</v>
+        <v>487</v>
       </c>
       <c r="E5" t="n">
         <v>532983.9</v>
       </c>
       <c r="F5" t="n">
-        <v>1715816.01</v>
+        <v>1819290.01</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1574741.01</v>
+        <v>1655029.01</v>
       </c>
       <c r="D6" t="n">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="E6" t="n">
         <v>49820</v>
       </c>
       <c r="F6" t="n">
-        <v>1524921.01</v>
+        <v>1605209.01</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>654058.9</v>
+        <v>677244.9</v>
       </c>
       <c r="D7" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="E7" t="n">
         <v>483163.9</v>
       </c>
       <c r="F7" t="n">
-        <v>170895</v>
+        <v>194081</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1725886.23</v>
+        <v>1856800.33</v>
       </c>
       <c r="D8" t="n">
-        <v>1294</v>
+        <v>1341</v>
       </c>
       <c r="E8" t="n">
-        <v>28334.7</v>
+        <v>28834.7</v>
       </c>
       <c r="F8" t="n">
-        <v>1697551.53</v>
+        <v>1827965.63</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1078687.08</v>
+        <v>1152921.18</v>
       </c>
       <c r="D9" t="n">
-        <v>670</v>
+        <v>705</v>
       </c>
       <c r="E9" t="n">
         <v>10626.88</v>
       </c>
       <c r="F9" t="n">
-        <v>1068060.2</v>
+        <v>1142294.3</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>645199.15</v>
+        <v>701879.15</v>
       </c>
       <c r="D10" t="n">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="E10" t="n">
-        <v>17707.82</v>
+        <v>18207.82</v>
       </c>
       <c r="F10" t="n">
-        <v>627491.33</v>
+        <v>683671.33</v>
       </c>
     </row>
     <row r="11">
@@ -682,7 +682,7 @@
         <v>432400</v>
       </c>
       <c r="D11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" t="n">
         <v>198400</v>
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>598471.8100000001</v>
+        <v>603258.8100000001</v>
       </c>
       <c r="D12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E12" t="n">
-        <v>392546.81</v>
+        <v>396334.81</v>
       </c>
       <c r="F12" t="n">
-        <v>205925</v>
+        <v>206924</v>
       </c>
     </row>
     <row r="13">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>290674</v>
+        <v>292654</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
-        <v>170474</v>
+        <v>172454</v>
       </c>
       <c r="F13" t="n">
         <v>120200</v>
@@ -751,13 +751,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19800</v>
+        <v>21780</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>19800</v>
+        <v>21780</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1595169.37</v>
+        <v>1707723.47</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>95.3</v>
+        <v>95.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 1519622.37；菌群线 49600.0；咨询线 21592.0；课程线 4355.0</t>
+          <t>医疗线 1630982.47；菌群线 49600.0；咨询线 22786.0；课程线 4355.0</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>368141.99</v>
+        <v>368539.99</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 233344.0；营地 50500.0；菌群线 45600.0；医疗线 20400.99；课程线 18297.0</t>
+          <t>咨询线 233742.0；营地 50500.0；菌群线 45600.0；医疗线 20400.99；课程线 18297.0</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>186297.94</v>
+        <v>214497.94</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -865,11 +865,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>67.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 126576.0；菌群线 24800.0；医疗线 19358.94；课程线 15563.0</t>
+          <t>咨询线 148176.0；菌群线 24800.0；课程线 22163.0；医疗线 19358.94</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>412672.71</v>
+        <v>440990.71</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>38</v>
+        <v>40.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 156760.01；菌群线 91200.0；课程线 47390.0；医疗线 40635.7；考证 40587.0；营地 36100.0</t>
+          <t>咨询线 176760.01；菌群线 91200.0；课程线 55708.0；医疗线 40635.7；考证 40587.0；营地 36100.0</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>309005.77</v>
+        <v>336875.77</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>72</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 222466.0；考证 40587.0；菌群线 22800.0；课程线 12387.0；医疗线 10765.77</t>
+          <t>咨询线 230964.0；考证 40587.0；医疗线 29819.77；菌群线 22800.0；课程线 12705.0</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>202517</v>
+        <v>202915</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 194562.0；课程线 6956.0；考证 999.0；菌群线 0.0</t>
+          <t>咨询线 194960.0；课程线 6956.0；考证 999.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>258047.94</v>
+        <v>288451.94</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -957,11 +957,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>82.3</v>
+        <v>84.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 212342.0；医疗线 31481.94；课程线 14224.0；菌群线 0.0</t>
+          <t>咨询线 242740.0；医疗线 31481.94；课程线 14230.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>213091.54</v>
+        <v>224526.54</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>96.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 205274.0；医疗线 7657.54；课程线 160.0；菌群线 0.0</t>
+          <t>咨询线 215672.0；医疗线 7657.54；考证 999.0；课程线 198.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>214429.3</v>
+        <v>216621.3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1003,11 +1003,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75</v>
+        <v>75.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 160746.0；医疗线 47026.3；课程线 6657.0；菌群线 0.0</t>
+          <t>咨询线 162938.0；医疗线 47026.3；课程线 6657.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>155694</v>
+        <v>164092</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1026,11 +1026,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>69.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 107582.0；营地 33600.0；课程线 14512.0；菌群线 0.0</t>
+          <t>咨询线 115980.0；营地 33600.0；课程线 14512.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>100710.01</v>
+        <v>113354.01</v>
       </c>
     </row>
     <row r="3">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>肖伟</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>51020</v>
+        <v>52800</v>
       </c>
     </row>
     <row r="6">
@@ -1176,11 +1176,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>王渊亮</t>
+          <t>肖伟</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>49080</v>
+        <v>51020</v>
       </c>
     </row>
     <row r="7">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>114786</v>
+        <v>120184</v>
       </c>
     </row>
     <row r="8">
@@ -1212,11 +1212,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>邓璐</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>94184</v>
+        <v>98378</v>
       </c>
     </row>
     <row r="9">
@@ -1230,11 +1230,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>邓璐</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>88378</v>
+        <v>94782</v>
       </c>
     </row>
     <row r="10">
@@ -1266,11 +1266,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>李雅玲</t>
+          <t>陈舒羽</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>79700</v>
+        <v>81780</v>
       </c>
     </row>
     <row r="12">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>396550</v>
+        <v>402520</v>
       </c>
     </row>
     <row r="13">
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>273902.96</v>
+        <v>302882.96</v>
       </c>
     </row>
     <row r="14">
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>163663</v>
+        <v>183279.74</v>
       </c>
     </row>
     <row r="15">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>150260.64</v>
+        <v>163663</v>
       </c>
     </row>
     <row r="16">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>143992</v>
+        <v>148460</v>
       </c>
     </row>
     <row r="17">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>赵越</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>李明</t>
+          <t>赵越</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>江敏</t>
+          <t>丁蕾</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1662,11 +1662,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>丁蕾</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5940</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="34">
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1267320.01</v>
+        <v>1312204.01</v>
       </c>
       <c r="C2" t="n">
-        <v>192963.57</v>
+        <v>200906.57</v>
       </c>
       <c r="D2" t="n">
-        <v>17019</v>
+        <v>18966</v>
       </c>
       <c r="E2" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="F2" t="n">
-        <v>175944.57</v>
+        <v>181940.57</v>
       </c>
       <c r="G2" t="n">
-        <v>13.88</v>
+        <v>13.87</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>青少年同行者计划护航营（6月） 51599.0；青少年同行者计划 48138.0；青少年同行者计划-护航营 23021.66</t>
+          <t>青少年同行者计划护航营（6月） 51599.0；青少年同行者计划 48138.0；青少年同行者计划-护航营 27204.66</t>
         </is>
       </c>
     </row>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2248799.91</v>
+        <v>2352273.91</v>
       </c>
       <c r="C3" t="n">
-        <v>331188</v>
+        <v>335207.9</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1828,14 +1828,14 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>331188</v>
+        <v>335207.9</v>
       </c>
       <c r="G3" t="n">
-        <v>14.73</v>
+        <v>14.25</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 131800.0；精神心理 83796.0；暑假礼遇咨询套餐 39600.0</t>
+          <t>儿童青少年 135800.0；精神心理 83796.0；暑假礼遇咨询套餐 39600.0</t>
         </is>
       </c>
     </row>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1725886.23</v>
+        <v>1856800.33</v>
       </c>
       <c r="C4" t="n">
-        <v>574904.5699999999</v>
+        <v>633074.5699999999</v>
       </c>
       <c r="D4" t="n">
         <v>1800</v>
@@ -1858,14 +1858,14 @@
         <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>573104.5699999999</v>
+        <v>631274.5699999999</v>
       </c>
       <c r="G4" t="n">
-        <v>33.21</v>
+        <v>34</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>日间中心 Ⅱ 212000.0；治疗I（个体1000） 159859.14；日间中心 Ⅰ 78000.0</t>
+          <t>日间中心 Ⅱ 212000.0；治疗I（个体1000） 210859.14；日间中心 Ⅰ 78000.0</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>598471.8100000001</v>
+        <v>603258.8100000001</v>
       </c>
       <c r="C6" t="n">
         <v>113405.07</v>
@@ -1915,13 +1915,13 @@
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="F6" t="n">
         <v>111387.17</v>
       </c>
       <c r="G6" t="n">
-        <v>18.61</v>
+        <v>18.46</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>290674</v>
+        <v>292654</v>
       </c>
       <c r="C7" t="n">
         <v>361480</v>
@@ -1945,13 +1945,13 @@
         <v>20000</v>
       </c>
       <c r="E7" t="n">
-        <v>6.88</v>
+        <v>6.83</v>
       </c>
       <c r="F7" t="n">
         <v>341480</v>
       </c>
       <c r="G7" t="n">
-        <v>117.48</v>
+        <v>116.68</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19800</v>
+        <v>21780</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1312204.01</v>
+        <v>1420465.02</v>
       </c>
       <c r="D2" t="n">
-        <v>3535</v>
+        <v>3868</v>
       </c>
       <c r="E2" t="n">
-        <v>1125034.01</v>
+        <v>1226619.02</v>
       </c>
       <c r="F2" t="n">
-        <v>187170</v>
+        <v>193846</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1206450</v>
+        <v>1307628</v>
       </c>
       <c r="D3" t="n">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="E3" t="n">
-        <v>1022950</v>
+        <v>1117528</v>
       </c>
       <c r="F3" t="n">
-        <v>183500</v>
+        <v>190100</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>105754.01</v>
+        <v>112837.02</v>
       </c>
       <c r="D4" t="n">
-        <v>3294</v>
+        <v>3599</v>
       </c>
       <c r="E4" t="n">
-        <v>102084.01</v>
+        <v>109091.02</v>
       </c>
       <c r="F4" t="n">
-        <v>3670</v>
+        <v>3746</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2352273.91</v>
+        <v>2506303.81</v>
       </c>
       <c r="D5" t="n">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="E5" t="n">
-        <v>532983.9</v>
+        <v>545033.8</v>
       </c>
       <c r="F5" t="n">
-        <v>1819290.01</v>
+        <v>1961270.01</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1655029.01</v>
+        <v>1764019.01</v>
       </c>
       <c r="D6" t="n">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="E6" t="n">
         <v>49820</v>
       </c>
       <c r="F6" t="n">
-        <v>1605209.01</v>
+        <v>1714199.01</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>677244.9</v>
+        <v>722284.8</v>
       </c>
       <c r="D7" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E7" t="n">
-        <v>483163.9</v>
+        <v>495213.8</v>
       </c>
       <c r="F7" t="n">
-        <v>194081</v>
+        <v>227071</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1856800.33</v>
+        <v>1873476.82</v>
       </c>
       <c r="D8" t="n">
-        <v>1341</v>
+        <v>1371</v>
       </c>
       <c r="E8" t="n">
-        <v>28834.7</v>
+        <v>29334.7</v>
       </c>
       <c r="F8" t="n">
-        <v>1827965.63</v>
+        <v>1844142.12</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1152921.18</v>
+        <v>1159018.68</v>
       </c>
       <c r="D9" t="n">
-        <v>705</v>
+        <v>718</v>
       </c>
       <c r="E9" t="n">
-        <v>10626.88</v>
+        <v>11126.88</v>
       </c>
       <c r="F9" t="n">
-        <v>1142294.3</v>
+        <v>1147891.8</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>701879.15</v>
+        <v>712458.14</v>
       </c>
       <c r="D10" t="n">
-        <v>635</v>
+        <v>652</v>
       </c>
       <c r="E10" t="n">
         <v>18207.82</v>
       </c>
       <c r="F10" t="n">
-        <v>683671.33</v>
+        <v>694250.3199999999</v>
       </c>
     </row>
     <row r="11">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>292654</v>
+        <v>309454</v>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>172454</v>
+        <v>189254</v>
       </c>
       <c r="F13" t="n">
         <v>120200</v>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1707723.47</v>
+        <v>1733497.97</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>95.5</v>
+        <v>95</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 1630982.47；菌群线 49600.0；咨询线 22786.0；课程线 4355.0</t>
+          <t>医疗线 1646737.97；菌群线 49600.0；咨询线 32786.0；课程线 4374.0</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>368539.99</v>
+        <v>385933.99</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>63.4</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 233742.0；营地 50500.0；菌群线 45600.0；医疗线 20400.99；课程线 18297.0</t>
+          <t>咨询线 251136.0；营地 50500.0；菌群线 45600.0；医疗线 20400.99；课程线 18297.0</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>214497.94</v>
+        <v>231516.94</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -865,11 +865,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>69.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 148176.0；菌群线 24800.0；课程线 22163.0；医疗线 19358.94</t>
+          <t>咨询线 165176.0；菌群线 24800.0；课程线 22182.0；医疗线 19358.94</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>440990.71</v>
+        <v>442207.71</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 176760.01；菌群线 91200.0；课程线 55708.0；医疗线 40635.7；考证 40587.0；营地 36100.0</t>
+          <t>咨询线 177958.01；菌群线 91200.0；课程线 55727.0；医疗线 40635.7；考证 40587.0；营地 36100.0</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>336875.77</v>
+        <v>379795.77</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>68.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 230964.0；考证 40587.0；医疗线 29819.77；菌群线 22800.0；课程线 12705.0</t>
+          <t>咨询线 273464.0；考证 40587.0；医疗线 30239.77；菌群线 22800.0；课程线 12705.0</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>202915</v>
+        <v>246715</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -934,11 +934,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>96.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 194960.0；课程线 6956.0；考证 999.0；菌群线 0.0</t>
+          <t>咨询线 238760.0；课程线 6956.0；考证 999.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>288451.94</v>
+        <v>296047.94</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -957,11 +957,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>84.2</v>
+        <v>82.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 242740.0；医疗线 31481.94；课程线 14230.0；菌群线 0.0</t>
+          <t>咨询线 243736.0；医疗线 31481.94；课程线 20830.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>224526.54</v>
+        <v>232443.54</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>96.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 215672.0；医疗线 7657.54；考证 999.0；课程线 198.0；菌群线 0.0</t>
+          <t>咨询线 223570.0；医疗线 7657.54；考证 999.0；课程线 217.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>216621.3</v>
+        <v>217019.3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1003,11 +1003,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75.2</v>
+        <v>75.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 162938.0；医疗线 47026.3；课程线 6657.0；菌群线 0.0</t>
+          <t>咨询线 163336.0；医疗线 47026.3；课程线 6657.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>164092</v>
+        <v>164490</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1026,11 +1026,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70.7</v>
+        <v>70.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 115980.0；营地 33600.0；课程线 14512.0；菌群线 0.0</t>
+          <t>咨询线 116378.0；营地 33600.0；课程线 14512.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>218434.98</v>
+        <v>218833.97</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1049,11 +1049,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>56.7</v>
+        <v>56.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>考证 123752.0；咨询线 74572.0；课程线 19809.0；医疗线 301.98；菌群线 0.0</t>
+          <t>考证 123752.0；咨询线 74970.0；课程线 19809.0；医疗线 302.97；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>113354.01</v>
+        <v>116875.02</v>
       </c>
     </row>
     <row r="3">
@@ -1122,11 +1122,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>龙少海</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>66000</v>
+        <v>76840</v>
       </c>
     </row>
     <row r="4">
@@ -1140,11 +1140,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>龙少海</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>62280</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="5">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>肖伟</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52800</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="6">
@@ -1176,11 +1176,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>肖伟</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>51020</v>
+        <v>52800</v>
       </c>
     </row>
     <row r="7">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>120184</v>
+        <v>140184</v>
       </c>
     </row>
     <row r="8">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>陈静</t>
+          <t>谌黎平</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>86990</v>
+        <v>87392</v>
       </c>
     </row>
     <row r="11">
@@ -1266,11 +1266,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>陈舒羽</t>
+          <t>李雅玲</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>81780</v>
+        <v>87200</v>
       </c>
     </row>
     <row r="12">
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>302882.96</v>
+        <v>303420.46</v>
       </c>
     </row>
     <row r="14">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>148460</v>
+        <v>159718</v>
       </c>
     </row>
     <row r="17">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>李天阳</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>安百柠</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>安百柠</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1312204.01</v>
+        <v>1420465.02</v>
       </c>
       <c r="C2" t="n">
-        <v>200906.57</v>
+        <v>224232.57</v>
       </c>
       <c r="D2" t="n">
-        <v>18966</v>
+        <v>21039</v>
       </c>
       <c r="E2" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="F2" t="n">
-        <v>181940.57</v>
+        <v>203193.57</v>
       </c>
       <c r="G2" t="n">
-        <v>13.87</v>
+        <v>14.3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>青少年同行者计划护航营（6月） 51599.0；青少年同行者计划 48138.0；青少年同行者计划-护航营 27204.66</t>
+          <t>青少年同行者计划 52288.0；青少年同行者计划护航营（6月） 51599.0；青少年同行者计划-护航营 31387.66</t>
         </is>
       </c>
     </row>
@@ -1816,26 +1816,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2352273.91</v>
+        <v>2506303.81</v>
       </c>
       <c r="C3" t="n">
-        <v>335207.9</v>
+        <v>368353.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F3" t="n">
-        <v>335207.9</v>
+        <v>367955.9</v>
       </c>
       <c r="G3" t="n">
-        <v>14.25</v>
+        <v>14.68</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 135800.0；精神心理 83796.0；暑假礼遇咨询套餐 39600.0</t>
+          <t>儿童青少年 155800.0；精神心理 96544.0；暑假礼遇咨询套餐 39600.0</t>
         </is>
       </c>
     </row>
@@ -1846,22 +1846,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1856800.33</v>
+        <v>1873476.82</v>
       </c>
       <c r="C4" t="n">
-        <v>633074.5699999999</v>
+        <v>633303.5699999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1800</v>
+        <v>1829</v>
       </c>
       <c r="E4" t="n">
         <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>631274.5699999999</v>
+        <v>631474.5699999999</v>
       </c>
       <c r="G4" t="n">
-        <v>34</v>
+        <v>33.71</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>432400</v>
       </c>
       <c r="C5" t="n">
-        <v>237000</v>
+        <v>261800</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1888,14 +1888,14 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>237000</v>
+        <v>261800</v>
       </c>
       <c r="G5" t="n">
-        <v>54.81</v>
+        <v>60.55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>肠道菌群移植 147800.0；肠道菌群移植（双疗程优惠）  45600.0；开业/店庆菌群移植优惠（深圳） 22800.0</t>
+          <t>肠道菌群移植 172600.0；肠道菌群移植（双疗程优惠）  45600.0；开业/店庆菌群移植优惠（深圳） 22800.0</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
         <v>603258.8100000001</v>
       </c>
       <c r="C6" t="n">
-        <v>113405.07</v>
+        <v>152193.07</v>
       </c>
       <c r="D6" t="n">
         <v>2017.9</v>
@@ -1918,14 +1918,14 @@
         <v>0.33</v>
       </c>
       <c r="F6" t="n">
-        <v>111387.17</v>
+        <v>150175.17</v>
       </c>
       <c r="G6" t="n">
-        <v>18.46</v>
+        <v>24.89</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 103016.0；观心学院-国康网心理咨询师专业技能培训（3788） 3156.67；完形心理基训课 2997.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 103016.0；心灯计划-实战派心理咨询师执业培训项目（初+中阶-尾款） 38788.0；观心学院-国康网心理咨询师专业技能培训（3788） 3156.67</t>
         </is>
       </c>
     </row>
@@ -1936,26 +1936,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>292654</v>
+        <v>309454</v>
       </c>
       <c r="C7" t="n">
-        <v>361480</v>
+        <v>378280</v>
       </c>
       <c r="D7" t="n">
         <v>20000</v>
       </c>
       <c r="E7" t="n">
-        <v>6.83</v>
+        <v>6.46</v>
       </c>
       <c r="F7" t="n">
-        <v>341480</v>
+        <v>358280</v>
       </c>
       <c r="G7" t="n">
-        <v>116.68</v>
+        <v>115.78</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>青少年成长基地3月营（金盏基地） 171200.0；蛋壳跳动身心复能营21天（一阶） 119600.0；青少年基地3个月慈善价 49920.0</t>
+          <t>青少年成长基地3月营（金盏基地） 188000.0；蛋壳跳动身心复能营21天（一阶） 119600.0；青少年基地3个月慈善价 49920.0</t>
         </is>
       </c>
     </row>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -1104,11 +1104,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>116875.02</v>
+        <v>76840</v>
       </c>
     </row>
     <row r="3">
@@ -1122,11 +1122,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>龙少海</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>76840</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="4">
@@ -1140,11 +1140,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>龙少海</t>
+          <t>肖伟</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>66000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="5">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>肖伟</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>55000</v>
+        <v>52800</v>
       </c>
     </row>
     <row r="6">
@@ -1176,11 +1176,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52800</v>
+        <v>51740</v>
       </c>
     </row>
     <row r="7">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>赵越</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>赵越</t>
+          <t>李明</t>
         </is>
       </c>
       <c r="D26" t="n">

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1420465.02</v>
+        <v>1603988.02</v>
       </c>
       <c r="D2" t="n">
-        <v>3868</v>
+        <v>4936</v>
       </c>
       <c r="E2" t="n">
-        <v>1226619.02</v>
+        <v>1368605.02</v>
       </c>
       <c r="F2" t="n">
-        <v>193846</v>
+        <v>235383</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1307628</v>
+        <v>1464424</v>
       </c>
       <c r="D3" t="n">
-        <v>269</v>
+        <v>318</v>
       </c>
       <c r="E3" t="n">
-        <v>1117528</v>
+        <v>1233025</v>
       </c>
       <c r="F3" t="n">
-        <v>190100</v>
+        <v>231399</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>112837.02</v>
+        <v>139564.02</v>
       </c>
       <c r="D4" t="n">
-        <v>3599</v>
+        <v>4618</v>
       </c>
       <c r="E4" t="n">
-        <v>109091.02</v>
+        <v>135580.02</v>
       </c>
       <c r="F4" t="n">
-        <v>3746</v>
+        <v>3984</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2506303.81</v>
+        <v>3211975.82</v>
       </c>
       <c r="D5" t="n">
-        <v>514</v>
+        <v>637</v>
       </c>
       <c r="E5" t="n">
-        <v>545033.8</v>
+        <v>696471.8</v>
       </c>
       <c r="F5" t="n">
-        <v>1961270.01</v>
+        <v>2515504.02</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1764019.01</v>
+        <v>2297007.02</v>
       </c>
       <c r="D6" t="n">
-        <v>321</v>
+        <v>411</v>
       </c>
       <c r="E6" t="n">
-        <v>49820</v>
+        <v>116440</v>
       </c>
       <c r="F6" t="n">
-        <v>1714199.01</v>
+        <v>2180567.02</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>722284.8</v>
+        <v>894968.8</v>
       </c>
       <c r="D7" t="n">
-        <v>192</v>
+        <v>225</v>
       </c>
       <c r="E7" t="n">
-        <v>495213.8</v>
+        <v>580031.8</v>
       </c>
       <c r="F7" t="n">
-        <v>227071</v>
+        <v>314937</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1873476.82</v>
+        <v>2236888.76</v>
       </c>
       <c r="D8" t="n">
-        <v>1371</v>
+        <v>1739</v>
       </c>
       <c r="E8" t="n">
-        <v>29334.7</v>
+        <v>34369.45</v>
       </c>
       <c r="F8" t="n">
-        <v>1844142.12</v>
+        <v>2202519.31</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1159018.68</v>
+        <v>1387351.92</v>
       </c>
       <c r="D9" t="n">
-        <v>718</v>
+        <v>903</v>
       </c>
       <c r="E9" t="n">
-        <v>11126.88</v>
+        <v>12634.63</v>
       </c>
       <c r="F9" t="n">
-        <v>1147891.8</v>
+        <v>1374717.29</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>712458.14</v>
+        <v>847536.84</v>
       </c>
       <c r="D10" t="n">
-        <v>652</v>
+        <v>835</v>
       </c>
       <c r="E10" t="n">
-        <v>18207.82</v>
+        <v>21734.82</v>
       </c>
       <c r="F10" t="n">
-        <v>694250.3199999999</v>
+        <v>825802.02</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>432400</v>
+        <v>482000</v>
       </c>
       <c r="D11" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E11" t="n">
-        <v>198400</v>
+        <v>224200</v>
       </c>
       <c r="F11" t="n">
-        <v>234000</v>
+        <v>257800</v>
       </c>
     </row>
     <row r="12">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>309454</v>
+        <v>310454</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
-        <v>189254</v>
+        <v>190254</v>
       </c>
       <c r="F13" t="n">
         <v>120200</v>
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21780</v>
+        <v>33660</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>21780</v>
+        <v>25740</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>7920</v>
       </c>
     </row>
   </sheetData>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1733497.97</v>
+        <v>2018871.04</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 1646737.97；菌群线 49600.0；咨询线 32786.0；课程线 4374.0</t>
+          <t>医疗线 1922063.04；菌群线 49600.0；咨询线 42786.0；课程线 4422.0</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>385933.99</v>
+        <v>490146.99</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>65.09999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 251136.0；营地 50500.0；菌群线 45600.0；医疗线 20400.99；课程线 18297.0</t>
+          <t>咨询线 338530.0；营地 50500.0；菌群线 45600.0；医疗线 37200.99；课程线 18316.0</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>231516.94</v>
+        <v>258196.96</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -865,11 +865,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>71.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 165176.0；菌群线 24800.0；课程线 22182.0；医疗线 19358.94</t>
+          <t>咨询线 191370.0；菌群线 24800.0；课程线 22220.0；医疗线 19806.96</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>442207.71</v>
+        <v>542985.72</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>40.2</v>
+        <v>44</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 177958.01；菌群线 91200.0；课程线 55727.0；医疗线 40635.7；考证 40587.0；营地 36100.0</t>
+          <t>咨询线 238738.02；菌群线 92200.0；课程线 88765.0；医疗线 42635.7；考证 40587.0；营地 36100.0；工作坊 3960.0</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>379795.77</v>
+        <v>502163.76</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>72</v>
+        <v>68.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 273464.0；考证 40587.0；医疗线 30239.77；菌群线 22800.0；课程线 12705.0</t>
+          <t>咨询线 344160.0；医疗线 81892.76；考证 40587.0；菌群线 22800.0；课程线 12724.0</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>246715</v>
+        <v>284528</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -934,11 +934,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>96.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 238760.0；课程线 6956.0；考证 999.0；菌群线 0.0</t>
+          <t>咨询线 269954.0；课程线 13575.0；考证 999.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>296047.94</v>
+        <v>381202.14</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -957,11 +957,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>82.3</v>
+        <v>86.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 243736.0；医疗线 31481.94；课程线 20830.0；菌群线 0.0</t>
+          <t>咨询线 328732.0；医疗线 31583.14；课程线 20887.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232443.54</v>
+        <v>300393.05</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>96.2</v>
+        <v>88.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 223570.0；医疗线 7657.54；考证 999.0；课程线 217.0；菌群线 0.0</t>
+          <t>咨询线 266566.0；菌群线 22800.0；医疗线 9811.05；考证 999.0；课程线 217.0</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>217019.3</v>
+        <v>334007.7</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1003,11 +1003,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 163336.0；医疗线 47026.3；课程线 6657.0；菌群线 0.0</t>
+          <t>咨询线 270928.0；医疗线 56422.7；课程线 6657.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>164490</v>
+        <v>171426</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1026,11 +1026,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 116378.0；营地 33600.0；课程线 14512.0；菌群线 0.0</t>
+          <t>咨询线 117174.0；营地 33600.0；课程线 16192.0；工作坊 3960.0；医疗线 500.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>218833.97</v>
+        <v>250448.97</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1049,11 +1049,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>56.6</v>
+        <v>49.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>考证 123752.0；咨询线 74970.0；课程线 19809.0；医疗线 302.97；菌群线 0.0</t>
+          <t>考证 123752.0；咨询线 106566.0；课程线 19828.0；医疗线 302.97；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>76840</v>
+        <v>88780</v>
       </c>
     </row>
     <row r="3">
@@ -1122,11 +1122,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>龙少海</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>66000</v>
+        <v>74940</v>
       </c>
     </row>
     <row r="4">
@@ -1140,11 +1140,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>肖伟</t>
+          <t>龙少海</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>55000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="5">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>肖伟</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52800</v>
+        <v>61600</v>
       </c>
     </row>
     <row r="6">
@@ -1176,11 +1176,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>51740</v>
+        <v>59400</v>
       </c>
     </row>
     <row r="7">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>140184</v>
+        <v>171184</v>
       </c>
     </row>
     <row r="8">
@@ -1212,11 +1212,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>邓璐</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>98378</v>
+        <v>151180</v>
       </c>
     </row>
     <row r="9">
@@ -1230,11 +1230,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>邓璐</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>94782</v>
+        <v>109168</v>
       </c>
     </row>
     <row r="10">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>谌黎平</t>
+          <t>陈静</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>87392</v>
+        <v>107388</v>
       </c>
     </row>
     <row r="11">
@@ -1266,11 +1266,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>李雅玲</t>
+          <t>郑巨光</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>87200</v>
+        <v>103996</v>
       </c>
     </row>
     <row r="12">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>402520</v>
+        <v>410510</v>
       </c>
     </row>
     <row r="13">
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>303420.46</v>
+        <v>385891.53</v>
       </c>
     </row>
     <row r="14">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>183279.74</v>
+        <v>202395.74</v>
       </c>
     </row>
     <row r="15">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>163663</v>
+        <v>197482</v>
       </c>
     </row>
     <row r="16">
@@ -1356,11 +1356,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>159718</v>
+        <v>191116</v>
       </c>
     </row>
     <row r="17">
@@ -1374,11 +1374,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>49600</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="18">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>许冰</t>
+          <t>赵越</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>赵越</t>
+          <t>许冰</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1644,11 +1644,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>丁蕾</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>7920</v>
+        <v>11880</v>
       </c>
     </row>
     <row r="33">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>江敏</t>
+          <t>丁蕾</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1680,11 +1680,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>安百柠</t>
+          <t>余婉丽</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1980</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="35">
@@ -1698,11 +1698,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>田婉丽</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1980</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="36">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>安百柠</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1420465.02</v>
+        <v>1603988.02</v>
       </c>
       <c r="C2" t="n">
-        <v>224232.57</v>
+        <v>246272.58</v>
       </c>
       <c r="D2" t="n">
-        <v>21039</v>
+        <v>27781.01</v>
       </c>
       <c r="E2" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="F2" t="n">
-        <v>203193.57</v>
+        <v>218491.57</v>
       </c>
       <c r="G2" t="n">
-        <v>14.3</v>
+        <v>13.62</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>青少年同行者计划 52288.0；青少年同行者计划护航营（6月） 51599.0；青少年同行者计划-护航营 31387.66</t>
+          <t>青少年同行者计划护航营（6月） 56579.0；青少年同行者计划 52288.0；青少年同行者计划-护航营 31387.66</t>
         </is>
       </c>
     </row>
@@ -1816,26 +1816,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2506303.81</v>
+        <v>3211975.82</v>
       </c>
       <c r="C3" t="n">
-        <v>368353.9</v>
+        <v>439328.28</v>
       </c>
       <c r="D3" t="n">
-        <v>398</v>
+        <v>25398</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02</v>
+        <v>0.79</v>
       </c>
       <c r="F3" t="n">
-        <v>367955.9</v>
+        <v>413930.28</v>
       </c>
       <c r="G3" t="n">
-        <v>14.68</v>
+        <v>12.89</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 155800.0；精神心理 96544.0；暑假礼遇咨询套餐 39600.0</t>
+          <t>儿童青少年 175244.48；精神心理 116544.0；暑假礼遇咨询套餐 49600.0</t>
         </is>
       </c>
     </row>
@@ -1846,26 +1846,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1873476.82</v>
+        <v>2236888.76</v>
       </c>
       <c r="C4" t="n">
-        <v>633303.5699999999</v>
+        <v>633773.5699999999</v>
       </c>
       <c r="D4" t="n">
         <v>1829</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="F4" t="n">
-        <v>631474.5699999999</v>
+        <v>631944.5699999999</v>
       </c>
       <c r="G4" t="n">
-        <v>33.71</v>
+        <v>28.25</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>日间中心 Ⅱ 212000.0；治疗I（个体1000） 210859.14；日间中心 Ⅰ 78000.0</t>
+          <t>日间中心 Ⅱ 212000.0；治疗I（个体1000） 210861.14；日间中心 Ⅰ 78000.0</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>432400</v>
+        <v>482000</v>
       </c>
       <c r="C5" t="n">
         <v>261800</v>
@@ -1891,7 +1891,7 @@
         <v>261800</v>
       </c>
       <c r="G5" t="n">
-        <v>60.55</v>
+        <v>54.32</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1936,26 +1936,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>309454</v>
+        <v>310454</v>
       </c>
       <c r="C7" t="n">
-        <v>378280</v>
+        <v>408080</v>
       </c>
       <c r="D7" t="n">
         <v>20000</v>
       </c>
       <c r="E7" t="n">
-        <v>6.46</v>
+        <v>6.44</v>
       </c>
       <c r="F7" t="n">
-        <v>358280</v>
+        <v>388080</v>
       </c>
       <c r="G7" t="n">
-        <v>115.78</v>
+        <v>125</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>青少年成长基地3月营（金盏基地） 188000.0；蛋壳跳动身心复能营21天（一阶） 119600.0；青少年基地3个月慈善价 49920.0</t>
+          <t>青少年成长基地3月营（金盏基地） 188000.0；蛋壳跳动身心复能营21天（一阶） 149400.0；青少年基地3个月慈善价 49920.0</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21780</v>
+        <v>33660</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1603988.02</v>
+        <v>1769102.02</v>
       </c>
       <c r="D2" t="n">
-        <v>4936</v>
+        <v>5331</v>
       </c>
       <c r="E2" t="n">
-        <v>1368605.02</v>
+        <v>1525017.02</v>
       </c>
       <c r="F2" t="n">
-        <v>235383</v>
+        <v>244085</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1464424</v>
+        <v>1620374</v>
       </c>
       <c r="D3" t="n">
-        <v>318</v>
+        <v>365</v>
       </c>
       <c r="E3" t="n">
-        <v>1233025</v>
+        <v>1380676</v>
       </c>
       <c r="F3" t="n">
-        <v>231399</v>
+        <v>239698</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>139564.02</v>
+        <v>148728.02</v>
       </c>
       <c r="D4" t="n">
-        <v>4618</v>
+        <v>4966</v>
       </c>
       <c r="E4" t="n">
-        <v>135580.02</v>
+        <v>144341.02</v>
       </c>
       <c r="F4" t="n">
-        <v>3984</v>
+        <v>4387</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3211975.82</v>
+        <v>3421271.82</v>
       </c>
       <c r="D5" t="n">
-        <v>637</v>
+        <v>674</v>
       </c>
       <c r="E5" t="n">
-        <v>696471.8</v>
+        <v>744087.8</v>
       </c>
       <c r="F5" t="n">
-        <v>2515504.02</v>
+        <v>2677184.02</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2297007.02</v>
+        <v>2437697.02</v>
       </c>
       <c r="D6" t="n">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="E6" t="n">
         <v>116440</v>
       </c>
       <c r="F6" t="n">
-        <v>2180567.02</v>
+        <v>2321257.02</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>894968.8</v>
+        <v>963574.8</v>
       </c>
       <c r="D7" t="n">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="E7" t="n">
-        <v>580031.8</v>
+        <v>627647.8</v>
       </c>
       <c r="F7" t="n">
-        <v>314937</v>
+        <v>335927</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2236888.76</v>
+        <v>2347040.34</v>
       </c>
       <c r="D8" t="n">
-        <v>1739</v>
+        <v>1869</v>
       </c>
       <c r="E8" t="n">
-        <v>34369.45</v>
+        <v>35069.45</v>
       </c>
       <c r="F8" t="n">
-        <v>2202519.31</v>
+        <v>2311970.89</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1387351.92</v>
+        <v>1433111.29</v>
       </c>
       <c r="D9" t="n">
-        <v>903</v>
+        <v>1023</v>
       </c>
       <c r="E9" t="n">
-        <v>12634.63</v>
+        <v>13134.63</v>
       </c>
       <c r="F9" t="n">
-        <v>1374717.29</v>
+        <v>1419976.66</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>847536.84</v>
+        <v>911929.05</v>
       </c>
       <c r="D10" t="n">
-        <v>835</v>
+        <v>845</v>
       </c>
       <c r="E10" t="n">
-        <v>21734.82</v>
+        <v>21934.82</v>
       </c>
       <c r="F10" t="n">
-        <v>825802.02</v>
+        <v>889994.23</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>482000</v>
+        <v>601000</v>
       </c>
       <c r="D11" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E11" t="n">
-        <v>224200</v>
+        <v>248000</v>
       </c>
       <c r="F11" t="n">
-        <v>257800</v>
+        <v>353000</v>
       </c>
     </row>
     <row r="12">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>310454</v>
+        <v>342234</v>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E13" t="n">
-        <v>190254</v>
+        <v>222034</v>
       </c>
       <c r="F13" t="n">
         <v>120200</v>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2018871.04</v>
+        <v>2126844.04</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 1922063.04；菌群线 49600.0；咨询线 42786.0；课程线 4422.0</t>
+          <t>医疗线 2030036.04；菌群线 49600.0；咨询线 42786.0；课程线 4422.0</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>490146.99</v>
+        <v>587045.99</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>69.09999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 338530.0；营地 50500.0；菌群线 45600.0；医疗线 37200.99；课程线 18316.0</t>
+          <t>咨询线 363330.0；菌群线 116000.0；营地 50500.0；医疗线 37200.99；课程线 20015.0</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>258196.96</v>
+        <v>267697.95</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -865,11 +865,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>74.09999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 191370.0；菌群线 24800.0；课程线 22220.0；医疗线 19806.96</t>
+          <t>咨询线 200370.0；菌群线 24800.0；课程线 22220.0；医疗线 20307.95</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>542985.72</v>
+        <v>572024.72</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>44</v>
+        <v>45.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 238738.02；菌群线 92200.0；课程线 88765.0；医疗线 42635.7；考证 40587.0；营地 36100.0；工作坊 3960.0</t>
+          <t>咨询线 261330.02；课程线 95412.0；菌群线 92200.0；医疗线 42435.7；考证 40587.0；营地 36100.0；工作坊 3960.0</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>502163.76</v>
+        <v>539386.86</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>68.5</v>
+        <v>70.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 344160.0；医疗线 81892.76；考证 40587.0；菌群线 22800.0；课程线 12724.0</t>
+          <t>咨询线 381260.0；医疗线 81996.86；考证 40587.0；菌群线 22800.0；课程线 12743.0</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>284528</v>
+        <v>325324</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -934,11 +934,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>94.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 269954.0；课程线 13575.0；考证 999.0；菌群线 0.0</t>
+          <t>咨询线 310750.0；课程线 13575.0；考证 999.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>381202.14</v>
+        <v>382432.35</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 328732.0；医疗线 31583.14；课程线 20887.0；菌群线 0.0</t>
+          <t>咨询线 329532.0；医疗线 32013.35；课程线 20887.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>300393.05</v>
+        <v>302632.33</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>88.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 266566.0；菌群线 22800.0；医疗线 9811.05；考证 999.0；课程线 217.0</t>
+          <t>咨询线 268162.0；菌群线 22800.0；医疗线 10454.33；考证 999.0；课程线 217.0</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>334007.7</v>
+        <v>350904.7</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1003,11 +1003,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>81.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 270928.0；医疗线 56422.7；课程线 6657.0；菌群线 0.0</t>
+          <t>咨询线 287526.0；医疗线 56422.7；课程线 6956.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>171426</v>
+        <v>171445</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1026,11 +1026,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>68.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 117174.0；营地 33600.0；课程线 16192.0；工作坊 3960.0；医疗线 500.0；菌群线 0.0</t>
+          <t>咨询线 117174.0；营地 33600.0；课程线 16211.0；工作坊 3960.0；医疗线 500.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>250448.97</v>
+        <v>283665.97</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1049,11 +1049,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>49.4</v>
+        <v>43.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>考证 123752.0；咨询线 106566.0；课程线 19828.0；医疗线 302.97；菌群线 0.0</t>
+          <t>考证 123752.0；咨询线 114964.0；菌群线 24800.0；课程线 19847.0；医疗线 302.97</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>74940</v>
+        <v>81540</v>
       </c>
     </row>
     <row r="4">
@@ -1140,11 +1140,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>龙少海</t>
+          <t>王渊亮</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>66000</v>
+        <v>72960</v>
       </c>
     </row>
     <row r="5">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>肖伟</t>
+          <t>龙少海</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>61600</v>
+        <v>72600</v>
       </c>
     </row>
     <row r="6">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>59400</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="7">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>171184</v>
+        <v>200184</v>
       </c>
     </row>
     <row r="8">
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>151180</v>
+        <v>159180</v>
       </c>
     </row>
     <row r="9">
@@ -1230,11 +1230,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>陈静</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>109168</v>
+        <v>137786</v>
       </c>
     </row>
     <row r="10">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>陈静</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>107388</v>
+        <v>109168</v>
       </c>
     </row>
     <row r="11">
@@ -1266,11 +1266,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>郑巨光</t>
+          <t>郑美琦</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>103996</v>
+        <v>105900</v>
       </c>
     </row>
     <row r="12">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>410510</v>
+        <v>414637</v>
       </c>
     </row>
     <row r="13">
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>385891.53</v>
+        <v>394214.53</v>
       </c>
     </row>
     <row r="14">
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>202395.74</v>
+        <v>222603</v>
       </c>
     </row>
     <row r="15">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>197482</v>
+        <v>202395.74</v>
       </c>
     </row>
     <row r="16">
@@ -1356,11 +1356,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>191116</v>
+        <v>197482</v>
       </c>
     </row>
     <row r="17">
@@ -1392,11 +1392,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>49600</v>
+        <v>70400</v>
       </c>
     </row>
     <row r="19">
@@ -1410,11 +1410,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>45600</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="20">
@@ -1572,11 +1572,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>王秋</t>
+          <t>闫丽东</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>36100</v>
+        <v>46600</v>
       </c>
     </row>
     <row r="29">
@@ -1590,11 +1590,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>刘沁</t>
+          <t>王秋</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>33700</v>
+        <v>36100</v>
       </c>
     </row>
     <row r="30">
@@ -1608,11 +1608,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>田婉丽</t>
+          <t>刘沁</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>33600</v>
+        <v>33700</v>
       </c>
     </row>
     <row r="31">
@@ -1626,11 +1626,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>江敏</t>
+          <t>田婉丽</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>29800</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="32">
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1603988.02</v>
+        <v>1769102.02</v>
       </c>
       <c r="C2" t="n">
-        <v>246272.58</v>
+        <v>281958.91</v>
       </c>
       <c r="D2" t="n">
-        <v>27781.01</v>
+        <v>31061.01</v>
       </c>
       <c r="E2" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="F2" t="n">
-        <v>218491.57</v>
+        <v>250897.9</v>
       </c>
       <c r="G2" t="n">
-        <v>13.62</v>
+        <v>14.18</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>青少年同行者计划护航营（6月） 56579.0；青少年同行者计划 52288.0；青少年同行者计划-护航营 31387.66</t>
+          <t>青少年同行者计划护航营（6月） 59965.0；青少年同行者计划 57268.0；少年说陪伴计划 39600.0</t>
         </is>
       </c>
     </row>
@@ -1816,26 +1816,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3211975.82</v>
+        <v>3421271.82</v>
       </c>
       <c r="C3" t="n">
-        <v>439328.28</v>
+        <v>524698.28</v>
       </c>
       <c r="D3" t="n">
-        <v>25398</v>
+        <v>35498</v>
       </c>
       <c r="E3" t="n">
-        <v>0.79</v>
+        <v>1.04</v>
       </c>
       <c r="F3" t="n">
-        <v>413930.28</v>
+        <v>489200.28</v>
       </c>
       <c r="G3" t="n">
-        <v>12.89</v>
+        <v>14.3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 175244.48；精神心理 116544.0；暑假礼遇咨询套餐 49600.0</t>
+          <t>儿童青少年 204242.48；精神心理 124694.0；暑假礼遇咨询套餐 73600.0</t>
         </is>
       </c>
     </row>
@@ -1846,26 +1846,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2236888.76</v>
+        <v>2347040.34</v>
       </c>
       <c r="C4" t="n">
-        <v>633773.5699999999</v>
+        <v>754690.5699999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1829</v>
+        <v>2029</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="F4" t="n">
-        <v>631944.5699999999</v>
+        <v>752661.5699999999</v>
       </c>
       <c r="G4" t="n">
-        <v>28.25</v>
+        <v>32.07</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>日间中心 Ⅱ 212000.0；治疗I（个体1000） 210861.14；日间中心 Ⅰ 78000.0</t>
+          <t>治疗I（个体1000） 294861.14；日间中心 Ⅱ 212000.0；日间中心 Ⅰ 78000.0</t>
         </is>
       </c>
     </row>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>482000</v>
+        <v>601000</v>
       </c>
       <c r="C5" t="n">
-        <v>261800</v>
+        <v>286600</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1888,14 +1888,14 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>261800</v>
+        <v>286600</v>
       </c>
       <c r="G5" t="n">
-        <v>54.32</v>
+        <v>47.69</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>肠道菌群移植 172600.0；肠道菌群移植（双疗程优惠）  45600.0；开业/店庆菌群移植优惠（深圳） 22800.0</t>
+          <t>肠道菌群移植 197400.0；肠道菌群移植（双疗程优惠）  45600.0；开业/店庆菌群移植优惠（深圳） 22800.0</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
         <v>603258.8100000001</v>
       </c>
       <c r="C6" t="n">
-        <v>152193.07</v>
+        <v>157073.07</v>
       </c>
       <c r="D6" t="n">
         <v>2017.9</v>
@@ -1918,14 +1918,14 @@
         <v>0.33</v>
       </c>
       <c r="F6" t="n">
-        <v>150175.17</v>
+        <v>155055.17</v>
       </c>
       <c r="G6" t="n">
-        <v>24.89</v>
+        <v>25.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 103016.0；心灯计划-实战派心理咨询师执业培训项目（初+中阶-尾款） 38788.0；观心学院-国康网心理咨询师专业技能培训（3788） 3156.67</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 103016.0；心灯计划-实战派心理咨询师执业培训项目（初+中阶-尾款） 38788.0；心理咨询基本功实战营 4880.0</t>
         </is>
       </c>
     </row>
@@ -1936,26 +1936,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>310454</v>
+        <v>342234</v>
       </c>
       <c r="C7" t="n">
-        <v>408080</v>
+        <v>437880</v>
       </c>
       <c r="D7" t="n">
         <v>20000</v>
       </c>
       <c r="E7" t="n">
-        <v>6.44</v>
+        <v>5.84</v>
       </c>
       <c r="F7" t="n">
-        <v>388080</v>
+        <v>417880</v>
       </c>
       <c r="G7" t="n">
-        <v>125</v>
+        <v>122.1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>青少年成长基地3月营（金盏基地） 188000.0；蛋壳跳动身心复能营21天（一阶） 149400.0；青少年基地3个月慈善价 49920.0</t>
+          <t>青少年成长基地3月营（金盏基地） 188000.0；蛋壳跳动身心复能营21天（一阶） 179200.0；青少年基地3个月慈善价 49920.0</t>
         </is>
       </c>
     </row>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1769102.02</v>
+        <v>1857331.02</v>
       </c>
       <c r="D2" t="n">
-        <v>5331</v>
+        <v>5760</v>
       </c>
       <c r="E2" t="n">
-        <v>1525017.02</v>
+        <v>1611042.02</v>
       </c>
       <c r="F2" t="n">
-        <v>244085</v>
+        <v>246289</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1620374</v>
+        <v>1695575</v>
       </c>
       <c r="D3" t="n">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="E3" t="n">
-        <v>1380676</v>
+        <v>1454178</v>
       </c>
       <c r="F3" t="n">
-        <v>239698</v>
+        <v>241397</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>148728.02</v>
+        <v>161756.02</v>
       </c>
       <c r="D4" t="n">
-        <v>4966</v>
+        <v>5369</v>
       </c>
       <c r="E4" t="n">
-        <v>144341.02</v>
+        <v>156864.02</v>
       </c>
       <c r="F4" t="n">
-        <v>4387</v>
+        <v>4892</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3421271.82</v>
+        <v>3577641.82</v>
       </c>
       <c r="D5" t="n">
-        <v>674</v>
+        <v>708</v>
       </c>
       <c r="E5" t="n">
         <v>744087.8</v>
       </c>
       <c r="F5" t="n">
-        <v>2677184.02</v>
+        <v>2833554.02</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2437697.02</v>
+        <v>2551081.02</v>
       </c>
       <c r="D6" t="n">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="E6" t="n">
         <v>116440</v>
       </c>
       <c r="F6" t="n">
-        <v>2321257.02</v>
+        <v>2434641.02</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>963574.8</v>
+        <v>1006560.8</v>
       </c>
       <c r="D7" t="n">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="E7" t="n">
         <v>627647.8</v>
       </c>
       <c r="F7" t="n">
-        <v>335927</v>
+        <v>378913</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2347040.34</v>
+        <v>2372956.94</v>
       </c>
       <c r="D8" t="n">
-        <v>1869</v>
+        <v>1893</v>
       </c>
       <c r="E8" t="n">
-        <v>35069.45</v>
+        <v>35328.79</v>
       </c>
       <c r="F8" t="n">
-        <v>2311970.89</v>
+        <v>2337628.15</v>
       </c>
     </row>
     <row r="9">
@@ -631,13 +631,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1433111.29</v>
+        <v>1433272.63</v>
       </c>
       <c r="D9" t="n">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="E9" t="n">
-        <v>13134.63</v>
+        <v>13295.97</v>
       </c>
       <c r="F9" t="n">
         <v>1419976.66</v>
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>911929.05</v>
+        <v>937684.3100000001</v>
       </c>
       <c r="D10" t="n">
-        <v>845</v>
+        <v>867</v>
       </c>
       <c r="E10" t="n">
-        <v>21934.82</v>
+        <v>22032.82</v>
       </c>
       <c r="F10" t="n">
-        <v>889994.23</v>
+        <v>915651.49</v>
       </c>
     </row>
     <row r="11">
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>601000</v>
+        <v>603000</v>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E11" t="n">
-        <v>248000</v>
+        <v>250000</v>
       </c>
       <c r="F11" t="n">
         <v>353000</v>
@@ -703,13 +703,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>603258.8100000001</v>
+        <v>608045.8100000001</v>
       </c>
       <c r="D12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E12" t="n">
-        <v>396334.81</v>
+        <v>401121.81</v>
       </c>
       <c r="F12" t="n">
         <v>206924</v>
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>33660</v>
+        <v>65340</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E14" t="n">
-        <v>25740</v>
+        <v>49500</v>
       </c>
       <c r="F14" t="n">
-        <v>7920</v>
+        <v>15840</v>
       </c>
     </row>
   </sheetData>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2126844.04</v>
+        <v>2153832.64</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 2030036.04；菌群线 49600.0；咨询线 42786.0；课程线 4422.0</t>
+          <t>医疗线 2055025.64；菌群线 49600.0；咨询线 42786.0；课程线 4441.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>587045.99</v>
+        <v>637819.99</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>61.9</v>
+        <v>63.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 363330.0；菌群线 116000.0；营地 50500.0；医疗线 37200.99；课程线 20015.0</t>
+          <t>咨询线 405524.0；菌群线 116000.0；营地 50500.0；医疗线 37200.99；课程线 26615.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>267697.95</v>
+        <v>290091.95</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -865,11 +865,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>74.8</v>
+        <v>76.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 200370.0；菌群线 24800.0；课程线 22220.0；医疗线 20307.95</t>
+          <t>咨询线 222764.0；菌群线 24800.0；课程线 22220.0；医疗线 20307.95</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>572024.72</v>
+        <v>602062.72</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>45.7</v>
+        <v>49.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 261330.02；课程线 95412.0；菌群线 92200.0；医疗线 42435.7；考证 40587.0；营地 36100.0；工作坊 3960.0</t>
+          <t>咨询线 297930.02；菌群线 92200.0；课程线 88850.0；医疗线 42435.7；考证 40587.0；营地 36100.0；工作坊 3960.0</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>539386.86</v>
+        <v>540830.86</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 381260.0；医疗线 81996.86；考证 40587.0；菌群线 22800.0；课程线 12743.0</t>
+          <t>咨询线 382256.0；医疗线 81996.86；考证 40587.0；菌群线 22800.0；课程线 13191.0</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>325324</v>
+        <v>325343</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 310750.0；课程线 13575.0；考证 999.0；菌群线 0.0</t>
+          <t>咨询线 310750.0；课程线 13594.0；考证 999.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>382432.35</v>
+        <v>383807.35</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 329532.0；医疗线 32013.35；课程线 20887.0；菌群线 0.0</t>
+          <t>咨询线 330926.0；医疗线 32013.35；课程线 20868.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>302632.33</v>
+        <v>313887.09</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>88.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 268162.0；菌群线 22800.0；医疗线 10454.33；考证 999.0；课程线 217.0</t>
+          <t>咨询线 278962.0；菌群线 22800.0；医疗线 10890.09；考证 999.0；课程线 236.0</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>350904.7</v>
+        <v>369612.6</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1003,11 +1003,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>81.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 287526.0；医疗线 56422.7；课程线 6956.0；菌群线 0.0</t>
+          <t>咨询线 304322.0；医疗线 56654.6；课程线 8636.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>171445</v>
+        <v>181405</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1026,11 +1026,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>68.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 117174.0；营地 33600.0；课程线 16211.0；工作坊 3960.0；医疗线 500.0；菌群线 0.0</t>
+          <t>咨询线 123174.0；营地 33600.0；课程线 16211.0；工作坊 7920.0；医疗线 500.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1041,19 +1041,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>283665.97</v>
+        <v>302861.97</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>考证</t>
+          <t>咨询线</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>43.6</v>
+        <v>44.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>考证 123752.0；咨询线 114964.0；菌群线 24800.0；课程线 19847.0；医疗线 302.97</t>
+          <t>咨询线 134160.0；考证 123752.0；菌群线 24800.0；课程线 19847.0；医疗线 302.97</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>72960</v>
+        <v>80920</v>
       </c>
     </row>
     <row r="5">
@@ -1176,11 +1176,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>66000</v>
+        <v>69190</v>
       </c>
     </row>
     <row r="7">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>200184</v>
+        <v>200582</v>
       </c>
     </row>
     <row r="8">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>109168</v>
+        <v>135768</v>
       </c>
     </row>
     <row r="11">
@@ -1266,11 +1266,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>郑美琦</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>105900</v>
+        <v>112168</v>
       </c>
     </row>
     <row r="12">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>赵越</t>
+          <t>许冰</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>许冰</t>
+          <t>赵越</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>134776</v>
+        <v>138564</v>
       </c>
     </row>
     <row r="24">
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11880</v>
+        <v>23760</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>7920</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="34">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>余婉丽</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>田婉丽</t>
+          <t>余婉丽</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1716,11 +1716,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>安百柠</t>
+          <t>陈新星</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1980</v>
+        <v>3960</v>
       </c>
     </row>
   </sheetData>
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1769102.02</v>
+        <v>1857331.02</v>
       </c>
       <c r="C2" t="n">
-        <v>281958.91</v>
+        <v>304737.91</v>
       </c>
       <c r="D2" t="n">
-        <v>31061.01</v>
+        <v>34640.01</v>
       </c>
       <c r="E2" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="F2" t="n">
-        <v>250897.9</v>
+        <v>270097.9</v>
       </c>
       <c r="G2" t="n">
-        <v>14.18</v>
+        <v>14.54</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>青少年同行者计划护航营（6月） 59965.0；青少年同行者计划 57268.0；少年说陪伴计划 39600.0</t>
+          <t>青少年同行者计划护航营（6月） 64945.0；青少年同行者计划 62248.0；青少年同行者计划-护航营 41346.99</t>
         </is>
       </c>
     </row>
@@ -1816,26 +1816,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3421271.82</v>
+        <v>3577641.82</v>
       </c>
       <c r="C3" t="n">
-        <v>524698.28</v>
+        <v>567596.28</v>
       </c>
       <c r="D3" t="n">
         <v>35498</v>
       </c>
       <c r="E3" t="n">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="F3" t="n">
-        <v>489200.28</v>
+        <v>532098.28</v>
       </c>
       <c r="G3" t="n">
-        <v>14.3</v>
+        <v>14.87</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 204242.48；精神心理 124694.0；暑假礼遇咨询套餐 73600.0</t>
+          <t>儿童青少年 214242.48；精神心理 153194.0；暑假礼遇咨询套餐 73600.0</t>
         </is>
       </c>
     </row>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2347040.34</v>
+        <v>2372956.94</v>
       </c>
       <c r="C4" t="n">
-        <v>754690.5699999999</v>
+        <v>761070.5699999999</v>
       </c>
       <c r="D4" t="n">
         <v>2029</v>
@@ -1858,14 +1858,14 @@
         <v>0.09</v>
       </c>
       <c r="F4" t="n">
-        <v>752661.5699999999</v>
+        <v>759041.5699999999</v>
       </c>
       <c r="G4" t="n">
-        <v>32.07</v>
+        <v>31.99</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>治疗I（个体1000） 294861.14；日间中心 Ⅱ 212000.0；日间中心 Ⅰ 78000.0</t>
+          <t>治疗I（个体1000） 294861.14；日间中心 Ⅱ 212000.0；日间中心 Ⅰ 84000.0</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>601000</v>
+        <v>603000</v>
       </c>
       <c r="C5" t="n">
         <v>286600</v>
@@ -1891,7 +1891,7 @@
         <v>286600</v>
       </c>
       <c r="G5" t="n">
-        <v>47.69</v>
+        <v>47.53</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>603258.8100000001</v>
+        <v>608045.8100000001</v>
       </c>
       <c r="C6" t="n">
         <v>157073.07</v>
@@ -1921,7 +1921,7 @@
         <v>155055.17</v>
       </c>
       <c r="G6" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33660</v>
+        <v>65340</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1857331.02</v>
+        <v>1907541.02</v>
       </c>
       <c r="D2" t="n">
-        <v>5760</v>
+        <v>6102</v>
       </c>
       <c r="E2" t="n">
-        <v>1611042.02</v>
+        <v>1654377.02</v>
       </c>
       <c r="F2" t="n">
-        <v>246289</v>
+        <v>253164</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1695575</v>
+        <v>1734219</v>
       </c>
       <c r="D3" t="n">
-        <v>391</v>
+        <v>414</v>
       </c>
       <c r="E3" t="n">
-        <v>1454178</v>
+        <v>1486165</v>
       </c>
       <c r="F3" t="n">
-        <v>241397</v>
+        <v>248054</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>161756.02</v>
+        <v>173322.02</v>
       </c>
       <c r="D4" t="n">
-        <v>5369</v>
+        <v>5688</v>
       </c>
       <c r="E4" t="n">
-        <v>156864.02</v>
+        <v>168212.02</v>
       </c>
       <c r="F4" t="n">
-        <v>4892</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3577641.82</v>
+        <v>3707035.82</v>
       </c>
       <c r="D5" t="n">
-        <v>708</v>
+        <v>737</v>
       </c>
       <c r="E5" t="n">
-        <v>744087.8</v>
+        <v>758907.8</v>
       </c>
       <c r="F5" t="n">
-        <v>2833554.02</v>
+        <v>2948128.02</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2551081.02</v>
+        <v>2624859.02</v>
       </c>
       <c r="D6" t="n">
-        <v>456</v>
+        <v>479</v>
       </c>
       <c r="E6" t="n">
         <v>116440</v>
       </c>
       <c r="F6" t="n">
-        <v>2434641.02</v>
+        <v>2508419.02</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1006560.8</v>
+        <v>1062176.8</v>
       </c>
       <c r="D7" t="n">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="E7" t="n">
-        <v>627647.8</v>
+        <v>642467.8</v>
       </c>
       <c r="F7" t="n">
-        <v>378913</v>
+        <v>419709</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2372956.94</v>
+        <v>2521367.63</v>
       </c>
       <c r="D8" t="n">
-        <v>1893</v>
+        <v>2014</v>
       </c>
       <c r="E8" t="n">
-        <v>35328.79</v>
+        <v>37235</v>
       </c>
       <c r="F8" t="n">
-        <v>2337628.15</v>
+        <v>2484132.63</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1433272.63</v>
+        <v>1522772.32</v>
       </c>
       <c r="D9" t="n">
-        <v>1025</v>
+        <v>1075</v>
       </c>
       <c r="E9" t="n">
-        <v>13295.97</v>
+        <v>13402.18</v>
       </c>
       <c r="F9" t="n">
-        <v>1419976.66</v>
+        <v>1509370.14</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>937684.3100000001</v>
+        <v>996595.3100000001</v>
       </c>
       <c r="D10" t="n">
-        <v>867</v>
+        <v>938</v>
       </c>
       <c r="E10" t="n">
-        <v>22032.82</v>
+        <v>23832.82</v>
       </c>
       <c r="F10" t="n">
-        <v>915651.49</v>
+        <v>972762.49</v>
       </c>
     </row>
     <row r="11">
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>603000</v>
+        <v>673400</v>
       </c>
       <c r="D11" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>250000</v>
+        <v>320400</v>
       </c>
       <c r="F11" t="n">
         <v>353000</v>
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>608045.8100000001</v>
+        <v>651421.8100000001</v>
       </c>
       <c r="D12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E12" t="n">
-        <v>401121.81</v>
+        <v>445496.81</v>
       </c>
       <c r="F12" t="n">
-        <v>206924</v>
+        <v>205925</v>
       </c>
     </row>
     <row r="13">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>65340</v>
+        <v>67320</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
         <v>49500</v>
       </c>
       <c r="F14" t="n">
-        <v>15840</v>
+        <v>17820</v>
       </c>
     </row>
   </sheetData>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2153832.64</v>
+        <v>2297588.42</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>95.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 2055025.64；菌群线 49600.0；咨询线 42786.0；课程线 4441.0；工作坊 1980.0</t>
+          <t>医疗线 2198781.42；菌群线 49600.0；咨询线 42786.0；课程线 4441.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>637819.99</v>
+        <v>650805.99</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>63.6</v>
+        <v>64.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 405524.0；菌群线 116000.0；营地 50500.0；医疗线 37200.99；课程线 26615.0；工作坊 1980.0</t>
+          <t>咨询线 418320.0；菌群线 116000.0；营地 50500.0；医疗线 37200.99；课程线 26805.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>290091.95</v>
+        <v>303708.95</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -865,11 +865,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>76.8</v>
+        <v>77.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 222764.0；菌群线 24800.0；课程线 22220.0；医疗线 20307.95</t>
+          <t>咨询线 236162.0；菌群线 24800.0；课程线 22239.0；医疗线 20507.95</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>602062.72</v>
+        <v>626060.72</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>49.5</v>
+        <v>49.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 297930.02；菌群线 92200.0；课程线 88850.0；医疗线 42435.7；考证 40587.0；营地 36100.0；工作坊 3960.0</t>
+          <t>咨询线 312528.02；课程线 95469.0；菌群线 92200.0；医疗线 44235.7；考证 39588.0；营地 36100.0；工作坊 5940.0</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>540830.86</v>
+        <v>553607.5600000001</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>70.7</v>
+        <v>71.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 382256.0；医疗线 81996.86；考证 40587.0；菌群线 22800.0；课程线 13191.0</t>
+          <t>咨询线 394256.0；医疗线 82745.56；考证 40587.0；菌群线 22800.0；课程线 13219.0</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>325343</v>
+        <v>325741</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 310750.0；课程线 13594.0；考证 999.0；菌群线 0.0</t>
+          <t>咨询线 311148.0；课程线 13594.0；考证 999.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>383807.35</v>
+        <v>392405.35</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -957,11 +957,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>86.2</v>
+        <v>86.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 330926.0；医疗线 32013.35；课程线 20868.0；菌群线 0.0</t>
+          <t>咨询线 339524.0；医疗线 32013.35；课程线 20868.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>313887.09</v>
+        <v>343485.09</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>88.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 278962.0；菌群线 22800.0；医疗线 10890.09；考证 999.0；课程线 236.0</t>
+          <t>咨询线 308560.0；菌群线 22800.0；医疗线 10890.09；考证 999.0；课程线 236.0</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>369612.6</v>
+        <v>370806.6</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1003,11 +1003,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 304322.0；医疗线 56654.6；课程线 8636.0；菌群线 0.0</t>
+          <t>咨询线 305516.0；医疗线 56654.6；课程线 8636.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>181405</v>
+        <v>195001</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1026,11 +1026,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>67.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 123174.0；营地 33600.0；课程线 16211.0；工作坊 7920.0；医疗线 500.0；菌群线 0.0</t>
+          <t>咨询线 136770.0；营地 33600.0；课程线 16211.0；工作坊 7920.0；医疗线 500.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>302861.97</v>
+        <v>311278.97</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1049,11 +1049,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>44.3</v>
+        <v>45.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 134160.0；考证 123752.0；菌群线 24800.0；课程线 19847.0；医疗线 302.97</t>
+          <t>咨询线 142558.0；考证 123752.0；菌群线 24800.0；课程线 19866.0；医疗线 302.97</t>
         </is>
       </c>
     </row>
@@ -1176,11 +1176,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>肖伟</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>69190</v>
+        <v>69560</v>
       </c>
     </row>
     <row r="7">
@@ -1230,11 +1230,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>陈静</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>137786</v>
+        <v>148968</v>
       </c>
     </row>
     <row r="10">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>陈静</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>135768</v>
+        <v>137786</v>
       </c>
     </row>
     <row r="11">
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>112168</v>
+        <v>112964</v>
       </c>
     </row>
     <row r="12">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>414637</v>
+        <v>416437</v>
       </c>
     </row>
     <row r="13">
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>394214.53</v>
+        <v>412882.74</v>
       </c>
     </row>
     <row r="14">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>222603</v>
+        <v>229670.57</v>
       </c>
     </row>
     <row r="15">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>202395.74</v>
+        <v>221083</v>
       </c>
     </row>
     <row r="16">
@@ -1356,11 +1356,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>197482</v>
+        <v>217584.74</v>
       </c>
     </row>
     <row r="17">
@@ -1428,11 +1428,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>许冰</t>
+          <t>龙少海</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>45600</v>
+        <v>46600</v>
       </c>
     </row>
     <row r="21">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>赵越</t>
+          <t>许冰</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>138564</v>
+        <v>181940</v>
       </c>
     </row>
     <row r="24">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>余婉丽</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>余婉丽</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>陈新星</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1857331.02</v>
+        <v>1907541.02</v>
       </c>
       <c r="C2" t="n">
-        <v>304737.91</v>
+        <v>312709.91</v>
       </c>
       <c r="D2" t="n">
-        <v>34640.01</v>
+        <v>37632.01</v>
       </c>
       <c r="E2" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="F2" t="n">
-        <v>270097.9</v>
+        <v>275077.9</v>
       </c>
       <c r="G2" t="n">
-        <v>14.54</v>
+        <v>14.42</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>青少年同行者计划护航营（6月） 64945.0；青少年同行者计划 62248.0；青少年同行者计划-护航营 41346.99</t>
+          <t>青少年同行者计划 67228.0；青少年同行者计划护航营（6月） 64945.0；青少年同行者计划-护航营 41346.99</t>
         </is>
       </c>
     </row>
@@ -1816,26 +1816,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3577641.82</v>
+        <v>3707035.82</v>
       </c>
       <c r="C3" t="n">
-        <v>567596.28</v>
+        <v>612596.28</v>
       </c>
       <c r="D3" t="n">
         <v>35498</v>
       </c>
       <c r="E3" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="F3" t="n">
-        <v>532098.28</v>
+        <v>577098.28</v>
       </c>
       <c r="G3" t="n">
-        <v>14.87</v>
+        <v>15.57</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 214242.48；精神心理 153194.0；暑假礼遇咨询套餐 73600.0</t>
+          <t>儿童青少年 231242.48；精神心理 173194.0；暑假礼遇咨询套餐 73600.0</t>
         </is>
       </c>
     </row>
@@ -1846,26 +1846,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2372956.94</v>
+        <v>2521367.63</v>
       </c>
       <c r="C4" t="n">
-        <v>761070.5699999999</v>
+        <v>848421.5699999999</v>
       </c>
       <c r="D4" t="n">
         <v>2029</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F4" t="n">
-        <v>759041.5699999999</v>
+        <v>846392.5699999999</v>
       </c>
       <c r="G4" t="n">
-        <v>31.99</v>
+        <v>33.57</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>治疗I（个体1000） 294861.14；日间中心 Ⅱ 212000.0；日间中心 Ⅰ 84000.0</t>
+          <t>治疗I（个体1000） 315861.14；日间中心 Ⅱ 212000.0；日间中心 Ⅰ 126000.0</t>
         </is>
       </c>
     </row>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>603000</v>
+        <v>673400</v>
       </c>
       <c r="C5" t="n">
-        <v>286600</v>
+        <v>311400</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1888,14 +1888,14 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>286600</v>
+        <v>311400</v>
       </c>
       <c r="G5" t="n">
-        <v>47.53</v>
+        <v>46.24</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>肠道菌群移植 197400.0；肠道菌群移植（双疗程优惠）  45600.0；开业/店庆菌群移植优惠（深圳） 22800.0</t>
+          <t>肠道菌群移植 222200.0；肠道菌群移植（双疗程优惠）  45600.0；开业/店庆菌群移植优惠（深圳） 22800.0</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>608045.8100000001</v>
+        <v>651421.8100000001</v>
       </c>
       <c r="C6" t="n">
         <v>157073.07</v>
@@ -1915,13 +1915,13 @@
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="F6" t="n">
         <v>155055.17</v>
       </c>
       <c r="G6" t="n">
-        <v>25.5</v>
+        <v>23.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>342234</v>
       </c>
       <c r="C7" t="n">
-        <v>437880</v>
+        <v>467680</v>
       </c>
       <c r="D7" t="n">
         <v>20000</v>
@@ -1948,14 +1948,14 @@
         <v>5.84</v>
       </c>
       <c r="F7" t="n">
-        <v>417880</v>
+        <v>447680</v>
       </c>
       <c r="G7" t="n">
-        <v>122.1</v>
+        <v>130.81</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>青少年成长基地3月营（金盏基地） 188000.0；蛋壳跳动身心复能营21天（一阶） 179200.0；青少年基地3个月慈善价 49920.0</t>
+          <t>蛋壳跳动身心复能营21天（一阶） 209000.0；青少年成长基地3月营（金盏基地） 188000.0；青少年基地3个月慈善价 49920.0</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>65340</v>
+        <v>67320</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1907541.02</v>
+        <v>2052421.07</v>
       </c>
       <c r="D2" t="n">
-        <v>6102</v>
+        <v>6579</v>
       </c>
       <c r="E2" t="n">
-        <v>1654377.02</v>
+        <v>1797283.07</v>
       </c>
       <c r="F2" t="n">
-        <v>253164</v>
+        <v>255138</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1734219</v>
+        <v>1864690</v>
       </c>
       <c r="D3" t="n">
-        <v>414</v>
+        <v>455</v>
       </c>
       <c r="E3" t="n">
-        <v>1486165</v>
+        <v>1614918</v>
       </c>
       <c r="F3" t="n">
-        <v>248054</v>
+        <v>249772</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>173322.02</v>
+        <v>187731.07</v>
       </c>
       <c r="D4" t="n">
-        <v>5688</v>
+        <v>6124</v>
       </c>
       <c r="E4" t="n">
-        <v>168212.02</v>
+        <v>182365.07</v>
       </c>
       <c r="F4" t="n">
-        <v>5110</v>
+        <v>5366</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3707035.82</v>
+        <v>3915139.82</v>
       </c>
       <c r="D5" t="n">
-        <v>737</v>
+        <v>767</v>
       </c>
       <c r="E5" t="n">
-        <v>758907.8</v>
+        <v>816925.8</v>
       </c>
       <c r="F5" t="n">
-        <v>2948128.02</v>
+        <v>3098214.02</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2624859.02</v>
+        <v>2765655.02</v>
       </c>
       <c r="D6" t="n">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="E6" t="n">
         <v>116440</v>
       </c>
       <c r="F6" t="n">
-        <v>2508419.02</v>
+        <v>2649215.02</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1062176.8</v>
+        <v>1129484.8</v>
       </c>
       <c r="D7" t="n">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="E7" t="n">
-        <v>642467.8</v>
+        <v>700485.8</v>
       </c>
       <c r="F7" t="n">
-        <v>419709</v>
+        <v>428999</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2521367.63</v>
+        <v>2579598.23</v>
       </c>
       <c r="D8" t="n">
-        <v>2014</v>
+        <v>2027</v>
       </c>
       <c r="E8" t="n">
-        <v>37235</v>
+        <v>37435</v>
       </c>
       <c r="F8" t="n">
-        <v>2484132.63</v>
+        <v>2542163.23</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1522772.32</v>
+        <v>1579733.32</v>
       </c>
       <c r="D9" t="n">
-        <v>1075</v>
+        <v>1085</v>
       </c>
       <c r="E9" t="n">
         <v>13402.18</v>
       </c>
       <c r="F9" t="n">
-        <v>1509370.14</v>
+        <v>1566331.14</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>996595.3100000001</v>
+        <v>997864.91</v>
       </c>
       <c r="D10" t="n">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="E10" t="n">
-        <v>23832.82</v>
+        <v>24032.82</v>
       </c>
       <c r="F10" t="n">
-        <v>972762.49</v>
+        <v>973832.09</v>
       </c>
     </row>
     <row r="11">
@@ -703,13 +703,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>651421.8100000001</v>
+        <v>655209.8100000001</v>
       </c>
       <c r="D12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E12" t="n">
-        <v>445496.81</v>
+        <v>449284.81</v>
       </c>
       <c r="F12" t="n">
         <v>205925</v>
@@ -751,13 +751,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>67320</v>
+        <v>71280</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E14" t="n">
-        <v>49500</v>
+        <v>53460</v>
       </c>
       <c r="F14" t="n">
         <v>17820</v>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2297588.42</v>
+        <v>2338749.42</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>95.7</v>
+        <v>95.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 2198781.42；菌群线 49600.0；咨询线 42786.0；课程线 4441.0；工作坊 1980.0</t>
+          <t>医疗线 2239942.42；菌群线 49600.0；咨询线 42786.0；课程线 4441.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>650805.99</v>
+        <v>689126.99</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>64.3</v>
+        <v>63.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 418320.0；菌群线 116000.0；营地 50500.0；医疗线 37200.99；课程线 26805.0；工作坊 1980.0</t>
+          <t>咨询线 439718.0；菌群线 116000.0；医疗线 54000.99；营地 50500.0；课程线 26928.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>303708.95</v>
+        <v>305144.95</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -865,11 +865,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>77.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 236162.0；菌群线 24800.0；课程线 22239.0；医疗线 20507.95</t>
+          <t>咨询线 237560.0；菌群线 24800.0；课程线 22277.0；医疗线 20507.95</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>626060.72</v>
+        <v>634894.72</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>49.9</v>
+        <v>50.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 312528.02；课程线 95469.0；菌群线 92200.0；医疗线 44235.7；考证 39588.0；营地 36100.0；工作坊 5940.0</t>
+          <t>咨询线 321324.02；课程线 95507.0；菌群线 92200.0；医疗线 44235.7；考证 39588.0；营地 36100.0；工作坊 5940.0</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>553607.5600000001</v>
+        <v>565894.16</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>71.2</v>
+        <v>71.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 394256.0；医疗线 82745.56；考证 40587.0；菌群线 22800.0；课程线 13219.0</t>
+          <t>咨询线 406454.0；医疗线 82815.16；考证 40587.0；菌群线 22800.0；课程线 13238.0</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>325741</v>
+        <v>357440</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -934,11 +934,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>95.5</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 311148.0；课程线 13594.0；考证 999.0；菌群线 0.0</t>
+          <t>咨询线 341148.0；课程线 15293.0；考证 999.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>392405.35</v>
+        <v>427822.35</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -957,11 +957,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>86.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 339524.0；医疗线 32013.35；课程线 20868.0；菌群线 0.0</t>
+          <t>咨询线 374922.0；医疗线 32013.35；课程线 20887.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>343485.09</v>
+        <v>373985.09</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>89.8</v>
+        <v>90.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 308560.0；菌群线 22800.0；医疗线 10890.09；考证 999.0；课程线 236.0</t>
+          <t>咨询线 339060.0；菌群线 22800.0；医疗线 10890.09；考证 999.0；课程线 236.0</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>370806.6</v>
+        <v>370825.6</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 305516.0；医疗线 56654.6；课程线 8636.0；菌群线 0.0</t>
+          <t>咨询线 305516.0；医疗线 56654.6；课程线 8655.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>195001</v>
+        <v>195418</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1026,11 +1026,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 136770.0；营地 33600.0；课程线 16211.0；工作坊 7920.0；医疗线 500.0；菌群线 0.0</t>
+          <t>咨询线 137168.0；营地 33600.0；课程线 16230.0；工作坊 7920.0；医疗线 500.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>311278.97</v>
+        <v>321278.97</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1049,11 +1049,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>45.8</v>
+        <v>47.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 142558.0；考证 123752.0；菌群线 24800.0；课程线 19866.0；医疗线 302.97</t>
+          <t>咨询线 152558.0；考证 123752.0；菌群线 24800.0；课程线 19866.0；医疗线 302.97</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>88780</v>
+        <v>103340</v>
       </c>
     </row>
     <row r="3">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>龙少海</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>72600</v>
+        <v>79600</v>
       </c>
     </row>
     <row r="6">
@@ -1176,11 +1176,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>肖伟</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>69560</v>
+        <v>73170</v>
       </c>
     </row>
     <row r="7">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>200582</v>
+        <v>210582</v>
       </c>
     </row>
     <row r="8">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>137786</v>
+        <v>147786</v>
       </c>
     </row>
     <row r="11">
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>112964</v>
+        <v>133964</v>
       </c>
     </row>
     <row r="12">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>416437</v>
+        <v>420301.74</v>
       </c>
     </row>
     <row r="13">
@@ -1302,11 +1302,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>412882.74</v>
+        <v>414662</v>
       </c>
     </row>
     <row r="14">
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>229670.57</v>
+        <v>247083</v>
       </c>
     </row>
     <row r="15">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>221083</v>
+        <v>222251.57</v>
       </c>
     </row>
     <row r="16">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>217584.74</v>
+        <v>219359.74</v>
       </c>
     </row>
     <row r="17">
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>181940</v>
+        <v>185728</v>
       </c>
     </row>
     <row r="24">
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>23760</v>
+        <v>25740</v>
       </c>
     </row>
     <row r="33">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>余婉丽</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>张孟蝶</t>
+          <t>陈新星</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1907541.02</v>
+        <v>2052421.07</v>
       </c>
       <c r="C2" t="n">
-        <v>312709.91</v>
+        <v>325206.91</v>
       </c>
       <c r="D2" t="n">
-        <v>37632.01</v>
+        <v>40918.01</v>
       </c>
       <c r="E2" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="F2" t="n">
-        <v>275077.9</v>
+        <v>284288.9</v>
       </c>
       <c r="G2" t="n">
-        <v>14.42</v>
+        <v>13.85</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>青少年同行者计划 67228.0；青少年同行者计划护航营（6月） 64945.0；青少年同行者计划-护航营 41346.99</t>
+          <t>青少年同行者计划 67228.0；青少年同行者计划护航营（6月） 64945.0；青少年同行者计划-护航营 43938.99</t>
         </is>
       </c>
     </row>
@@ -1816,26 +1816,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3707035.82</v>
+        <v>3915139.82</v>
       </c>
       <c r="C3" t="n">
-        <v>612596.28</v>
+        <v>623994.28</v>
       </c>
       <c r="D3" t="n">
         <v>35498</v>
       </c>
       <c r="E3" t="n">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="F3" t="n">
-        <v>577098.28</v>
+        <v>588496.28</v>
       </c>
       <c r="G3" t="n">
-        <v>15.57</v>
+        <v>15.03</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 231242.48；精神心理 173194.0；暑假礼遇咨询套餐 73600.0</t>
+          <t>儿童青少年 232242.48；精神心理 183194.0；暑假礼遇咨询套餐 73600.0</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2521367.63</v>
+        <v>2579598.23</v>
       </c>
       <c r="C4" t="n">
         <v>848421.5699999999</v>
@@ -1861,7 +1861,7 @@
         <v>846392.5699999999</v>
       </c>
       <c r="G4" t="n">
-        <v>33.57</v>
+        <v>32.81</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>673400</v>
       </c>
       <c r="C5" t="n">
-        <v>311400</v>
+        <v>335200</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1888,14 +1888,14 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>311400</v>
+        <v>335200</v>
       </c>
       <c r="G5" t="n">
-        <v>46.24</v>
+        <v>49.78</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>肠道菌群移植 222200.0；肠道菌群移植（双疗程优惠）  45600.0；开业/店庆菌群移植优惠（深圳） 22800.0</t>
+          <t>肠道菌群移植 246000.0；肠道菌群移植（双疗程优惠）  45600.0；开业/店庆菌群移植优惠（深圳） 22800.0</t>
         </is>
       </c>
     </row>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>651421.8100000001</v>
+        <v>655209.8100000001</v>
       </c>
       <c r="C6" t="n">
-        <v>157073.07</v>
+        <v>173061.07</v>
       </c>
       <c r="D6" t="n">
         <v>2017.9</v>
@@ -1918,14 +1918,14 @@
         <v>0.31</v>
       </c>
       <c r="F6" t="n">
-        <v>155055.17</v>
+        <v>171043.17</v>
       </c>
       <c r="G6" t="n">
-        <v>23.8</v>
+        <v>26.11</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 103016.0；心灯计划-实战派心理咨询师执业培训项目（初+中阶-尾款） 38788.0；心理咨询基本功实战营 4880.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 119004.0；心灯计划-实战派心理咨询师执业培训项目（初+中阶-尾款） 38788.0；心理咨询基本功实战营 4880.0</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>67320</v>
+        <v>71280</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2052421.07</v>
+        <v>2123775.07</v>
       </c>
       <c r="D2" t="n">
-        <v>6579</v>
+        <v>6925</v>
       </c>
       <c r="E2" t="n">
-        <v>1797283.07</v>
+        <v>1861619.07</v>
       </c>
       <c r="F2" t="n">
-        <v>255138</v>
+        <v>262156</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1864690</v>
+        <v>1927088</v>
       </c>
       <c r="D3" t="n">
-        <v>455</v>
+        <v>478</v>
       </c>
       <c r="E3" t="n">
-        <v>1614918</v>
+        <v>1670697</v>
       </c>
       <c r="F3" t="n">
-        <v>249772</v>
+        <v>256391</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>187731.07</v>
+        <v>196687.07</v>
       </c>
       <c r="D4" t="n">
-        <v>6124</v>
+        <v>6447</v>
       </c>
       <c r="E4" t="n">
-        <v>182365.07</v>
+        <v>190922.07</v>
       </c>
       <c r="F4" t="n">
-        <v>5366</v>
+        <v>5765</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3915139.82</v>
+        <v>4010753.82</v>
       </c>
       <c r="D5" t="n">
-        <v>767</v>
+        <v>817</v>
       </c>
       <c r="E5" t="n">
-        <v>816925.8</v>
+        <v>811945.8</v>
       </c>
       <c r="F5" t="n">
-        <v>3098214.02</v>
+        <v>3198808.02</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2765655.02</v>
+        <v>2871643.02</v>
       </c>
       <c r="D6" t="n">
-        <v>497</v>
+        <v>535</v>
       </c>
       <c r="E6" t="n">
         <v>116440</v>
       </c>
       <c r="F6" t="n">
-        <v>2649215.02</v>
+        <v>2755203.02</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1129484.8</v>
+        <v>1119110.8</v>
       </c>
       <c r="D7" t="n">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="E7" t="n">
-        <v>700485.8</v>
+        <v>695505.8</v>
       </c>
       <c r="F7" t="n">
-        <v>428999</v>
+        <v>423605</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2579598.23</v>
+        <v>2841988.04</v>
       </c>
       <c r="D8" t="n">
-        <v>2027</v>
+        <v>2087</v>
       </c>
       <c r="E8" t="n">
-        <v>37435</v>
+        <v>38424.25</v>
       </c>
       <c r="F8" t="n">
-        <v>2542163.23</v>
+        <v>2803563.79</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1579733.32</v>
+        <v>1670814.89</v>
       </c>
       <c r="D9" t="n">
-        <v>1085</v>
+        <v>1130</v>
       </c>
       <c r="E9" t="n">
-        <v>13402.18</v>
+        <v>13802.18</v>
       </c>
       <c r="F9" t="n">
-        <v>1566331.14</v>
+        <v>1657012.71</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>997864.91</v>
+        <v>1169173.15</v>
       </c>
       <c r="D10" t="n">
-        <v>941</v>
+        <v>956</v>
       </c>
       <c r="E10" t="n">
-        <v>24032.82</v>
+        <v>24622.07</v>
       </c>
       <c r="F10" t="n">
-        <v>973832.09</v>
+        <v>1144551.08</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>673400</v>
+        <v>698200</v>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E11" t="n">
         <v>320400</v>
       </c>
       <c r="F11" t="n">
-        <v>353000</v>
+        <v>377800</v>
       </c>
     </row>
     <row r="12">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2338749.42</v>
+        <v>2609948.99</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 2239942.42；菌群线 49600.0；咨询线 42786.0；课程线 4441.0；工作坊 1980.0</t>
+          <t>医疗线 2500941.99；咨询线 52786.0；菌群线 49600.0；课程线 4641.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>689126.99</v>
+        <v>686240.99</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>63.8</v>
+        <v>63.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 439718.0；菌群线 116000.0；医疗线 54000.99；营地 50500.0；课程线 26928.0；工作坊 1980.0</t>
+          <t>咨询线 436718.0；菌群线 116000.0；医疗线 54000.99；营地 50500.0；课程线 27042.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>305144.95</v>
+        <v>316751.95</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -865,11 +865,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>77.90000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 237560.0；菌群线 24800.0；课程线 22277.0；医疗线 20507.95</t>
+          <t>咨询线 248958.0；菌群线 24800.0；课程线 22286.0；医疗线 20707.95</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>634894.72</v>
+        <v>654948.72</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>50.6</v>
+        <v>52.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 321324.02；课程线 95507.0；菌群线 92200.0；医疗线 44235.7；考证 39588.0；营地 36100.0；工作坊 5940.0</t>
+          <t>咨询线 341340.02；课程线 95545.0；菌群线 92200.0；医疗线 44235.7；考证 39588.0；营地 36100.0；工作坊 5940.0</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>565894.16</v>
+        <v>575311.16</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>71.8</v>
+        <v>72.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 406454.0；医疗线 82815.16；考证 40587.0；菌群线 22800.0；课程线 13238.0</t>
+          <t>咨询线 415652.0；医疗线 83015.16；考证 40587.0；菌群线 22800.0；课程线 13257.0</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>357440</v>
+        <v>367838.99</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -934,11 +934,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>95.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 341148.0；课程线 15293.0；考证 999.0；菌群线 0.0</t>
+          <t>咨询线 351546.0；课程线 15293.0；考证 999.0；医疗线 0.99；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>427822.35</v>
+        <v>439235.35</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -957,11 +957,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>87.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 374922.0；医疗线 32013.35；课程线 20887.0；菌群线 0.0</t>
+          <t>咨询线 386316.0；医疗线 32013.35；课程线 20906.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>373985.09</v>
+        <v>380585.09</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>90.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 339060.0；菌群线 22800.0；医疗线 10890.09；考证 999.0；课程线 236.0</t>
+          <t>咨询线 339060.0；菌群线 22800.0；医疗线 10890.09；课程线 6836.0；考证 999.0</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>370825.6</v>
+        <v>425019.6</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1003,11 +1003,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>82.40000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 305516.0；医疗线 56654.6；课程线 8655.0；菌群线 0.0</t>
+          <t>咨询线 334910.0；医疗线 56654.6；菌群线 24800.0；课程线 8655.0</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>195418</v>
+        <v>196214</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1026,11 +1026,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70.2</v>
+        <v>70.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 137168.0；营地 33600.0；课程线 16230.0；工作坊 7920.0；医疗线 500.0；菌群线 0.0</t>
+          <t>咨询线 137964.0；营地 33600.0；课程线 16230.0；工作坊 7920.0；医疗线 500.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>321278.97</v>
+        <v>322297.97</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1049,11 +1049,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 152558.0；考证 123752.0；菌群线 24800.0；课程线 19866.0；医疗线 302.97</t>
+          <t>咨询线 153558.0；考证 123752.0；菌群线 24800.0；课程线 19885.0；医疗线 302.97</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>73170</v>
+        <v>77150</v>
       </c>
     </row>
     <row r="7">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>210582</v>
+        <v>210980</v>
       </c>
     </row>
     <row r="8">
@@ -1212,11 +1212,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>邓璐</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>159180</v>
+        <v>168188</v>
       </c>
     </row>
     <row r="9">
@@ -1230,11 +1230,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>邓璐</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>148968</v>
+        <v>167180</v>
       </c>
     </row>
     <row r="10">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>147786</v>
+        <v>148184</v>
       </c>
     </row>
     <row r="11">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>420301.74</v>
+        <v>588962.5699999999</v>
       </c>
     </row>
     <row r="13">
@@ -1302,11 +1302,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>414662</v>
+        <v>439922.74</v>
       </c>
     </row>
     <row r="14">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>247083</v>
+        <v>249881</v>
       </c>
     </row>
     <row r="15">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>222251.57</v>
+        <v>245709.74</v>
       </c>
     </row>
     <row r="16">
@@ -1356,11 +1356,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>李浩然</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>219359.74</v>
+        <v>238171</v>
       </c>
     </row>
     <row r="17">
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2052421.07</v>
+        <v>2123775.07</v>
       </c>
       <c r="C2" t="n">
-        <v>325206.91</v>
+        <v>339464.91</v>
       </c>
       <c r="D2" t="n">
-        <v>40918.01</v>
+        <v>48254.01</v>
       </c>
       <c r="E2" t="n">
-        <v>1.99</v>
+        <v>2.27</v>
       </c>
       <c r="F2" t="n">
-        <v>284288.9</v>
+        <v>291210.9</v>
       </c>
       <c r="G2" t="n">
-        <v>13.85</v>
+        <v>13.71</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>青少年同行者计划 67228.0；青少年同行者计划护航营（6月） 64945.0；青少年同行者计划-护航营 43938.99</t>
+          <t>青少年同行者计划护航营（6月） 69925.0；青少年同行者计划 67228.0；青少年同行者计划-护航营 44933.99</t>
         </is>
       </c>
     </row>
@@ -1816,26 +1816,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3915139.82</v>
+        <v>4010753.82</v>
       </c>
       <c r="C3" t="n">
-        <v>623994.28</v>
+        <v>633994.28</v>
       </c>
       <c r="D3" t="n">
         <v>35498</v>
       </c>
       <c r="E3" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="F3" t="n">
-        <v>588496.28</v>
+        <v>598496.28</v>
       </c>
       <c r="G3" t="n">
-        <v>15.03</v>
+        <v>14.92</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 232242.48；精神心理 183194.0；暑假礼遇咨询套餐 73600.0</t>
+          <t>儿童青少年 232242.48；精神心理 183194.0；暑假礼遇咨询套餐 83600.0</t>
         </is>
       </c>
     </row>
@@ -1846,26 +1846,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2579598.23</v>
+        <v>2841988.04</v>
       </c>
       <c r="C4" t="n">
-        <v>848421.5699999999</v>
+        <v>1057341.57</v>
       </c>
       <c r="D4" t="n">
         <v>2029</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>846392.5699999999</v>
+        <v>1055312.57</v>
       </c>
       <c r="G4" t="n">
-        <v>32.81</v>
+        <v>37.13</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>治疗I（个体1000） 315861.14；日间中心 Ⅱ 212000.0；日间中心 Ⅰ 126000.0</t>
+          <t>治疗I（个体1000） 346861.14；日间中心 Ⅱ 212000.0；多动精灵产品套餐 188691.43</t>
         </is>
       </c>
     </row>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>673400</v>
+        <v>698200</v>
       </c>
       <c r="C5" t="n">
-        <v>335200</v>
+        <v>377800</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1888,14 +1888,14 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>335200</v>
+        <v>377800</v>
       </c>
       <c r="G5" t="n">
-        <v>49.78</v>
+        <v>54.11</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>肠道菌群移植 246000.0；肠道菌群移植（双疗程优惠）  45600.0；开业/店庆菌群移植优惠（深圳） 22800.0</t>
+          <t>肠道菌群移植 267800.0；肠道菌群移植（双疗程优惠）  45600.0；肠道菌群移植（双疗程优惠） 41600.0</t>
         </is>
       </c>
     </row>
@@ -1909,13 +1909,13 @@
         <v>655209.8100000001</v>
       </c>
       <c r="C6" t="n">
-        <v>173061.07</v>
+        <v>173861.07</v>
       </c>
       <c r="D6" t="n">
-        <v>2017.9</v>
+        <v>2817.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
       <c r="F6" t="n">
         <v>171043.17</v>
@@ -1939,13 +1939,13 @@
         <v>342234</v>
       </c>
       <c r="C7" t="n">
-        <v>467680</v>
+        <v>497480</v>
       </c>
       <c r="D7" t="n">
-        <v>20000</v>
+        <v>49800</v>
       </c>
       <c r="E7" t="n">
-        <v>5.84</v>
+        <v>14.55</v>
       </c>
       <c r="F7" t="n">
         <v>447680</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>蛋壳跳动身心复能营21天（一阶） 209000.0；青少年成长基地3月营（金盏基地） 188000.0；青少年基地3个月慈善价 49920.0</t>
+          <t>蛋壳跳动身心复能营21天（一阶） 238800.0；青少年成长基地3月营（金盏基地） 188000.0；青少年基地3个月慈善价 49920.0</t>
         </is>
       </c>
     </row>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2841988.04</v>
+        <v>3004333.19</v>
       </c>
       <c r="D8" t="n">
-        <v>2087</v>
+        <v>2443</v>
       </c>
       <c r="E8" t="n">
         <v>38424.25</v>
       </c>
       <c r="F8" t="n">
-        <v>2803563.79</v>
+        <v>2965908.94</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1670814.89</v>
+        <v>1735309.1</v>
       </c>
       <c r="D9" t="n">
-        <v>1130</v>
+        <v>1289</v>
       </c>
       <c r="E9" t="n">
         <v>13802.18</v>
       </c>
       <c r="F9" t="n">
-        <v>1657012.71</v>
+        <v>1721506.92</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1169173.15</v>
+        <v>1265524.09</v>
       </c>
       <c r="D10" t="n">
-        <v>956</v>
+        <v>1152</v>
       </c>
       <c r="E10" t="n">
         <v>24622.07</v>
       </c>
       <c r="F10" t="n">
-        <v>1144551.08</v>
+        <v>1240902.02</v>
       </c>
     </row>
     <row r="11">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>575311.16</v>
+        <v>578559.98</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>72.2</v>
+        <v>71.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 415652.0；医疗线 83015.16；考证 40587.0；菌群线 22800.0；课程线 13257.0</t>
+          <t>咨询线 415652.0；医疗线 86263.98；考证 40587.0；菌群线 22800.0；课程线 13257.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>380585.09</v>
+        <v>381026.53</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>89.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 339060.0；菌群线 22800.0；医疗线 10890.09；课程线 6836.0；考证 999.0</t>
+          <t>咨询线 339060.0；菌群线 22800.0；医疗线 11331.53；课程线 6836.0；考证 999.0</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>425019.6</v>
+        <v>427649.7</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1003,11 +1003,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>78.8</v>
+        <v>78.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 334910.0；医疗线 56654.6；菌群线 24800.0；课程线 8655.0</t>
+          <t>咨询线 334910.0；医疗线 59284.7；菌群线 24800.0；课程线 8655.0</t>
         </is>
       </c>
     </row>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2841988.04</v>
+        <v>3004333.19</v>
       </c>
       <c r="C4" t="n">
-        <v>1057341.57</v>
+        <v>1085301.23</v>
       </c>
       <c r="D4" t="n">
         <v>2029</v>
@@ -1858,10 +1858,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1055312.57</v>
+        <v>1083272.23</v>
       </c>
       <c r="G4" t="n">
-        <v>37.13</v>
+        <v>36.06</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>655209.8100000001</v>
       </c>
       <c r="C6" t="n">
-        <v>173861.07</v>
+        <v>190361.07</v>
       </c>
       <c r="D6" t="n">
         <v>2817.9</v>
@@ -1918,14 +1918,14 @@
         <v>0.43</v>
       </c>
       <c r="F6" t="n">
-        <v>171043.17</v>
+        <v>187543.17</v>
       </c>
       <c r="G6" t="n">
-        <v>26.11</v>
+        <v>28.62</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 119004.0；心灯计划-实战派心理咨询师执业培训项目（初+中阶-尾款） 38788.0；心理咨询基本功实战营 4880.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 119004.0；心灯计划-实战派心理咨询师执业培训项目（初+中阶-尾款） 38788.0；心理咨询 - 资深咨询 - 10次 16500.0</t>
         </is>
       </c>
     </row>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2123775.07</v>
+        <v>2151970.07</v>
       </c>
       <c r="D2" t="n">
-        <v>6925</v>
+        <v>7206</v>
       </c>
       <c r="E2" t="n">
-        <v>1861619.07</v>
+        <v>1889472.07</v>
       </c>
       <c r="F2" t="n">
-        <v>262156</v>
+        <v>262498</v>
       </c>
     </row>
     <row r="3">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1927088</v>
+        <v>1949763</v>
       </c>
       <c r="D3" t="n">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="E3" t="n">
-        <v>1670697</v>
+        <v>1693372</v>
       </c>
       <c r="F3" t="n">
         <v>256391</v>
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>196687.07</v>
+        <v>202207.07</v>
       </c>
       <c r="D4" t="n">
-        <v>6447</v>
+        <v>6717</v>
       </c>
       <c r="E4" t="n">
-        <v>190922.07</v>
+        <v>196100.07</v>
       </c>
       <c r="F4" t="n">
-        <v>5765</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4010753.82</v>
+        <v>4357617.82</v>
       </c>
       <c r="D5" t="n">
-        <v>817</v>
+        <v>868</v>
       </c>
       <c r="E5" t="n">
-        <v>811945.8</v>
+        <v>824343.8</v>
       </c>
       <c r="F5" t="n">
-        <v>3198808.02</v>
+        <v>3533274.02</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2871643.02</v>
+        <v>3146531.02</v>
       </c>
       <c r="D6" t="n">
-        <v>535</v>
+        <v>569</v>
       </c>
       <c r="E6" t="n">
         <v>116440</v>
       </c>
       <c r="F6" t="n">
-        <v>2755203.02</v>
+        <v>3030091.02</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1119110.8</v>
+        <v>1191086.8</v>
       </c>
       <c r="D7" t="n">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="E7" t="n">
-        <v>695505.8</v>
+        <v>707903.8</v>
       </c>
       <c r="F7" t="n">
-        <v>423605</v>
+        <v>483183</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3004333.19</v>
+        <v>3269813.05</v>
       </c>
       <c r="D8" t="n">
-        <v>2443</v>
+        <v>2657</v>
       </c>
       <c r="E8" t="n">
-        <v>38424.25</v>
+        <v>38869.57</v>
       </c>
       <c r="F8" t="n">
-        <v>2965908.94</v>
+        <v>3230943.48</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1735309.1</v>
+        <v>1876944.93</v>
       </c>
       <c r="D9" t="n">
-        <v>1289</v>
+        <v>1374</v>
       </c>
       <c r="E9" t="n">
         <v>13802.18</v>
       </c>
       <c r="F9" t="n">
-        <v>1721506.92</v>
+        <v>1863142.75</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1265524.09</v>
+        <v>1389368.12</v>
       </c>
       <c r="D10" t="n">
-        <v>1152</v>
+        <v>1281</v>
       </c>
       <c r="E10" t="n">
-        <v>24622.07</v>
+        <v>25067.39</v>
       </c>
       <c r="F10" t="n">
-        <v>1240902.02</v>
+        <v>1364300.73</v>
       </c>
     </row>
     <row r="11">
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>698200</v>
+        <v>723000</v>
       </c>
       <c r="D11" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>320400</v>
+        <v>345200</v>
       </c>
       <c r="F11" t="n">
         <v>377800</v>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2609948.99</v>
+        <v>2811608.99</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>95.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 2500941.99；咨询线 52786.0；菌群线 49600.0；课程线 4641.0；工作坊 1980.0</t>
+          <t>医疗线 2701805.99；咨询线 53582.0；菌群线 49600.0；课程线 4641.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>686240.99</v>
+        <v>698733.99</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>63.6</v>
+        <v>64.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 436718.0；菌群线 116000.0；医疗线 54000.99；营地 50500.0；课程线 27042.0；工作坊 1980.0</t>
+          <t>咨询线 449116.0；菌群线 116000.0；医疗线 54000.99；营地 50500.0；课程线 27137.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>316751.95</v>
+        <v>335174.06</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -865,11 +865,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>78.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 248958.0；菌群线 24800.0；课程线 22286.0；医疗线 20707.95</t>
+          <t>咨询线 267356.0；菌群线 24800.0；课程线 22286.0；医疗线 20732.06</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>654948.72</v>
+        <v>716151.72</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52.1</v>
+        <v>56.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 341340.02；课程线 95545.0；菌群线 92200.0；医疗线 44235.7；考证 39588.0；营地 36100.0；工作坊 5940.0</t>
+          <t>咨询线 402534.02；课程线 95554.0；菌群线 92200.0；医疗线 44235.7；考证 39588.0；营地 36100.0；工作坊 5940.0</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>578559.98</v>
+        <v>663795.58</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>71.8</v>
+        <v>75.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 415652.0；医疗线 86263.98；考证 40587.0；菌群线 22800.0；课程线 13257.0</t>
+          <t>咨询线 499948.0；医疗线 87003.58；考证 40587.0；菌群线 22800.0；课程线 13457.0</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>367838.99</v>
+        <v>379032.99</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -934,11 +934,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>95.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 351546.0；课程线 15293.0；考证 999.0；医疗线 0.99；菌群线 0.0</t>
+          <t>咨询线 362740.0；课程线 15293.0；考证 999.0；医疗线 0.99；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>439235.35</v>
+        <v>490235.35</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -957,11 +957,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>88</v>
+        <v>89.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 386316.0；医疗线 32013.35；课程线 20906.0；菌群线 0.0</t>
+          <t>咨询线 437316.0；医疗线 32013.35；课程线 20906.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>381026.53</v>
+        <v>383421.55</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>89</v>
+        <v>88.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 339060.0；菌群线 22800.0；医疗线 11331.53；课程线 6836.0；考证 999.0</t>
+          <t>咨询线 340260.0；菌群线 22800.0；医疗线 12488.55；课程线 6874.0；考证 999.0</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>427649.7</v>
+        <v>509092.2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1003,11 +1003,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>78.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 334910.0；医疗线 59284.7；菌群线 24800.0；课程线 8655.0</t>
+          <t>咨询线 415308.0；医疗线 60329.2；菌群线 24800.0；课程线 8655.0</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>196214</v>
+        <v>208612</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1026,11 +1026,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 137964.0；营地 33600.0；课程线 16230.0；工作坊 7920.0；医疗线 500.0；菌群线 0.0</t>
+          <t>咨询线 150362.0；营地 33600.0；课程线 16230.0；工作坊 7920.0；医疗线 500.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>322297.97</v>
+        <v>323491.97</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1049,11 +1049,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>47.6</v>
+        <v>47.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 153558.0；考证 123752.0；菌群线 24800.0；课程线 19885.0；医疗线 302.97</t>
+          <t>咨询线 154752.0；考证 123752.0；菌群线 24800.0；课程线 19885.0；医疗线 302.97</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>103340</v>
+        <v>107320</v>
       </c>
     </row>
     <row r="3">
@@ -1122,11 +1122,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>张孟蝶</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>81540</v>
+        <v>83580</v>
       </c>
     </row>
     <row r="4">
@@ -1140,11 +1140,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>王渊亮</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>80920</v>
+        <v>81540</v>
       </c>
     </row>
     <row r="5">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>王渊亮</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>79600</v>
+        <v>80920</v>
       </c>
     </row>
     <row r="6">
@@ -1194,11 +1194,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>邓璐</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>210980</v>
+        <v>239180</v>
       </c>
     </row>
     <row r="8">
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>168188</v>
+        <v>228984</v>
       </c>
     </row>
     <row r="9">
@@ -1230,11 +1230,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>邓璐</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>167180</v>
+        <v>221378</v>
       </c>
     </row>
     <row r="10">
@@ -1266,11 +1266,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>郑巨光</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>133964</v>
+        <v>142394</v>
       </c>
     </row>
     <row r="12">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>588962.5699999999</v>
+        <v>600058.5699999999</v>
       </c>
     </row>
     <row r="13">
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>439922.74</v>
+        <v>445409.74</v>
       </c>
     </row>
     <row r="14">
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>李浩然</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>249881</v>
+        <v>307200</v>
       </c>
     </row>
     <row r="15">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>245709.74</v>
+        <v>289404.57</v>
       </c>
     </row>
     <row r="16">
@@ -1356,11 +1356,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>李浩然</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>238171</v>
+        <v>275746.74</v>
       </c>
     </row>
     <row r="17">
@@ -1786,22 +1786,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2123775.07</v>
+        <v>2151970.07</v>
       </c>
       <c r="C2" t="n">
-        <v>339464.91</v>
+        <v>340613.91</v>
       </c>
       <c r="D2" t="n">
-        <v>48254.01</v>
+        <v>49394.01</v>
       </c>
       <c r="E2" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="F2" t="n">
-        <v>291210.9</v>
+        <v>291219.9</v>
       </c>
       <c r="G2" t="n">
-        <v>13.71</v>
+        <v>13.53</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4010753.82</v>
+        <v>4357617.82</v>
       </c>
       <c r="C3" t="n">
         <v>633994.28</v>
@@ -1825,13 +1825,13 @@
         <v>35498</v>
       </c>
       <c r="E3" t="n">
-        <v>0.89</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>598496.28</v>
       </c>
       <c r="G3" t="n">
-        <v>14.92</v>
+        <v>13.73</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1846,26 +1846,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3004333.19</v>
+        <v>3269813.05</v>
       </c>
       <c r="C4" t="n">
-        <v>1085301.23</v>
+        <v>1185598.23</v>
       </c>
       <c r="D4" t="n">
         <v>2029</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="F4" t="n">
-        <v>1083272.23</v>
+        <v>1183569.23</v>
       </c>
       <c r="G4" t="n">
-        <v>36.06</v>
+        <v>36.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>治疗I（个体1000） 346861.14；日间中心 Ⅱ 212000.0；多动精灵产品套餐 188691.43</t>
+          <t>治疗I（个体1000） 446863.14；日间中心 Ⅱ 212000.0；多动精灵产品套餐 188691.43</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>698200</v>
+        <v>723000</v>
       </c>
       <c r="C5" t="n">
         <v>377800</v>
@@ -1891,7 +1891,7 @@
         <v>377800</v>
       </c>
       <c r="G5" t="n">
-        <v>54.11</v>
+        <v>52.25</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2151970.07</v>
+        <v>2219355.07</v>
       </c>
       <c r="D2" t="n">
-        <v>7206</v>
+        <v>7507</v>
       </c>
       <c r="E2" t="n">
-        <v>1889472.07</v>
+        <v>1941489.07</v>
       </c>
       <c r="F2" t="n">
-        <v>262498</v>
+        <v>277866</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1949763</v>
+        <v>2006294</v>
       </c>
       <c r="D3" t="n">
-        <v>489</v>
+        <v>512</v>
       </c>
       <c r="E3" t="n">
-        <v>1693372</v>
+        <v>1734985</v>
       </c>
       <c r="F3" t="n">
-        <v>256391</v>
+        <v>271309</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>202207.07</v>
+        <v>213061.07</v>
       </c>
       <c r="D4" t="n">
-        <v>6717</v>
+        <v>6995</v>
       </c>
       <c r="E4" t="n">
-        <v>196100.07</v>
+        <v>206504.07</v>
       </c>
       <c r="F4" t="n">
-        <v>6107</v>
+        <v>6557</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4357617.82</v>
+        <v>4597291.82</v>
       </c>
       <c r="D5" t="n">
-        <v>868</v>
+        <v>911</v>
       </c>
       <c r="E5" t="n">
         <v>824343.8</v>
       </c>
       <c r="F5" t="n">
-        <v>3533274.02</v>
+        <v>3772948.02</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3146531.02</v>
+        <v>3347011.02</v>
       </c>
       <c r="D6" t="n">
-        <v>569</v>
+        <v>606</v>
       </c>
       <c r="E6" t="n">
         <v>116440</v>
       </c>
       <c r="F6" t="n">
-        <v>3030091.02</v>
+        <v>3230571.02</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1191086.8</v>
+        <v>1230280.8</v>
       </c>
       <c r="D7" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E7" t="n">
         <v>707903.8</v>
       </c>
       <c r="F7" t="n">
-        <v>483183</v>
+        <v>522377</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3269813.05</v>
+        <v>3550221.13</v>
       </c>
       <c r="D8" t="n">
-        <v>2657</v>
+        <v>2809</v>
       </c>
       <c r="E8" t="n">
-        <v>38869.57</v>
+        <v>39399.56</v>
       </c>
       <c r="F8" t="n">
-        <v>3230943.48</v>
+        <v>3510821.57</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1876944.93</v>
+        <v>2103137.8</v>
       </c>
       <c r="D9" t="n">
-        <v>1374</v>
+        <v>1468</v>
       </c>
       <c r="E9" t="n">
-        <v>13802.18</v>
+        <v>14302.18</v>
       </c>
       <c r="F9" t="n">
-        <v>1863142.75</v>
+        <v>2088835.62</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1389368.12</v>
+        <v>1443583.33</v>
       </c>
       <c r="D10" t="n">
-        <v>1281</v>
+        <v>1339</v>
       </c>
       <c r="E10" t="n">
-        <v>25067.39</v>
+        <v>25097.38</v>
       </c>
       <c r="F10" t="n">
-        <v>1364300.73</v>
+        <v>1418485.95</v>
       </c>
     </row>
     <row r="11">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>71280</v>
+        <v>75240</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14" t="n">
         <v>53460</v>
       </c>
       <c r="F14" t="n">
-        <v>17820</v>
+        <v>21780</v>
       </c>
     </row>
   </sheetData>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2811608.99</v>
+        <v>3057450.56</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>96.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 2701805.99；咨询线 53582.0；菌群线 49600.0；课程线 4641.0；工作坊 1980.0</t>
+          <t>医疗线 2947647.56；咨询线 53582.0；菌群线 49600.0；课程线 4641.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>698733.99</v>
+        <v>717595.99</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>64.3</v>
+        <v>65.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 449116.0；菌群线 116000.0；医疗线 54000.99；营地 50500.0；课程线 27137.0；工作坊 1980.0</t>
+          <t>咨询线 467912.0；菌群线 116000.0；医疗线 54000.99；营地 50500.0；课程线 27203.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>335174.06</v>
+        <v>342570.06</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -865,11 +865,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>79.8</v>
+        <v>78.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 267356.0；菌群线 24800.0；课程线 22286.0；医疗线 20732.06</t>
+          <t>咨询线 268152.0；课程线 28886.0；菌群线 24800.0；医疗线 20732.06</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>716151.72</v>
+        <v>744770.72</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>56.2</v>
+        <v>57</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 402534.02；课程线 95554.0；菌群线 92200.0；医疗线 44235.7；考证 39588.0；营地 36100.0；工作坊 5940.0</t>
+          <t>咨询线 424534.02；课程线 102173.0；菌群线 92200.0；医疗线 44235.7；考证 39588.0；营地 36100.0；工作坊 5940.0</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>663795.58</v>
+        <v>693613.48</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>75.3</v>
+        <v>75.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 499948.0；医疗线 87003.58；考证 40587.0；菌群线 22800.0；课程线 13457.0</t>
+          <t>咨询线 525448.0；医疗线 89584.48；考证 40587.0；菌群线 22800.0；课程线 15194.0</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>379032.99</v>
+        <v>380226.99</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 362740.0；课程线 15293.0；考证 999.0；医疗线 0.99；菌群线 0.0</t>
+          <t>咨询线 363934.0；课程线 15293.0；考证 999.0；医疗线 0.99；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>490235.35</v>
+        <v>563201.4300000001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -957,11 +957,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>89.2</v>
+        <v>90.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 437316.0；医疗线 32013.35；课程线 20906.0；菌群线 0.0</t>
+          <t>咨询线 509714.0；医疗线 32263.43；课程线 21224.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>383421.55</v>
+        <v>410851.64</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>88.7</v>
+        <v>89.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 340260.0；菌群线 22800.0；医疗线 12488.55；课程线 6874.0；考证 999.0</t>
+          <t>咨询线 367060.0；菌群线 22800.0；医疗线 13118.64；课程线 6874.0；考证 999.0</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>509092.2</v>
+        <v>583358.6</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1003,11 +1003,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>81.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 415308.0；医疗线 60329.2；菌群线 24800.0；课程线 8655.0</t>
+          <t>咨询线 487100.0；医疗线 62784.6；菌群线 24800.0；课程线 8674.0</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>208612</v>
+        <v>212572</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1026,11 +1026,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>72.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 150362.0；营地 33600.0；课程线 16230.0；工作坊 7920.0；医疗线 500.0；菌群线 0.0</t>
+          <t>咨询线 150362.0；营地 33600.0；课程线 16230.0；工作坊 11880.0；医疗线 500.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>323491.97</v>
+        <v>323898.97</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1049,11 +1049,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 154752.0；考证 123752.0；菌群线 24800.0；课程线 19885.0；医疗线 302.97</t>
+          <t>咨询线 155150.0；考证 123752.0；菌群线 24800.0；课程线 19894.0；医疗线 302.97</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>83580</v>
+        <v>91540</v>
       </c>
     </row>
     <row r="4">
@@ -1140,11 +1140,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>张孟蝶</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>81540</v>
+        <v>85110</v>
       </c>
     </row>
     <row r="5">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>王渊亮</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>80920</v>
+        <v>81540</v>
       </c>
     </row>
     <row r="6">
@@ -1176,11 +1176,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>王渊亮</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>77150</v>
+        <v>80920</v>
       </c>
     </row>
     <row r="7">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>239180</v>
+        <v>267578</v>
       </c>
     </row>
     <row r="8">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>陈静</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>148184</v>
+        <v>191182</v>
       </c>
     </row>
     <row r="11">
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>142394</v>
+        <v>150394</v>
       </c>
     </row>
     <row r="12">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>600058.5699999999</v>
+        <v>629803.5699999999</v>
       </c>
     </row>
     <row r="13">
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>445409.74</v>
+        <v>488426.74</v>
       </c>
     </row>
     <row r="14">
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>李浩然</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>307200</v>
+        <v>338486.14</v>
       </c>
     </row>
     <row r="15">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>289404.57</v>
+        <v>334273</v>
       </c>
     </row>
     <row r="16">
@@ -1356,11 +1356,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>李浩然</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>275746.74</v>
+        <v>317200</v>
       </c>
     </row>
     <row r="17">
@@ -1680,11 +1680,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>田婉丽</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3960</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="35">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>张孟蝶</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1786,22 +1786,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2151970.07</v>
+        <v>2219355.07</v>
       </c>
       <c r="C2" t="n">
-        <v>340613.91</v>
+        <v>342247.91</v>
       </c>
       <c r="D2" t="n">
-        <v>49394.01</v>
+        <v>50990.01</v>
       </c>
       <c r="E2" t="n">
         <v>2.3</v>
       </c>
       <c r="F2" t="n">
-        <v>291219.9</v>
+        <v>291257.9</v>
       </c>
       <c r="G2" t="n">
-        <v>13.53</v>
+        <v>13.12</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4357617.82</v>
+        <v>4597291.82</v>
       </c>
       <c r="C3" t="n">
         <v>633994.28</v>
@@ -1825,13 +1825,13 @@
         <v>35498</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="F3" t="n">
         <v>598496.28</v>
       </c>
       <c r="G3" t="n">
-        <v>13.73</v>
+        <v>13.02</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3269813.05</v>
+        <v>3550221.13</v>
       </c>
       <c r="C4" t="n">
-        <v>1185598.23</v>
+        <v>1253730.54</v>
       </c>
       <c r="D4" t="n">
         <v>2029</v>
@@ -1858,14 +1858,14 @@
         <v>0.06</v>
       </c>
       <c r="F4" t="n">
-        <v>1183569.23</v>
+        <v>1251701.54</v>
       </c>
       <c r="G4" t="n">
-        <v>36.2</v>
+        <v>35.26</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>治疗I（个体1000） 446863.14；日间中心 Ⅱ 212000.0；多动精灵产品套餐 188691.43</t>
+          <t>治疗I（个体1000） 466863.14；日间中心 Ⅱ 212000.0；多动精灵产品套餐 194671.43</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>71280</v>
+        <v>75240</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2219355.07</v>
+        <v>2407996.07</v>
       </c>
       <c r="D2" t="n">
-        <v>7507</v>
+        <v>7879</v>
       </c>
       <c r="E2" t="n">
-        <v>1941489.07</v>
+        <v>2124393.07</v>
       </c>
       <c r="F2" t="n">
-        <v>277866</v>
+        <v>283603</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2006294</v>
+        <v>2185131</v>
       </c>
       <c r="D3" t="n">
-        <v>512</v>
+        <v>555</v>
       </c>
       <c r="E3" t="n">
-        <v>1734985</v>
+        <v>1908902</v>
       </c>
       <c r="F3" t="n">
-        <v>271309</v>
+        <v>276229</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>213061.07</v>
+        <v>222865.07</v>
       </c>
       <c r="D4" t="n">
-        <v>6995</v>
+        <v>7324</v>
       </c>
       <c r="E4" t="n">
-        <v>206504.07</v>
+        <v>215491.07</v>
       </c>
       <c r="F4" t="n">
-        <v>6557</v>
+        <v>7374</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4597291.82</v>
+        <v>5246931.82</v>
       </c>
       <c r="D5" t="n">
-        <v>911</v>
+        <v>980</v>
       </c>
       <c r="E5" t="n">
-        <v>824343.8</v>
+        <v>1001783.8</v>
       </c>
       <c r="F5" t="n">
-        <v>3772948.02</v>
+        <v>4245148.02</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3347011.02</v>
+        <v>3687601.02</v>
       </c>
       <c r="D6" t="n">
-        <v>606</v>
+        <v>651</v>
       </c>
       <c r="E6" t="n">
         <v>116440</v>
       </c>
       <c r="F6" t="n">
-        <v>3230571.02</v>
+        <v>3571161.02</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1230280.8</v>
+        <v>1559330.8</v>
       </c>
       <c r="D7" t="n">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="E7" t="n">
-        <v>707903.8</v>
+        <v>885343.8</v>
       </c>
       <c r="F7" t="n">
-        <v>522377</v>
+        <v>673987</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3550221.13</v>
+        <v>3342840.2</v>
       </c>
       <c r="D8" t="n">
-        <v>2809</v>
+        <v>2048</v>
       </c>
       <c r="E8" t="n">
-        <v>39399.56</v>
+        <v>41843.55</v>
       </c>
       <c r="F8" t="n">
-        <v>3510821.57</v>
+        <v>3300996.65</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2103137.8</v>
+        <v>2073024.51</v>
       </c>
       <c r="D9" t="n">
-        <v>1468</v>
+        <v>1127</v>
       </c>
       <c r="E9" t="n">
-        <v>14302.18</v>
+        <v>15445.18</v>
       </c>
       <c r="F9" t="n">
-        <v>2088835.62</v>
+        <v>2057579.33</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1443583.33</v>
+        <v>1269815.69</v>
       </c>
       <c r="D10" t="n">
-        <v>1339</v>
+        <v>921</v>
       </c>
       <c r="E10" t="n">
-        <v>25097.38</v>
+        <v>26398.37</v>
       </c>
       <c r="F10" t="n">
-        <v>1418485.95</v>
+        <v>1243417.32</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>723000</v>
+        <v>1139722</v>
       </c>
       <c r="D11" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E11" t="n">
-        <v>345200</v>
+        <v>716322</v>
       </c>
       <c r="F11" t="n">
-        <v>377800</v>
+        <v>423400</v>
       </c>
     </row>
     <row r="12">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>655209.8100000001</v>
+        <v>659109.8100000001</v>
       </c>
       <c r="D12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E12" t="n">
-        <v>449284.81</v>
+        <v>453084.81</v>
       </c>
       <c r="F12" t="n">
-        <v>205925</v>
+        <v>206025</v>
       </c>
     </row>
     <row r="13">
@@ -751,13 +751,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>75240</v>
+        <v>77220</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" t="n">
-        <v>53460</v>
+        <v>55440</v>
       </c>
       <c r="F14" t="n">
         <v>21780</v>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3057450.56</v>
+        <v>3216882.06</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>96.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 2947647.56；咨询线 53582.0；菌群线 49600.0；课程线 4641.0；工作坊 1980.0</t>
+          <t>医疗线 3107079.06；咨询线 53582.0；菌群线 49600.0；课程线 4641.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>717595.99</v>
+        <v>737671.99</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>65.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 467912.0；菌群线 116000.0；医疗线 54000.99；营地 50500.0；课程线 27203.0；工作坊 1980.0</t>
+          <t>咨询线 487912.0；菌群线 116000.0；医疗线 54000.99；营地 50500.0；课程线 27279.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>342570.06</v>
+        <v>446849.62</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -865,11 +865,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>78.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 268152.0；课程线 28886.0；菌群线 24800.0；医疗线 20732.06</t>
+          <t>咨询线 371550.0；课程线 29204.0；菌群线 24800.0；医疗线 21295.62</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>744770.72</v>
+        <v>846184.72</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>62.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 424534.02；课程线 102173.0；菌群线 92200.0；医疗线 44235.7；考证 39588.0；营地 36100.0；工作坊 5940.0</t>
+          <t>咨询线 527148.02；课程线 102173.0；菌群线 92200.0；医疗线 43035.7；考证 39588.0；营地 36100.0；工作坊 5940.0</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>693613.48</v>
+        <v>678649.11</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>75.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 525448.0；医疗线 89584.48；考证 40587.0；菌群线 22800.0；课程线 15194.0</t>
+          <t>咨询线 533448.0；医疗线 66601.11；考证 40587.0；菌群线 22800.0；课程线 15213.0</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>380226.99</v>
+        <v>382022.99</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 363934.0；课程线 15293.0；考证 999.0；医疗线 0.99；菌群线 0.0</t>
+          <t>咨询线 365730.0；课程线 15293.0；考证 999.0；医疗线 0.99；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>563201.4300000001</v>
+        <v>538837.21</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -957,11 +957,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>90.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 509714.0；医疗线 32263.43；课程线 21224.0；菌群线 0.0</t>
+          <t>咨询线 509714.0；课程线 21243.0；医疗线 7880.21；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>410851.64</v>
+        <v>406931</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>89.3</v>
+        <v>92.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 367060.0；菌群线 22800.0；医疗线 13118.64；课程线 6874.0；考证 999.0</t>
+          <t>咨询线 376258.0；菌群线 22800.0；课程线 6874.0；考证 999.0</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>583358.6</v>
+        <v>716591</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1003,11 +1003,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>83.5</v>
+        <v>89</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 487100.0；医疗线 62784.6；菌群线 24800.0；课程线 8674.0</t>
+          <t>咨询线 637498.0；菌群线 70400.0；课程线 8693.0</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>212572</v>
+        <v>253829</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1026,11 +1026,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 150362.0；营地 33600.0；课程线 16230.0；工作坊 11880.0；医疗线 500.0；菌群线 0.0</t>
+          <t>咨询线 186362.0；营地 33600.0；课程线 21487.0；工作坊 11880.0；医疗线 500.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>323898.97</v>
+        <v>364723.97</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1049,11 +1049,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>47.9</v>
+        <v>53.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 155150.0；考证 123752.0；菌群线 24800.0；课程线 19894.0；医疗线 302.97</t>
+          <t>咨询线 195946.0；考证 123752.0；菌群线 24800.0；课程线 19923.0；医疗线 302.97</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>107320</v>
+        <v>128220</v>
       </c>
     </row>
     <row r="3">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>91540</v>
+        <v>95520</v>
       </c>
     </row>
     <row r="4">
@@ -1140,11 +1140,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>王渊亮</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>85110</v>
+        <v>93860</v>
       </c>
     </row>
     <row r="5">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>张孟蝶</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>81540</v>
+        <v>93070</v>
       </c>
     </row>
     <row r="6">
@@ -1176,11 +1176,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>王渊亮</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>80920</v>
+        <v>81600</v>
       </c>
     </row>
     <row r="7">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>267578</v>
+        <v>339578</v>
       </c>
     </row>
     <row r="8">
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>228984</v>
+        <v>287804</v>
       </c>
     </row>
     <row r="9">
@@ -1266,11 +1266,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>郑巨光</t>
+          <t>周思若</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>150394</v>
+        <v>172354</v>
       </c>
     </row>
     <row r="12">
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>488426.74</v>
+        <v>519440.74</v>
       </c>
     </row>
     <row r="14">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>338486.14</v>
+        <v>408074.64</v>
       </c>
     </row>
     <row r="15">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>317200</v>
+        <v>322598</v>
       </c>
     </row>
     <row r="17">
@@ -1374,11 +1374,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>74400</v>
+        <v>169600</v>
       </c>
     </row>
     <row r="18">
@@ -1392,11 +1392,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>70400</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="19">
@@ -1410,11 +1410,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>49600</v>
+        <v>70400</v>
       </c>
     </row>
     <row r="20">
@@ -1428,11 +1428,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>龙少海</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>46600</v>
+        <v>70400</v>
       </c>
     </row>
     <row r="21">
@@ -1446,11 +1446,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>许冰</t>
+          <t>于鹏飞</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45600</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="22">
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>233588.01</v>
+        <v>237388.01</v>
       </c>
     </row>
     <row r="23">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>赵越</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>李明</t>
+          <t>赵越</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>25740</v>
+        <v>27720</v>
       </c>
     </row>
     <row r="33">
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2219355.07</v>
+        <v>2407996.07</v>
       </c>
       <c r="C2" t="n">
-        <v>342247.91</v>
+        <v>357349.91</v>
       </c>
       <c r="D2" t="n">
-        <v>50990.01</v>
+        <v>52625.01</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="F2" t="n">
-        <v>291257.9</v>
+        <v>304724.9</v>
       </c>
       <c r="G2" t="n">
-        <v>13.12</v>
+        <v>12.65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>青少年同行者计划护航营（6月） 69925.0；青少年同行者计划 67228.0；青少年同行者计划-护航营 44933.99</t>
+          <t>青少年同行者计划 75527.0；青少年同行者计划护航营（6月） 69925.0；青少年同行者计划-护航营 46527.99</t>
         </is>
       </c>
     </row>
@@ -1816,26 +1816,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4597291.82</v>
+        <v>5246931.82</v>
       </c>
       <c r="C3" t="n">
-        <v>633994.28</v>
+        <v>709042.28</v>
       </c>
       <c r="D3" t="n">
-        <v>35498</v>
+        <v>39796</v>
       </c>
       <c r="E3" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="F3" t="n">
-        <v>598496.28</v>
+        <v>669246.28</v>
       </c>
       <c r="G3" t="n">
-        <v>13.02</v>
+        <v>12.76</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 232242.48；精神心理 183194.0；暑假礼遇咨询套餐 83600.0</t>
+          <t>儿童青少年 265342.48；精神心理 210994.0；暑假礼遇咨询套餐 93600.0</t>
         </is>
       </c>
     </row>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3550221.13</v>
+        <v>3342840.2</v>
       </c>
       <c r="C4" t="n">
-        <v>1253730.54</v>
+        <v>1275939.07</v>
       </c>
       <c r="D4" t="n">
         <v>2029</v>
@@ -1858,14 +1858,14 @@
         <v>0.06</v>
       </c>
       <c r="F4" t="n">
-        <v>1251701.54</v>
+        <v>1273910.07</v>
       </c>
       <c r="G4" t="n">
-        <v>35.26</v>
+        <v>38.11</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>治疗I（个体1000） 466863.14；日间中心 Ⅱ 212000.0；多动精灵产品套餐 194671.43</t>
+          <t>治疗I（个体1000） 497903.14；日间中心 Ⅱ 212000.0；多动精灵产品套餐 194671.43</t>
         </is>
       </c>
     </row>
@@ -1876,26 +1876,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>723000</v>
+        <v>1139722</v>
       </c>
       <c r="C5" t="n">
-        <v>377800</v>
+        <v>427400</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="F5" t="n">
-        <v>377800</v>
+        <v>402600</v>
       </c>
       <c r="G5" t="n">
-        <v>52.25</v>
+        <v>35.32</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>肠道菌群移植 267800.0；肠道菌群移植（双疗程优惠）  45600.0；肠道菌群移植（双疗程优惠） 41600.0</t>
+          <t>肠道菌群移植 292600.0；肠道菌群移植（双疗程优惠）  45600.0；肠道菌群移植（双疗程优惠） 41600.0</t>
         </is>
       </c>
     </row>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>655209.8100000001</v>
+        <v>659109.8100000001</v>
       </c>
       <c r="C6" t="n">
-        <v>190361.07</v>
+        <v>180430.27</v>
       </c>
       <c r="D6" t="n">
         <v>2817.9</v>
@@ -1918,14 +1918,14 @@
         <v>0.43</v>
       </c>
       <c r="F6" t="n">
-        <v>187543.17</v>
+        <v>177612.37</v>
       </c>
       <c r="G6" t="n">
-        <v>28.62</v>
+        <v>26.95</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 119004.0；心灯计划-实战派心理咨询师执业培训项目（初+中阶-尾款） 38788.0；心理咨询 - 资深咨询 - 10次 16500.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 119004.0；心灯计划-实战派心理咨询师执业培训项目（初+中阶-尾款） 38788.0；心理咨询基本功实战营 4880.0</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
         <v>342234</v>
       </c>
       <c r="C7" t="n">
-        <v>497480</v>
+        <v>529780</v>
       </c>
       <c r="D7" t="n">
         <v>49800</v>
@@ -1948,14 +1948,14 @@
         <v>14.55</v>
       </c>
       <c r="F7" t="n">
-        <v>447680</v>
+        <v>479980</v>
       </c>
       <c r="G7" t="n">
-        <v>130.81</v>
+        <v>140.25</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>蛋壳跳动身心复能营21天（一阶） 238800.0；青少年成长基地3月营（金盏基地） 188000.0；青少年基地3个月慈善价 49920.0</t>
+          <t>蛋壳跳动身心复能营21天（一阶） 268600.0；青少年成长基地3月营（金盏基地） 188000.0；青少年基地3个月慈善价 49920.0</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>75240</v>
+        <v>77220</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5246931.82</v>
+        <v>5266931.82</v>
       </c>
       <c r="D5" t="n">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E5" t="n">
         <v>1001783.8</v>
       </c>
       <c r="F5" t="n">
-        <v>4245148.02</v>
+        <v>4265148.02</v>
       </c>
     </row>
     <row r="6">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3342840.2</v>
+        <v>3715549.6</v>
       </c>
       <c r="D8" t="n">
-        <v>2048</v>
+        <v>2961</v>
       </c>
       <c r="E8" t="n">
         <v>41843.55</v>
       </c>
       <c r="F8" t="n">
-        <v>3300996.65</v>
+        <v>3673706.05</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2073024.51</v>
+        <v>2200361.19</v>
       </c>
       <c r="D9" t="n">
-        <v>1127</v>
+        <v>1536</v>
       </c>
       <c r="E9" t="n">
         <v>15445.18</v>
       </c>
       <c r="F9" t="n">
-        <v>2057579.33</v>
+        <v>2184916.01</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1269815.69</v>
+        <v>1511688.41</v>
       </c>
       <c r="D10" t="n">
-        <v>921</v>
+        <v>1423</v>
       </c>
       <c r="E10" t="n">
         <v>26398.37</v>
       </c>
       <c r="F10" t="n">
-        <v>1243417.32</v>
+        <v>1485290.04</v>
       </c>
     </row>
     <row r="11">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>446849.62</v>
+        <v>447986.06</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -865,11 +865,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>83.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 371550.0；课程线 29204.0；菌群线 24800.0；医疗线 21295.62</t>
+          <t>咨询线 371550.0；课程线 29204.0；菌群线 24800.0；医疗线 22432.06</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>846184.72</v>
+        <v>867684.72</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>62.3</v>
+        <v>63.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 527148.02；课程线 102173.0；菌群线 92200.0；医疗线 43035.7；考证 39588.0；营地 36100.0；工作坊 5940.0</t>
+          <t>咨询线 547148.02；课程线 102173.0；菌群线 92200.0；医疗线 44535.7；考证 39588.0；营地 36100.0；工作坊 5940.0</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>678649.11</v>
+        <v>701632.48</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>78.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 533448.0；医疗线 66601.11；考证 40587.0；菌群线 22800.0；课程线 15213.0</t>
+          <t>咨询线 533448.0；医疗线 89584.48；考证 40587.0；菌群线 22800.0；课程线 15213.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>538837.21</v>
+        <v>563220.4300000001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -957,11 +957,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>94.59999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 509714.0；课程线 21243.0；医疗线 7880.21；菌群线 0.0</t>
+          <t>咨询线 509714.0；医疗线 32263.43；课程线 21243.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>406931</v>
+        <v>420389.73</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>92.5</v>
+        <v>89.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 376258.0；菌群线 22800.0；课程线 6874.0；考证 999.0</t>
+          <t>咨询线 376258.0；菌群线 22800.0；医疗线 13458.73；课程线 6874.0；考证 999.0</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>716591</v>
+        <v>779679.1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1003,11 +1003,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>89</v>
+        <v>81.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 637498.0；菌群线 70400.0；课程线 8693.0</t>
+          <t>咨询线 637498.0；菌群线 70400.0；医疗线 63088.1；课程线 8693.0</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>287804</v>
+        <v>307804</v>
       </c>
     </row>
     <row r="9">
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5246931.82</v>
+        <v>5266931.82</v>
       </c>
       <c r="C3" t="n">
         <v>709042.28</v>
@@ -1831,7 +1831,7 @@
         <v>669246.28</v>
       </c>
       <c r="G3" t="n">
-        <v>12.76</v>
+        <v>12.71</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1846,22 +1846,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3342840.2</v>
+        <v>3715549.6</v>
       </c>
       <c r="C4" t="n">
-        <v>1275939.07</v>
+        <v>1305783.04</v>
       </c>
       <c r="D4" t="n">
         <v>2029</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F4" t="n">
-        <v>1273910.07</v>
+        <v>1303754.04</v>
       </c>
       <c r="G4" t="n">
-        <v>38.11</v>
+        <v>35.09</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>659109.8100000001</v>
       </c>
       <c r="C6" t="n">
-        <v>180430.27</v>
+        <v>196930.27</v>
       </c>
       <c r="D6" t="n">
         <v>2817.9</v>
@@ -1918,14 +1918,14 @@
         <v>0.43</v>
       </c>
       <c r="F6" t="n">
-        <v>177612.37</v>
+        <v>194112.37</v>
       </c>
       <c r="G6" t="n">
-        <v>26.95</v>
+        <v>29.45</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 119004.0；心灯计划-实战派心理咨询师执业培训项目（初+中阶-尾款） 38788.0；心理咨询基本功实战营 4880.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 119004.0；心灯计划-实战派心理咨询师执业培训项目（初+中阶-尾款） 38788.0；心理咨询 - 资深咨询 - 10次 16500.0</t>
         </is>
       </c>
     </row>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2407996.07</v>
+        <v>238421</v>
       </c>
       <c r="D2" t="n">
-        <v>7879</v>
+        <v>1556</v>
       </c>
       <c r="E2" t="n">
-        <v>2124393.07</v>
+        <v>190457</v>
       </c>
       <c r="F2" t="n">
-        <v>283603</v>
+        <v>47964</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2185131</v>
+        <v>198156</v>
       </c>
       <c r="D3" t="n">
-        <v>555</v>
+        <v>64</v>
       </c>
       <c r="E3" t="n">
-        <v>1908902</v>
+        <v>153680</v>
       </c>
       <c r="F3" t="n">
-        <v>276229</v>
+        <v>44476</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>222865.07</v>
+        <v>40265</v>
       </c>
       <c r="D4" t="n">
-        <v>7324</v>
+        <v>1492</v>
       </c>
       <c r="E4" t="n">
-        <v>215491.07</v>
+        <v>36777</v>
       </c>
       <c r="F4" t="n">
-        <v>7374</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5266931.82</v>
+        <v>413862</v>
       </c>
       <c r="D5" t="n">
-        <v>981</v>
+        <v>71</v>
       </c>
       <c r="E5" t="n">
-        <v>1001783.8</v>
+        <v>82796</v>
       </c>
       <c r="F5" t="n">
-        <v>4265148.02</v>
+        <v>331066</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3687601.02</v>
+        <v>283698</v>
       </c>
       <c r="D6" t="n">
-        <v>651</v>
+        <v>42</v>
       </c>
       <c r="E6" t="n">
-        <v>116440</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3571161.02</v>
+        <v>283698</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1559330.8</v>
+        <v>130164</v>
       </c>
       <c r="D7" t="n">
-        <v>329</v>
+        <v>29</v>
       </c>
       <c r="E7" t="n">
-        <v>885343.8</v>
+        <v>82796</v>
       </c>
       <c r="F7" t="n">
-        <v>673987</v>
+        <v>47368</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3715549.6</v>
+        <v>221048.14</v>
       </c>
       <c r="D8" t="n">
-        <v>2961</v>
+        <v>183</v>
       </c>
       <c r="E8" t="n">
-        <v>41843.55</v>
+        <v>5281.62</v>
       </c>
       <c r="F8" t="n">
-        <v>3673706.05</v>
+        <v>215766.52</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2200361.19</v>
+        <v>136490.54</v>
       </c>
       <c r="D9" t="n">
-        <v>1536</v>
+        <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>15445.18</v>
+        <v>1280.2</v>
       </c>
       <c r="F9" t="n">
-        <v>2184916.01</v>
+        <v>135210.34</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1511688.41</v>
+        <v>84557.60000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1423</v>
+        <v>83</v>
       </c>
       <c r="E10" t="n">
-        <v>26398.37</v>
+        <v>4001.42</v>
       </c>
       <c r="F10" t="n">
-        <v>1485290.04</v>
+        <v>80556.17999999999</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1139722</v>
+        <v>95200</v>
       </c>
       <c r="D11" t="n">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>716322</v>
+        <v>49600</v>
       </c>
       <c r="F11" t="n">
-        <v>423400</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="12">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>659109.8100000001</v>
+        <v>14578</v>
       </c>
       <c r="D12" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>453084.81</v>
+        <v>13398</v>
       </c>
       <c r="F12" t="n">
-        <v>206025</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="13">
@@ -727,16 +727,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>342234</v>
+        <v>57600</v>
       </c>
       <c r="D13" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>222034</v>
+        <v>57600</v>
       </c>
       <c r="F13" t="n">
-        <v>120200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>77220</v>
+        <v>23760</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>55440</v>
+        <v>5940</v>
       </c>
       <c r="F14" t="n">
-        <v>21780</v>
+        <v>17820</v>
       </c>
     </row>
   </sheetData>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3216882.06</v>
+        <v>209263.1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>96.59999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 3107079.06；咨询线 53582.0；菌群线 49600.0；课程线 4641.0；工作坊 1980.0</t>
+          <t>医疗线 206885.1；工作坊 1980.0；咨询线 398.0</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>737671.99</v>
+        <v>70714.89999999999</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>66.09999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 487912.0；菌群线 116000.0；医疗线 54000.99；营地 50500.0；课程线 27279.0；工作坊 1980.0</t>
+          <t>咨询线 56386.0；课程线 12329.0；工作坊 1980.0；医疗线 19.9</t>
         </is>
       </c>
     </row>
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>447986.06</v>
+        <v>8203.35</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>咨询线</t>
+          <t>课程线</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>82.90000000000001</v>
+        <v>60.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 371550.0；课程线 29204.0；菌群线 24800.0；医疗线 22432.06</t>
+          <t>课程线 4999.0；医疗线 2010.35；咨询线 1194.0</t>
         </is>
       </c>
     </row>
@@ -880,19 +880,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>867684.72</v>
+        <v>110819</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>咨询线</t>
+          <t>菌群线</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63.1</v>
+        <v>41.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 547148.02；课程线 102173.0；菌群线 92200.0；医疗线 44535.7；考证 39588.0；营地 36100.0；工作坊 5940.0</t>
+          <t>菌群线 45600.0；咨询线 41412.0；课程线 19847.0；工作坊 3960.0</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>701632.48</v>
+        <v>63793.4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>76</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 533448.0；医疗线 89584.48；考证 40587.0；菌群线 22800.0；课程线 15213.0</t>
+          <t>咨询线 61194.0；医疗线 1877.4；课程线 722.0</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>382022.99</v>
+        <v>41531</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -934,11 +934,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>95.7</v>
+        <v>99.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 365730.0；课程线 15293.0；考证 999.0；医疗线 0.99；菌群线 0.0</t>
+          <t>咨询线 41194.0；课程线 337.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>563220.4300000001</v>
+        <v>76394.32000000001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -957,11 +957,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>90.5</v>
+        <v>99</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 509714.0；医疗线 32263.43；课程线 21243.0；菌群线 0.0</t>
+          <t>咨询线 75594.0；医疗线 562.32；课程线 238.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>420389.73</v>
+        <v>20819</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>89.5</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 376258.0；菌群线 22800.0；医疗线 13458.73；课程线 6874.0；考证 999.0</t>
+          <t>咨询线 20600.0；医疗线 200.0；课程线 19.0</t>
         </is>
       </c>
     </row>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>779679.1</v>
+        <v>10991</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>咨询线</t>
+          <t>工作坊</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>81.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 637498.0；菌群线 70400.0；医疗线 63088.1；课程线 8693.0</t>
+          <t>工作坊 7920.0；咨询线 2496.0；医疗线 546.0；课程线 29.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253829</v>
+        <v>19415</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1026,11 +1026,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>73.40000000000001</v>
+        <v>51.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 186362.0；营地 33600.0；课程线 21487.0；工作坊 11880.0；医疗线 500.0；菌群线 0.0</t>
+          <t>咨询线 10000.0；课程线 9415.0</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>364723.97</v>
+        <v>20627</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1049,11 +1049,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>53.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 195946.0；考证 123752.0；菌群线 24800.0；课程线 19923.0；医疗线 302.97</t>
+          <t>咨询线 20598.0；课程线 29.0</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1104,11 +1104,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>唐歌</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>128220</v>
+        <v>19920</v>
       </c>
     </row>
     <row r="3">
@@ -1122,11 +1122,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>95520</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="4">
@@ -1140,11 +1140,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>王渊亮</t>
+          <t>肖伟</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>93860</v>
+        <v>16560</v>
       </c>
     </row>
     <row r="5">
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>93070</v>
+        <v>12940</v>
       </c>
     </row>
     <row r="6">
@@ -1176,11 +1176,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>81600</v>
+        <v>12320</v>
       </c>
     </row>
     <row r="7">
@@ -1194,11 +1194,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>邓璐</t>
+          <t>郑巨光</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>339578</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="8">
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>307804</v>
+        <v>39218</v>
       </c>
     </row>
     <row r="9">
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>221378</v>
+        <v>35796</v>
       </c>
     </row>
     <row r="10">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>191182</v>
+        <v>33992</v>
       </c>
     </row>
     <row r="11">
@@ -1266,11 +1266,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>周思若</t>
+          <t>谌黎平</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>172354</v>
+        <v>30796</v>
       </c>
     </row>
     <row r="12">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>629803.5699999999</v>
+        <v>51234</v>
       </c>
     </row>
     <row r="13">
@@ -1302,11 +1302,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>余佼</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>519440.74</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="14">
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>408074.64</v>
+        <v>37810</v>
       </c>
     </row>
     <row r="15">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>334273</v>
+        <v>34195</v>
       </c>
     </row>
     <row r="16">
@@ -1356,11 +1356,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>李浩然</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>322598</v>
+        <v>12104.1</v>
       </c>
     </row>
     <row r="17">
@@ -1374,11 +1374,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>江敏</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>169600</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="18">
@@ -1392,11 +1392,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>74400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="19">
@@ -1410,11 +1410,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>70400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="20">
@@ -1428,11 +1428,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>张喆</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>70400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>49600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1464,11 +1464,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>丁蕾</t>
+          <t>周紫姻</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>237388.01</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="23">
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>185728</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="24">
@@ -1500,11 +1500,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>朱碧丹</t>
+          <t>樊帆</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>84164</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="25">
@@ -1518,29 +1518,29 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>刘婷婷</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>39588</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>考证</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>赵越</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>39588</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="27">
@@ -1550,87 +1550,87 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>周玉枝</t>
+          <t>冯岚</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>59600</v>
+        <v>27800</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>营地</t>
+          <t>工作坊</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>闫丽东</t>
+          <t>袁登玉</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>46600</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>营地</t>
+          <t>工作坊</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>王秋</t>
+          <t>梁志超</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>36100</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>营地</t>
+          <t>工作坊</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>刘沁</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>33700</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>营地</t>
+          <t>工作坊</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>田婉丽</t>
+          <t>余佼</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>33600</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="32">
@@ -1640,87 +1640,15 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>江敏</t>
+          <t>张镜茹</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>27720</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>工作坊</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>丁蕾</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>9900</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>工作坊</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>3</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>田婉丽</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>7920</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>工作坊</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>4</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>陈新星</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>3960</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>工作坊</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>5</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>岳跃峰</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>3960</v>
+        <v>1980</v>
       </c>
     </row>
   </sheetData>
@@ -1786,26 +1714,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2407996.07</v>
+        <v>238421</v>
       </c>
       <c r="C2" t="n">
-        <v>357349.91</v>
+        <v>51544</v>
       </c>
       <c r="D2" t="n">
-        <v>52625.01</v>
+        <v>3873</v>
       </c>
       <c r="E2" t="n">
-        <v>2.19</v>
+        <v>1.62</v>
       </c>
       <c r="F2" t="n">
-        <v>304724.9</v>
+        <v>47671</v>
       </c>
       <c r="G2" t="n">
-        <v>12.65</v>
+        <v>19.99</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>青少年同行者计划 75527.0；青少年同行者计划护航营（6月） 69925.0；青少年同行者计划-护航营 46527.99</t>
+          <t>少年说陪伴计划 26400.0；青少年同行者计划领航营 3980.0；青少年同行者计划护航营（6月） 3700.0</t>
         </is>
       </c>
     </row>
@@ -1816,26 +1744,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5266931.82</v>
+        <v>413862</v>
       </c>
       <c r="C3" t="n">
-        <v>709042.28</v>
+        <v>72898</v>
       </c>
       <c r="D3" t="n">
-        <v>39796</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>669246.28</v>
+        <v>72898</v>
       </c>
       <c r="G3" t="n">
-        <v>12.71</v>
+        <v>17.61</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 265342.48；精神心理 210994.0；暑假礼遇咨询套餐 93600.0</t>
+          <t>精神心理 31398.0；儿童青少年 25500.0；睡眠障碍 10000.0</t>
         </is>
       </c>
     </row>
@@ -1846,26 +1774,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3715549.6</v>
+        <v>221048.14</v>
       </c>
       <c r="C4" t="n">
-        <v>1305783.04</v>
+        <v>71449</v>
       </c>
       <c r="D4" t="n">
-        <v>2029</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1303754.04</v>
+        <v>71449</v>
       </c>
       <c r="G4" t="n">
-        <v>35.09</v>
+        <v>32.32</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>治疗I（个体1000） 497903.14；日间中心 Ⅱ 212000.0；多动精灵产品套餐 194671.43</t>
+          <t>治疗I（个体1000） 40000.0；治疗III（个体1500） 30000.0；盐酸鲁拉西酮片 616.0</t>
         </is>
       </c>
     </row>
@@ -1876,26 +1804,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1139722</v>
+        <v>95200</v>
       </c>
       <c r="C5" t="n">
-        <v>427400</v>
+        <v>45600</v>
       </c>
       <c r="D5" t="n">
-        <v>24800</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>402600</v>
+        <v>45600</v>
       </c>
       <c r="G5" t="n">
-        <v>35.32</v>
+        <v>47.9</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>肠道菌群移植 292600.0；肠道菌群移植（双疗程优惠）  45600.0；肠道菌群移植（双疗程优惠） 41600.0</t>
+          <t>肠道菌群移植（双疗程） 45600.0</t>
         </is>
       </c>
     </row>
@@ -1906,26 +1834,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>659109.8100000001</v>
+        <v>14578</v>
       </c>
       <c r="C6" t="n">
-        <v>196930.27</v>
+        <v>37200</v>
       </c>
       <c r="D6" t="n">
-        <v>2817.9</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>194112.37</v>
+        <v>37200</v>
       </c>
       <c r="G6" t="n">
-        <v>29.45</v>
+        <v>255.18</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 119004.0；心灯计划-实战派心理咨询师执业培训项目（初+中阶-尾款） 38788.0；心理咨询 - 资深咨询 - 10次 16500.0</t>
+          <t>心灯计划-实战派-高阶培训课程 37200.0</t>
         </is>
       </c>
     </row>
@@ -1936,26 +1864,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>342234</v>
+        <v>57600</v>
       </c>
       <c r="C7" t="n">
-        <v>529780</v>
+        <v>38400</v>
       </c>
       <c r="D7" t="n">
-        <v>49800</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>14.55</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>479980</v>
+        <v>38400</v>
       </c>
       <c r="G7" t="n">
-        <v>140.25</v>
+        <v>66.67</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>蛋壳跳动身心复能营21天（一阶） 268600.0；青少年成长基地3月营（金盏基地） 188000.0；青少年基地3个月慈善价 49920.0</t>
+          <t>蛋壳跳动身心复能营21天（一阶） 38400.0</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1894,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>77220</v>
+        <v>23760</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>238421</v>
+        <v>397828.56</v>
       </c>
       <c r="D2" t="n">
-        <v>1556</v>
+        <v>3199</v>
       </c>
       <c r="E2" t="n">
-        <v>190457</v>
+        <v>331873.56</v>
       </c>
       <c r="F2" t="n">
-        <v>47964</v>
+        <v>65955</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>198156</v>
+        <v>313984</v>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="E3" t="n">
-        <v>153680</v>
+        <v>252872</v>
       </c>
       <c r="F3" t="n">
-        <v>44476</v>
+        <v>61112</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40265</v>
+        <v>83844.56</v>
       </c>
       <c r="D4" t="n">
-        <v>1492</v>
+        <v>3074</v>
       </c>
       <c r="E4" t="n">
-        <v>36777</v>
+        <v>79001.56</v>
       </c>
       <c r="F4" t="n">
-        <v>3488</v>
+        <v>4843</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>413862</v>
+        <v>940396</v>
       </c>
       <c r="D5" t="n">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="E5" t="n">
-        <v>82796</v>
+        <v>127592</v>
       </c>
       <c r="F5" t="n">
-        <v>331066</v>
+        <v>812804</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>283698</v>
+        <v>683766</v>
       </c>
       <c r="D6" t="n">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>283698</v>
+        <v>683766</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>130164</v>
+        <v>256630</v>
       </c>
       <c r="D7" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="E7" t="n">
-        <v>82796</v>
+        <v>127592</v>
       </c>
       <c r="F7" t="n">
-        <v>47368</v>
+        <v>129038</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>221048.14</v>
+        <v>798469.59</v>
       </c>
       <c r="D8" t="n">
-        <v>183</v>
+        <v>678</v>
       </c>
       <c r="E8" t="n">
-        <v>5281.62</v>
+        <v>7452.99</v>
       </c>
       <c r="F8" t="n">
-        <v>215766.52</v>
+        <v>791016.6</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>136490.54</v>
+        <v>449940.91</v>
       </c>
       <c r="D9" t="n">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="E9" t="n">
-        <v>1280.2</v>
+        <v>1870.82</v>
       </c>
       <c r="F9" t="n">
-        <v>135210.34</v>
+        <v>448070.09</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>84557.60000000001</v>
+        <v>346978.08</v>
       </c>
       <c r="D10" t="n">
-        <v>83</v>
+        <v>386</v>
       </c>
       <c r="E10" t="n">
-        <v>4001.42</v>
+        <v>5582.17</v>
       </c>
       <c r="F10" t="n">
-        <v>80556.17999999999</v>
+        <v>341395.91</v>
       </c>
     </row>
     <row r="11">
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>140800</v>
+      </c>
+      <c r="D11" t="n">
+        <v>13</v>
+      </c>
+      <c r="E11" t="n">
         <v>95200</v>
-      </c>
-      <c r="D11" t="n">
-        <v>9</v>
-      </c>
-      <c r="E11" t="n">
-        <v>49600</v>
       </c>
       <c r="F11" t="n">
         <v>45600</v>
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14578</v>
+        <v>66302</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>13398</v>
+        <v>24994</v>
       </c>
       <c r="F12" t="n">
-        <v>1180</v>
+        <v>41308</v>
       </c>
     </row>
     <row r="13">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>57600</v>
+        <v>204580</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>57600</v>
+        <v>204580</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23760</v>
+        <v>83160</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E14" t="n">
-        <v>5940</v>
+        <v>9900</v>
       </c>
       <c r="F14" t="n">
-        <v>17820</v>
+        <v>73260</v>
       </c>
     </row>
   </sheetData>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>209263.1</v>
+        <v>672622.6</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>98.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 206885.1；工作坊 1980.0；咨询线 398.0</t>
+          <t>医疗线 670188.6；工作坊 1980.0；咨询线 398.0；课程线 56.0</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70714.89999999999</v>
+        <v>128080.9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>79.7</v>
+        <v>80.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 56386.0；课程线 12329.0；工作坊 1980.0；医疗线 19.9</t>
+          <t>咨询线 102780.0；课程线 23301.0；工作坊 1980.0；医疗线 19.9</t>
         </is>
       </c>
     </row>
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8203.35</v>
+        <v>60287.35</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>课程线</t>
+          <t>考证</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>60.9</v>
+        <v>65.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>课程线 4999.0；医疗线 2010.35；咨询线 1194.0</t>
+          <t>考证 39588.0；咨询线 13190.0；课程线 4999.0；医疗线 2510.35</t>
         </is>
       </c>
     </row>
@@ -880,19 +880,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>110819</v>
+        <v>212742</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>菌群线</t>
+          <t>咨询线</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>菌群线 45600.0；咨询线 41412.0；课程线 19847.0；工作坊 3960.0</t>
+          <t>咨询线 87600.0；工作坊 57420.0；菌群线 45600.0；课程线 19903.0；医疗线 2219.0</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63793.4</v>
+        <v>126329.18</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>95.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 61194.0；医疗线 1877.4；课程线 722.0</t>
+          <t>咨询线 111992.0；课程线 7360.0；医疗线 6977.18；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>41531</v>
+        <v>102757</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -934,11 +934,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>99.2</v>
+        <v>97.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 41194.0；课程线 337.0</t>
+          <t>咨询线 100402.0；工作坊 1980.0；课程线 375.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>76394.32000000001</v>
+        <v>141067.6</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -957,11 +957,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>99</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 75594.0；医疗线 562.32；课程线 238.0</t>
+          <t>咨询线 139084.0；医疗线 1672.6；课程线 311.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20819</v>
+        <v>79311.38</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>98.90000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 20600.0；医疗线 200.0；课程线 19.0</t>
+          <t>咨询线 76290.0；医疗线 2955.38；课程线 66.0</t>
         </is>
       </c>
     </row>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10991</v>
+        <v>76719.2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>工作坊</t>
+          <t>咨询线</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>72.09999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>工作坊 7920.0；咨询线 2496.0；医疗线 546.0；课程线 29.0；菌群线 0.0</t>
+          <t>咨询线 64486.0；工作坊 7920.0；医疗线 4236.2；课程线 77.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19415</v>
+        <v>58236</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1026,11 +1026,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>51.5</v>
+        <v>83.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 10000.0；课程线 9415.0</t>
+          <t>咨询线 48796.0；课程线 9440.0</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20627</v>
+        <v>54653</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 20598.0；课程线 29.0</t>
+          <t>咨询线 54586.0；课程线 67.0</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19920</v>
+        <v>24900</v>
       </c>
     </row>
     <row r="3">
@@ -1122,11 +1122,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19800</v>
+        <v>22280</v>
       </c>
     </row>
     <row r="4">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16560</v>
+        <v>21540</v>
       </c>
     </row>
     <row r="5">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12940</v>
+        <v>19920</v>
       </c>
     </row>
     <row r="6">
@@ -1176,11 +1176,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12320</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="7">
@@ -1194,11 +1194,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>郑巨光</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>44000</v>
+        <v>58390</v>
       </c>
     </row>
     <row r="8">
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>39218</v>
+        <v>56216</v>
       </c>
     </row>
     <row r="9">
@@ -1230,11 +1230,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>郑巨光</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>35796</v>
+        <v>54398</v>
       </c>
     </row>
     <row r="10">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>33992</v>
+        <v>53292</v>
       </c>
     </row>
     <row r="11">
@@ -1266,11 +1266,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>谌黎平</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>30796</v>
+        <v>45796</v>
       </c>
     </row>
     <row r="12">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>51234</v>
+        <v>141277.5</v>
       </c>
     </row>
     <row r="13">
@@ -1302,11 +1302,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>余佼</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>40000</v>
+        <v>95501</v>
       </c>
     </row>
     <row r="14">
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>37810</v>
+        <v>85047</v>
       </c>
     </row>
     <row r="15">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>余佼</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>34195</v>
+        <v>77864</v>
       </c>
     </row>
     <row r="16">
@@ -1356,11 +1356,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12104.1</v>
+        <v>73009</v>
       </c>
     </row>
     <row r="17">
@@ -1374,11 +1374,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>45600</v>
+        <v>70400</v>
       </c>
     </row>
     <row r="18">
@@ -1392,11 +1392,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>24800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="19">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>张喆</t>
+          <t>于鹏飞</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>于鹏飞</t>
+          <t>姜玮</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1464,11 +1464,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>周紫姻</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3800</v>
+        <v>39588</v>
       </c>
     </row>
     <row r="23">
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3800</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="24">
@@ -1518,29 +1518,29 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>刘婷婷</t>
+          <t>周紫姻</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1180</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>营地</t>
+          <t>考证</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>武存英</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>29800</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="27">
@@ -1550,83 +1550,83 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>冯岚</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>27800</v>
+        <v>89400</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>工作坊</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>袁登玉</t>
+          <t>宋晨曦</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>7920</v>
+        <v>55600</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>工作坊</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>梁志超</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3960</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>工作坊</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>冯岚</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1980</v>
+        <v>27800</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>工作坊</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>余佼</t>
+          <t>姜人荷</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1640,14 +1640,86 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>岳伟伟</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>51480</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>工作坊</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>袁登玉</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>7920</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>工作坊</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>王航</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>工作坊</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>梁志超</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>工作坊</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
         <v>5</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>张镜茹</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D36" t="n">
         <v>1980</v>
       </c>
     </row>
@@ -1714,26 +1786,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>238421</v>
+        <v>397828.56</v>
       </c>
       <c r="C2" t="n">
-        <v>51544</v>
+        <v>140262</v>
       </c>
       <c r="D2" t="n">
-        <v>3873</v>
+        <v>10499</v>
       </c>
       <c r="E2" t="n">
-        <v>1.62</v>
+        <v>2.64</v>
       </c>
       <c r="F2" t="n">
-        <v>47671</v>
+        <v>129763</v>
       </c>
       <c r="G2" t="n">
-        <v>19.99</v>
+        <v>32.62</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 26400.0；青少年同行者计划领航营 3980.0；青少年同行者计划护航营（6月） 3700.0</t>
+          <t>少年说陪伴计划 79200.0；青少年同行者计划领航营 15920.0；青少年同行者计划护航营（6月） 8680.0</t>
         </is>
       </c>
     </row>
@@ -1744,10 +1816,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>413862</v>
+        <v>940396</v>
       </c>
       <c r="C3" t="n">
-        <v>72898</v>
+        <v>102497.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1756,14 +1828,14 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>72898</v>
+        <v>102497.98</v>
       </c>
       <c r="G3" t="n">
-        <v>17.61</v>
+        <v>10.9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>精神心理 31398.0；儿童青少年 25500.0；睡眠障碍 10000.0</t>
+          <t>精神心理 43398.0；儿童青少年 41999.98；睡眠障碍 10000.0</t>
         </is>
       </c>
     </row>
@@ -1774,10 +1846,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>221048.14</v>
+        <v>798469.59</v>
       </c>
       <c r="C4" t="n">
-        <v>71449</v>
+        <v>266398.42</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1786,14 +1858,14 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>71449</v>
+        <v>266398.42</v>
       </c>
       <c r="G4" t="n">
-        <v>32.32</v>
+        <v>33.36</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>治疗I（个体1000） 40000.0；治疗III（个体1500） 30000.0；盐酸鲁拉西酮片 616.0</t>
+          <t>日间中心 Ⅱ 115000.0；治疗I（个体1000） 40000.0；诊费I（1000） 40000.0</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1876,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95200</v>
+        <v>140800</v>
       </c>
       <c r="C5" t="n">
         <v>45600</v>
@@ -1819,7 +1891,7 @@
         <v>45600</v>
       </c>
       <c r="G5" t="n">
-        <v>47.9</v>
+        <v>32.39</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1834,26 +1906,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14578</v>
+        <v>66302</v>
       </c>
       <c r="C6" t="n">
-        <v>37200</v>
+        <v>53106</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1998</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="F6" t="n">
-        <v>37200</v>
+        <v>51108</v>
       </c>
       <c r="G6" t="n">
-        <v>255.18</v>
+        <v>77.08</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>心灯计划-实战派-高阶培训课程 37200.0</t>
+          <t>心灯计划-实战派-高阶培训课程 37200.0；心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 13908.0；完形心理基训课 1998.0</t>
         </is>
       </c>
     </row>
@@ -1864,10 +1936,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57600</v>
+        <v>204580</v>
       </c>
       <c r="C7" t="n">
-        <v>38400</v>
+        <v>90200</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1876,14 +1948,14 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>38400</v>
+        <v>90200</v>
       </c>
       <c r="G7" t="n">
-        <v>66.67</v>
+        <v>44.09</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>蛋壳跳动身心复能营21天（一阶） 38400.0</t>
+          <t>蛋壳跳动身心复能营21天（一阶） 69200.0；青少年【未来之翼】身心节律复能7日营 16800.0；青少年营地食宿费补差价 4200.0</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1966,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23760</v>
+        <v>83160</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>397828.56</v>
+        <v>609916.5600000001</v>
       </c>
       <c r="D2" t="n">
-        <v>3199</v>
+        <v>3692</v>
       </c>
       <c r="E2" t="n">
-        <v>331873.56</v>
+        <v>541929.5600000001</v>
       </c>
       <c r="F2" t="n">
-        <v>65955</v>
+        <v>67987</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>313984</v>
+        <v>512895</v>
       </c>
       <c r="D3" t="n">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="E3" t="n">
-        <v>252872</v>
+        <v>450065</v>
       </c>
       <c r="F3" t="n">
-        <v>61112</v>
+        <v>62830</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>83844.56</v>
+        <v>97021.56</v>
       </c>
       <c r="D4" t="n">
-        <v>3074</v>
+        <v>3516</v>
       </c>
       <c r="E4" t="n">
-        <v>79001.56</v>
+        <v>91864.56</v>
       </c>
       <c r="F4" t="n">
-        <v>4843</v>
+        <v>5157</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>940396</v>
+        <v>1140102</v>
       </c>
       <c r="D5" t="n">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="E5" t="n">
-        <v>127592</v>
+        <v>179208</v>
       </c>
       <c r="F5" t="n">
-        <v>812804</v>
+        <v>960894</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>683766</v>
+        <v>776454</v>
       </c>
       <c r="D6" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>683766</v>
+        <v>776454</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>256630</v>
+        <v>363648</v>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E7" t="n">
-        <v>127592</v>
+        <v>179208</v>
       </c>
       <c r="F7" t="n">
-        <v>129038</v>
+        <v>184440</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>798469.59</v>
+        <v>839309.99</v>
       </c>
       <c r="D8" t="n">
-        <v>678</v>
+        <v>714</v>
       </c>
       <c r="E8" t="n">
-        <v>7452.99</v>
+        <v>10350.49</v>
       </c>
       <c r="F8" t="n">
-        <v>791016.6</v>
+        <v>828959.5</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>449940.91</v>
+        <v>475663.17</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="E9" t="n">
-        <v>1870.82</v>
+        <v>1921.32</v>
       </c>
       <c r="F9" t="n">
-        <v>448070.09</v>
+        <v>473741.85</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>346978.08</v>
+        <v>362096.22</v>
       </c>
       <c r="D10" t="n">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="E10" t="n">
-        <v>5582.17</v>
+        <v>8429.17</v>
       </c>
       <c r="F10" t="n">
-        <v>341395.91</v>
+        <v>353667.05</v>
       </c>
     </row>
     <row r="11">
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>140800</v>
+        <v>165600</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>95200</v>
+        <v>120000</v>
       </c>
       <c r="F11" t="n">
         <v>45600</v>
@@ -703,13 +703,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>66302</v>
+        <v>105909.9</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E12" t="n">
-        <v>24994</v>
+        <v>64601.9</v>
       </c>
       <c r="F12" t="n">
         <v>41308</v>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>204580</v>
+        <v>227780</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>204580</v>
+        <v>227780</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -751,13 +751,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>83160</v>
+        <v>85140</v>
       </c>
       <c r="D14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E14" t="n">
-        <v>9900</v>
+        <v>11880</v>
       </c>
       <c r="F14" t="n">
         <v>73260</v>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>672622.6</v>
+        <v>690719.6</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 670188.6；工作坊 1980.0；咨询线 398.0；课程线 56.0</t>
+          <t>医疗线 688285.6；工作坊 1980.0；咨询线 398.0；课程线 56.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>128080.9</v>
+        <v>173468.9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>80.2</v>
+        <v>84.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 102780.0；课程线 23301.0；工作坊 1980.0；医疗线 19.9</t>
+          <t>咨询线 146188.0；课程线 23301.0；工作坊 3960.0；医疗线 19.9</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60287.35</v>
+        <v>70885.35000000001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -865,11 +865,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>65.7</v>
+        <v>55.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>考证 39588.0；咨询线 13190.0；课程线 4999.0；医疗线 2510.35</t>
+          <t>考证 39588.0；咨询线 23788.0；课程线 4999.0；医疗线 2510.35</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>212742</v>
+        <v>244813.14</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>41.2</v>
+        <v>48.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 87600.0；工作坊 57420.0；菌群线 45600.0；课程线 19903.0；医疗线 2219.0</t>
+          <t>咨询线 118794.0；工作坊 57420.0；菌群线 45600.0；课程线 19969.0；医疗线 3030.14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>126329.18</v>
+        <v>130140.14</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>88.7</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 111992.0；课程线 7360.0；医疗线 6977.18；菌群线 0.0</t>
+          <t>咨询线 115092.0；医疗线 7669.14；课程线 7379.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>102757</v>
+        <v>129637</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -934,11 +934,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>97.7</v>
+        <v>96.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 100402.0；工作坊 1980.0；课程线 375.0</t>
+          <t>咨询线 125402.0；课程线 2255.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>141067.6</v>
+        <v>151067.6</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -957,11 +957,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>98.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 139084.0；医疗线 1672.6；课程线 311.0</t>
+          <t>咨询线 149084.0；医疗线 1672.6；课程线 311.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79311.38</v>
+        <v>98055.08</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>96.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 76290.0；医疗线 2955.38；课程线 66.0</t>
+          <t>咨询线 77886.0；医疗线 20103.08；课程线 66.0</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76719.2</v>
+        <v>88341.3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1003,11 +1003,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>84.09999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 64486.0；工作坊 7920.0；医疗线 4236.2；课程线 77.0；菌群线 0.0</t>
+          <t>咨询线 74884.0；工作坊 7920.0；医疗线 5431.3；课程线 106.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>58236</v>
+        <v>59051</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1026,11 +1026,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>83.8</v>
+        <v>84</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 48796.0；课程线 9440.0</t>
+          <t>咨询线 49592.0；课程线 9459.0</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54653</v>
+        <v>66672</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 54586.0；课程线 67.0</t>
+          <t>咨询线 66586.0；课程线 86.0</t>
         </is>
       </c>
     </row>
@@ -1104,11 +1104,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>唐歌</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24900</v>
+        <v>42820</v>
       </c>
     </row>
     <row r="3">
@@ -1122,11 +1122,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>肖伟</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22280</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="4">
@@ -1140,11 +1140,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>肖伟</t>
+          <t>郑鲁</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21540</v>
+        <v>26400</v>
       </c>
     </row>
     <row r="5">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>唐歌</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19920</v>
+        <v>24900</v>
       </c>
     </row>
     <row r="6">
@@ -1176,11 +1176,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>陈志强</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19800</v>
+        <v>24900</v>
       </c>
     </row>
     <row r="7">
@@ -1266,11 +1266,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>刘沁</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>45796</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="12">
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>余佼</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>85047</v>
+        <v>88906</v>
       </c>
     </row>
     <row r="15">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>余佼</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>77864</v>
+        <v>83407</v>
       </c>
     </row>
     <row r="16">
@@ -1356,11 +1356,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>73009</v>
+        <v>81704</v>
       </c>
     </row>
     <row r="17">
@@ -1428,11 +1428,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>于鹏飞</t>
+          <t>何媛媛</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="21">
@@ -1464,11 +1464,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>梁志超</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>39588</v>
+        <v>47188</v>
       </c>
     </row>
     <row r="23">
@@ -1482,11 +1482,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>梁志超</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7600</v>
+        <v>39588</v>
       </c>
     </row>
     <row r="24">
@@ -1626,11 +1626,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>姜人荷</t>
+          <t>武存英</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1980</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="32">
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3960</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="35">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>张镜茹</t>
+          <t>余佼</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>397828.56</v>
+        <v>609916.5600000001</v>
       </c>
       <c r="C2" t="n">
-        <v>140262</v>
+        <v>164098</v>
       </c>
       <c r="D2" t="n">
-        <v>10499</v>
+        <v>12468</v>
       </c>
       <c r="E2" t="n">
-        <v>2.64</v>
+        <v>2.04</v>
       </c>
       <c r="F2" t="n">
-        <v>129763</v>
+        <v>151630</v>
       </c>
       <c r="G2" t="n">
-        <v>32.62</v>
+        <v>24.86</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 79200.0；青少年同行者计划领航营 15920.0；青少年同行者计划护航营（6月） 8680.0</t>
+          <t>少年说陪伴计划 79200.0；青少年同行者计划领航营 19900.0；少年说 陪伴计划 13200.0</t>
         </is>
       </c>
     </row>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>940396</v>
+        <v>1140102</v>
       </c>
       <c r="C3" t="n">
-        <v>102497.98</v>
+        <v>119997.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1828,14 +1828,14 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>102497.98</v>
+        <v>119997.98</v>
       </c>
       <c r="G3" t="n">
-        <v>10.9</v>
+        <v>10.53</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>精神心理 43398.0；儿童青少年 41999.98；睡眠障碍 10000.0</t>
+          <t>儿童青少年 59499.98；精神心理 43398.0；睡眠障碍 10000.0</t>
         </is>
       </c>
     </row>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>798469.59</v>
+        <v>839309.99</v>
       </c>
       <c r="C4" t="n">
-        <v>266398.42</v>
+        <v>267398.42</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1858,10 +1858,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>266398.42</v>
+        <v>267398.42</v>
       </c>
       <c r="G4" t="n">
-        <v>33.36</v>
+        <v>31.86</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>140800</v>
+        <v>165600</v>
       </c>
       <c r="C5" t="n">
         <v>45600</v>
@@ -1891,7 +1891,7 @@
         <v>45600</v>
       </c>
       <c r="G5" t="n">
-        <v>32.39</v>
+        <v>27.54</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1906,26 +1906,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66302</v>
+        <v>105909.9</v>
       </c>
       <c r="C6" t="n">
-        <v>53106</v>
+        <v>95106</v>
       </c>
       <c r="D6" t="n">
         <v>1998</v>
       </c>
       <c r="E6" t="n">
-        <v>3.01</v>
+        <v>1.89</v>
       </c>
       <c r="F6" t="n">
-        <v>51108</v>
+        <v>93108</v>
       </c>
       <c r="G6" t="n">
-        <v>77.08</v>
+        <v>87.91</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>心灯计划-实战派-高阶培训课程 37200.0；心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 13908.0；完形心理基训课 1998.0</t>
+          <t>心灯计划-实战派-高阶培训课程 79200.0；心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 13908.0；完形心理基训课 1998.0</t>
         </is>
       </c>
     </row>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>204580</v>
+        <v>227780</v>
       </c>
       <c r="C7" t="n">
-        <v>90200</v>
+        <v>119866.67</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1948,14 +1948,14 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>90200</v>
+        <v>119866.67</v>
       </c>
       <c r="G7" t="n">
-        <v>44.09</v>
+        <v>52.62</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>蛋壳跳动身心复能营21天（一阶） 69200.0；青少年【未来之翼】身心节律复能7日营 16800.0；青少年营地食宿费补差价 4200.0</t>
+          <t>蛋壳跳动身心复能营21天（一阶） 98866.67；青少年【未来之翼】身心节律复能7日营 16800.0；青少年营地食宿费补差价 4200.0</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83160</v>
+        <v>85140</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>609916.5600000001</v>
+        <v>744693.5600000001</v>
       </c>
       <c r="D2" t="n">
-        <v>3692</v>
+        <v>4283</v>
       </c>
       <c r="E2" t="n">
-        <v>541929.5600000001</v>
+        <v>665921.5600000001</v>
       </c>
       <c r="F2" t="n">
-        <v>67987</v>
+        <v>78772</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>512895</v>
+        <v>632924</v>
       </c>
       <c r="D3" t="n">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="E3" t="n">
-        <v>450065</v>
+        <v>561277</v>
       </c>
       <c r="F3" t="n">
-        <v>62830</v>
+        <v>71647</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>97021.56</v>
+        <v>111769.56</v>
       </c>
       <c r="D4" t="n">
-        <v>3516</v>
+        <v>4075</v>
       </c>
       <c r="E4" t="n">
-        <v>91864.56</v>
+        <v>104644.56</v>
       </c>
       <c r="F4" t="n">
-        <v>5157</v>
+        <v>7125</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1140102</v>
+        <v>1341888</v>
       </c>
       <c r="D5" t="n">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="E5" t="n">
-        <v>179208</v>
+        <v>243406</v>
       </c>
       <c r="F5" t="n">
-        <v>960894</v>
+        <v>1098482</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>776454</v>
+        <v>894838</v>
       </c>
       <c r="D6" t="n">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>776454</v>
+        <v>894838</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>363648</v>
+        <v>447050</v>
       </c>
       <c r="D7" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E7" t="n">
-        <v>179208</v>
+        <v>243406</v>
       </c>
       <c r="F7" t="n">
-        <v>184440</v>
+        <v>203644</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>839309.99</v>
+        <v>854984.47</v>
       </c>
       <c r="D8" t="n">
-        <v>714</v>
+        <v>778</v>
       </c>
       <c r="E8" t="n">
-        <v>10350.49</v>
+        <v>12379.49</v>
       </c>
       <c r="F8" t="n">
-        <v>828959.5</v>
+        <v>842604.98</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>475663.17</v>
+        <v>477175.17</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="E9" t="n">
-        <v>1921.32</v>
+        <v>2121.32</v>
       </c>
       <c r="F9" t="n">
-        <v>473741.85</v>
+        <v>475053.85</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>362096.22</v>
+        <v>376258.7</v>
       </c>
       <c r="D10" t="n">
-        <v>403</v>
+        <v>460</v>
       </c>
       <c r="E10" t="n">
-        <v>8429.17</v>
+        <v>10258.17</v>
       </c>
       <c r="F10" t="n">
-        <v>353667.05</v>
+        <v>366000.53</v>
       </c>
     </row>
     <row r="11">
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>165600</v>
+        <v>167600</v>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E11" t="n">
-        <v>120000</v>
+        <v>122000</v>
       </c>
       <c r="F11" t="n">
         <v>45600</v>
@@ -703,13 +703,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>105909.9</v>
+        <v>131308.9</v>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E12" t="n">
-        <v>64601.9</v>
+        <v>90000.89999999999</v>
       </c>
       <c r="F12" t="n">
         <v>41308</v>
@@ -727,16 +727,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>227780</v>
+        <v>257080</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>227780</v>
+        <v>229280</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>27800</v>
       </c>
     </row>
     <row r="14">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>85140</v>
+        <v>89100</v>
       </c>
       <c r="D14" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E14" t="n">
-        <v>11880</v>
+        <v>13860</v>
       </c>
       <c r="F14" t="n">
-        <v>73260</v>
+        <v>75240</v>
       </c>
     </row>
   </sheetData>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>690719.6</v>
+        <v>709823.6</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>99.59999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 688285.6；工作坊 1980.0；咨询线 398.0；课程线 56.0；菌群线 0.0</t>
+          <t>医疗线 694792.6；咨询线 10398.0；工作坊 3960.0；课程线 673.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>173468.9</v>
+        <v>212939.9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>84.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 146188.0；课程线 23301.0；工作坊 3960.0；医疗线 19.9</t>
+          <t>咨询线 184994.0；课程线 23966.0；工作坊 3960.0；医疗线 19.9</t>
         </is>
       </c>
     </row>
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70885.35000000001</v>
+        <v>121716.35</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>考证</t>
+          <t>咨询线</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>55.8</v>
+        <v>38.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>考证 39588.0；咨询线 23788.0；课程线 4999.0；医疗线 2510.35</t>
+          <t>咨询线 46784.0；考证 39588.0；营地 27800.0；课程线 5034.0；医疗线 2510.35</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>244813.14</v>
+        <v>253557.14</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>48.5</v>
+        <v>47</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 118794.0；工作坊 57420.0；菌群线 45600.0；课程线 19969.0；医疗线 3030.14</t>
+          <t>咨询线 119192.0；工作坊 57420.0；菌群线 45600.0；课程线 28315.0；医疗线 3030.14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>130140.14</v>
+        <v>146937.94</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>88.40000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 115092.0；医疗线 7669.14；课程线 7379.0；菌群线 0.0</t>
+          <t>咨询线 131390.0；医疗线 7850.94；课程线 7697.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>129637</v>
+        <v>150140</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -934,11 +934,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>96.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 125402.0；课程线 2255.0；工作坊 1980.0</t>
+          <t>咨询线 145800.0；课程线 2360.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>151067.6</v>
+        <v>168196.38</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -957,11 +957,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>98.7</v>
+        <v>96.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 149084.0；医疗线 1672.6；课程线 311.0</t>
+          <t>咨询线 161880.0；医疗线 5449.38；课程线 867.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>98055.08</v>
+        <v>103479.08</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>79.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 77886.0；医疗线 20103.08；课程线 66.0</t>
+          <t>咨询线 82986.0；医疗线 20408.08；课程线 85.0</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>88341.3</v>
+        <v>101087.2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 74884.0；工作坊 7920.0；医疗线 5431.3；课程线 106.0；菌群线 0.0</t>
+          <t>咨询线 85680.0；工作坊 7920.0；医疗线 7276.2；课程线 211.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>66672</v>
+        <v>66691</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1049,11 +1049,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 66586.0；课程线 86.0</t>
+          <t>咨询线 66586.0；课程线 105.0</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>42820</v>
+        <v>54400</v>
       </c>
     </row>
     <row r="3">
@@ -1122,11 +1122,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>肖伟</t>
+          <t>陈志强</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31500</v>
+        <v>44820</v>
       </c>
     </row>
     <row r="4">
@@ -1140,11 +1140,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>郑鲁</t>
+          <t>肖伟</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>26400</v>
+        <v>41460</v>
       </c>
     </row>
     <row r="5">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>唐歌</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24900</v>
+        <v>32860</v>
       </c>
     </row>
     <row r="6">
@@ -1176,11 +1176,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>陈志强</t>
+          <t>刘士明</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24900</v>
+        <v>31560</v>
       </c>
     </row>
     <row r="7">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>58390</v>
+        <v>68390</v>
       </c>
     </row>
     <row r="8">
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>56216</v>
+        <v>56614</v>
       </c>
     </row>
     <row r="9">
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>54398</v>
+        <v>55194</v>
       </c>
     </row>
     <row r="10">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>刘沁</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>53292</v>
+        <v>55006</v>
       </c>
     </row>
     <row r="11">
@@ -1266,11 +1266,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>刘沁</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>46200</v>
+        <v>54196</v>
       </c>
     </row>
     <row r="12">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>141277.5</v>
+        <v>141831.5</v>
       </c>
     </row>
     <row r="13">
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>余佼</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>88906</v>
+        <v>89102</v>
       </c>
     </row>
     <row r="15">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>余佼</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>83407</v>
+        <v>88906</v>
       </c>
     </row>
     <row r="16">
@@ -1446,11 +1446,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>姜玮</t>
+          <t>武存英</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="22">
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>47188</v>
+        <v>67788</v>
       </c>
     </row>
     <row r="23">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>樊帆</t>
+          <t>卢忠慧</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>周紫姻</t>
+          <t>樊帆</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>武存英</t>
+          <t>周紫姻</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1626,11 +1626,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>武存英</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>23200</v>
+        <v>27800</v>
       </c>
     </row>
     <row r="32">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>余佼</t>
+          <t>刘沁</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>609916.5600000001</v>
+        <v>744693.5600000001</v>
       </c>
       <c r="C2" t="n">
-        <v>164098</v>
+        <v>190446.9</v>
       </c>
       <c r="D2" t="n">
-        <v>12468</v>
+        <v>13815</v>
       </c>
       <c r="E2" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="F2" t="n">
-        <v>151630</v>
+        <v>176631.9</v>
       </c>
       <c r="G2" t="n">
-        <v>24.86</v>
+        <v>23.72</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 79200.0；青少年同行者计划领航营 19900.0；少年说 陪伴计划 13200.0</t>
+          <t>少年说陪伴计划 85800.0；青少年同行者计划领航营 31840.0；少年说 陪伴计划 13200.0</t>
         </is>
       </c>
     </row>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1140102</v>
+        <v>1341888</v>
       </c>
       <c r="C3" t="n">
-        <v>119997.98</v>
+        <v>160997.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1828,14 +1828,14 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>119997.98</v>
+        <v>160997.98</v>
       </c>
       <c r="G3" t="n">
-        <v>10.53</v>
+        <v>12</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 59499.98；精神心理 43398.0；睡眠障碍 10000.0</t>
+          <t>儿童青少年 96499.98；精神心理 43398.0；电商咨询 10000.0</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>839309.99</v>
+        <v>854984.47</v>
       </c>
       <c r="C4" t="n">
         <v>267398.42</v>
@@ -1861,7 +1861,7 @@
         <v>267398.42</v>
       </c>
       <c r="G4" t="n">
-        <v>31.86</v>
+        <v>31.28</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>165600</v>
+        <v>167600</v>
       </c>
       <c r="C5" t="n">
         <v>45600</v>
@@ -1891,7 +1891,7 @@
         <v>45600</v>
       </c>
       <c r="G5" t="n">
-        <v>27.54</v>
+        <v>27.21</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1906,22 +1906,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>105909.9</v>
+        <v>131308.9</v>
       </c>
       <c r="C6" t="n">
-        <v>95106</v>
+        <v>95125.89999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>1998</v>
+        <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>1.89</v>
+        <v>1.54</v>
       </c>
       <c r="F6" t="n">
         <v>93108</v>
       </c>
       <c r="G6" t="n">
-        <v>87.91</v>
+        <v>70.91</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>227780</v>
+        <v>257080</v>
       </c>
       <c r="C7" t="n">
         <v>119866.67</v>
@@ -1951,7 +1951,7 @@
         <v>119866.67</v>
       </c>
       <c r="G7" t="n">
-        <v>52.62</v>
+        <v>46.63</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85140</v>
+        <v>89100</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>744693.5600000001</v>
+        <v>822596.5600000001</v>
       </c>
       <c r="D2" t="n">
-        <v>4283</v>
+        <v>4778</v>
       </c>
       <c r="E2" t="n">
-        <v>665921.5600000001</v>
+        <v>730134.5600000001</v>
       </c>
       <c r="F2" t="n">
-        <v>78772</v>
+        <v>92462</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>632924</v>
+        <v>696996</v>
       </c>
       <c r="D3" t="n">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="E3" t="n">
-        <v>561277</v>
+        <v>612149</v>
       </c>
       <c r="F3" t="n">
-        <v>71647</v>
+        <v>84847</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>111769.56</v>
+        <v>125600.56</v>
       </c>
       <c r="D4" t="n">
-        <v>4075</v>
+        <v>4549</v>
       </c>
       <c r="E4" t="n">
-        <v>104644.56</v>
+        <v>117985.56</v>
       </c>
       <c r="F4" t="n">
-        <v>7125</v>
+        <v>7615</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1341888</v>
+        <v>1562632</v>
       </c>
       <c r="D5" t="n">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="E5" t="n">
-        <v>243406</v>
+        <v>340662</v>
       </c>
       <c r="F5" t="n">
-        <v>1098482</v>
+        <v>1221970</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>894838</v>
+        <v>1001530</v>
       </c>
       <c r="D6" t="n">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="F6" t="n">
-        <v>894838</v>
+        <v>989530</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>447050</v>
+        <v>546102</v>
       </c>
       <c r="D7" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E7" t="n">
-        <v>243406</v>
+        <v>328662</v>
       </c>
       <c r="F7" t="n">
-        <v>203644</v>
+        <v>217440</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>854984.47</v>
+        <v>1058465.01</v>
       </c>
       <c r="D8" t="n">
-        <v>778</v>
+        <v>908</v>
       </c>
       <c r="E8" t="n">
-        <v>12379.49</v>
+        <v>10706.74</v>
       </c>
       <c r="F8" t="n">
-        <v>842604.98</v>
+        <v>1047758.27</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>477175.17</v>
+        <v>631410.54</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>396</v>
       </c>
       <c r="E9" t="n">
-        <v>2121.32</v>
+        <v>2161.37</v>
       </c>
       <c r="F9" t="n">
-        <v>475053.85</v>
+        <v>629249.17</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>376258.7</v>
+        <v>425503.87</v>
       </c>
       <c r="D10" t="n">
-        <v>460</v>
+        <v>510</v>
       </c>
       <c r="E10" t="n">
-        <v>10258.17</v>
+        <v>8545.370000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>366000.53</v>
+        <v>416958.5</v>
       </c>
     </row>
     <row r="11">
@@ -682,7 +682,7 @@
         <v>167600</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
         <v>122000</v>
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>131308.9</v>
+        <v>176691.9</v>
       </c>
       <c r="D12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E12" t="n">
-        <v>90000.89999999999</v>
+        <v>95795.89999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>41308</v>
+        <v>80896</v>
       </c>
     </row>
     <row r="13">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>89100</v>
+        <v>95040</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E14" t="n">
         <v>13860</v>
       </c>
       <c r="F14" t="n">
-        <v>75240</v>
+        <v>81180</v>
       </c>
     </row>
   </sheetData>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>709823.6</v>
+        <v>912460.6</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>97.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 694792.6；咨询线 10398.0；工作坊 3960.0；课程线 673.0；菌群线 0.0</t>
+          <t>医疗线 891489.6；咨询线 10398.0；工作坊 9900.0；课程线 673.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>212939.9</v>
+        <v>254048.9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>86.90000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 184994.0；课程线 23966.0；工作坊 3960.0；医疗线 19.9</t>
+          <t>咨询线 209994.0；课程线 37275.0；工作坊 3960.0；医疗线 2819.9</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>121716.35</v>
+        <v>142133.35</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -865,11 +865,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.4</v>
+        <v>47.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 46784.0；考证 39588.0；营地 27800.0；课程线 5034.0；医疗线 2510.35</t>
+          <t>咨询线 67182.0；考证 39588.0；营地 27800.0；课程线 5053.0；医疗线 2510.35</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>253557.14</v>
+        <v>261576.14</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>47</v>
+        <v>48.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 119192.0；工作坊 57420.0；菌群线 45600.0；课程线 28315.0；医疗线 3030.14</t>
+          <t>咨询线 127192.0；工作坊 57420.0；菌群线 45600.0；课程线 28334.0；医疗线 3030.14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>146937.94</v>
+        <v>184230.94</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>89.40000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 131390.0；医疗线 7850.94；课程线 7697.0；菌群线 0.0</t>
+          <t>咨询线 168184.0；医疗线 8050.94；课程线 7996.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>150140</v>
+        <v>150178</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 145800.0；课程线 2360.0；工作坊 1980.0</t>
+          <t>咨询线 145800.0；课程线 2398.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>168196.38</v>
+        <v>192514.4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -957,11 +957,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>96.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 161880.0；医疗线 5449.38；课程线 867.0</t>
+          <t>咨询线 182676.0；医疗线 8971.4；课程线 867.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>103479.08</v>
+        <v>110985.08</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>80.2</v>
+        <v>81.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 82986.0；医疗线 20408.08；课程线 85.0</t>
+          <t>咨询线 90486.0；医疗线 20408.08；课程线 91.0</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>66691</v>
+        <v>106279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1049,11 +1049,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>99.8</v>
+        <v>62.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 66586.0；课程线 105.0</t>
+          <t>咨询线 66586.0；考证 39588.0；课程线 105.0</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>44820</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="4">
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32860</v>
+        <v>37840</v>
       </c>
     </row>
     <row r="6">
@@ -1194,11 +1194,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>68390</v>
+        <v>74196</v>
       </c>
     </row>
     <row r="8">
@@ -1212,11 +1212,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>56614</v>
+        <v>73418</v>
       </c>
     </row>
     <row r="9">
@@ -1230,11 +1230,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>郑巨光</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>55194</v>
+        <v>68390</v>
       </c>
     </row>
     <row r="10">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>刘沁</t>
+          <t>郑巨光</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>55006</v>
+        <v>65592</v>
       </c>
     </row>
     <row r="11">
@@ -1266,11 +1266,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>54196</v>
+        <v>63292</v>
       </c>
     </row>
     <row r="12">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>141831.5</v>
+        <v>144981.5</v>
       </c>
     </row>
     <row r="13">
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>95501</v>
+        <v>143291</v>
       </c>
     </row>
     <row r="14">
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>李浩然</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>89102</v>
+        <v>99945</v>
       </c>
     </row>
     <row r="15">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>88906</v>
+        <v>95070</v>
       </c>
     </row>
     <row r="16">
@@ -1356,11 +1356,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>81704</v>
+        <v>94497</v>
       </c>
     </row>
     <row r="17">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>曾妍妍</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1500,11 +1500,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>卢忠慧</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3800</v>
+        <v>39588</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>樊帆</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>周紫姻</t>
+          <t>卢忠慧</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>王凯</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1698,11 +1698,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>梁志超</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3960</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="36">
@@ -1716,11 +1716,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>刘沁</t>
+          <t>梁志超</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1980</v>
+        <v>3960</v>
       </c>
     </row>
   </sheetData>
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>744693.5600000001</v>
+        <v>822596.5600000001</v>
       </c>
       <c r="C2" t="n">
-        <v>190446.9</v>
+        <v>200694.9</v>
       </c>
       <c r="D2" t="n">
-        <v>13815</v>
+        <v>14728</v>
       </c>
       <c r="E2" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="F2" t="n">
-        <v>176631.9</v>
+        <v>185966.9</v>
       </c>
       <c r="G2" t="n">
-        <v>23.72</v>
+        <v>22.61</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 85800.0；青少年同行者计划领航营 31840.0；少年说 陪伴计划 13200.0</t>
+          <t>少年说陪伴计划 85800.0；青少年同行者计划领航营 35820.0；少年说 陪伴计划 13200.0</t>
         </is>
       </c>
     </row>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1341888</v>
+        <v>1562632</v>
       </c>
       <c r="C3" t="n">
-        <v>160997.98</v>
+        <v>199797.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1828,14 +1828,14 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>160997.98</v>
+        <v>199797.98</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>12.79</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 96499.98；精神心理 43398.0；电商咨询 10000.0</t>
+          <t>儿童青少年 108499.98；精神心理 43398.0；睡眠障碍 10000.0</t>
         </is>
       </c>
     </row>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>854984.47</v>
+        <v>1058465.01</v>
       </c>
       <c r="C4" t="n">
-        <v>267398.42</v>
+        <v>399973.42</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1858,14 +1858,14 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>267398.42</v>
+        <v>399973.42</v>
       </c>
       <c r="G4" t="n">
-        <v>31.28</v>
+        <v>37.79</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>日间中心 Ⅱ 115000.0；治疗I（个体1000） 40000.0；诊费I（1000） 40000.0</t>
+          <t>日间中心 Ⅱ 115000.0；日间中心 Ⅰ 96000.0；治疗I（个体1000） 81000.0</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>131308.9</v>
+        <v>176691.9</v>
       </c>
       <c r="C6" t="n">
         <v>95125.89999999999</v>
@@ -1915,13 +1915,13 @@
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>1.54</v>
+        <v>1.14</v>
       </c>
       <c r="F6" t="n">
         <v>93108</v>
       </c>
       <c r="G6" t="n">
-        <v>70.91</v>
+        <v>52.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>89100</v>
+        <v>95040</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>822596.5600000001</v>
+        <v>991544.5600000001</v>
       </c>
       <c r="D2" t="n">
-        <v>4778</v>
+        <v>5324</v>
       </c>
       <c r="E2" t="n">
-        <v>730134.5600000001</v>
+        <v>882370.5600000001</v>
       </c>
       <c r="F2" t="n">
-        <v>92462</v>
+        <v>109174</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>696996</v>
+        <v>852428</v>
       </c>
       <c r="D3" t="n">
-        <v>229</v>
+        <v>270</v>
       </c>
       <c r="E3" t="n">
-        <v>612149</v>
+        <v>751703</v>
       </c>
       <c r="F3" t="n">
-        <v>84847</v>
+        <v>100725</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>125600.56</v>
+        <v>139116.56</v>
       </c>
       <c r="D4" t="n">
-        <v>4549</v>
+        <v>5054</v>
       </c>
       <c r="E4" t="n">
-        <v>117985.56</v>
+        <v>130667.56</v>
       </c>
       <c r="F4" t="n">
-        <v>7615</v>
+        <v>8449</v>
       </c>
     </row>
     <row r="5">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1562632</v>
+        <v>1727320</v>
       </c>
       <c r="D5" t="n">
-        <v>276</v>
+        <v>312</v>
       </c>
       <c r="E5" t="n">
-        <v>340662</v>
+        <v>377474</v>
       </c>
       <c r="F5" t="n">
-        <v>1221970</v>
+        <v>1349846</v>
       </c>
     </row>
     <row r="6">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1001530</v>
+        <v>1099440</v>
       </c>
       <c r="D6" t="n">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="E6" t="n">
-        <v>12000</v>
+        <v>14820</v>
       </c>
       <c r="F6" t="n">
-        <v>989530</v>
+        <v>1084620</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>546102</v>
+        <v>612880</v>
       </c>
       <c r="D7" t="n">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="E7" t="n">
-        <v>328662</v>
+        <v>362654</v>
       </c>
       <c r="F7" t="n">
-        <v>217440</v>
+        <v>250226</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1058465.01</v>
+        <v>1062538.75</v>
       </c>
       <c r="D8" t="n">
-        <v>908</v>
+        <v>918</v>
       </c>
       <c r="E8" t="n">
-        <v>10706.74</v>
+        <v>11206.74</v>
       </c>
       <c r="F8" t="n">
-        <v>1047758.27</v>
+        <v>1051332.01</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>631410.54</v>
+        <v>634447.3</v>
       </c>
       <c r="D9" t="n">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="E9" t="n">
-        <v>2161.37</v>
+        <v>2661.37</v>
       </c>
       <c r="F9" t="n">
-        <v>629249.17</v>
+        <v>631785.9300000001</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>425503.87</v>
+        <v>426540.85</v>
       </c>
       <c r="D10" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="E10" t="n">
         <v>8545.370000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>416958.5</v>
+        <v>417995.48</v>
       </c>
     </row>
     <row r="11">
@@ -682,7 +682,7 @@
         <v>167600</v>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" t="n">
         <v>122000</v>
@@ -703,13 +703,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>176691.9</v>
+        <v>182391.9</v>
       </c>
       <c r="D12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>95795.89999999999</v>
+        <v>101495.9</v>
       </c>
       <c r="F12" t="n">
         <v>80896</v>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>257080</v>
+        <v>263380</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>229280</v>
+        <v>235580</v>
       </c>
       <c r="F13" t="n">
         <v>27800</v>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>912460.6</v>
+        <v>915652.6</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 891489.6；咨询线 10398.0；工作坊 9900.0；课程线 673.0；菌群线 0.0</t>
+          <t>医疗线 894681.6；咨询线 10398.0；工作坊 9900.0；课程线 673.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254048.9</v>
+        <v>270770.9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>82.7</v>
+        <v>83.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>咨询线 209994.0；课程线 37275.0；工作坊 3960.0；医疗线 2819.9</t>
+          <t>咨询线 226586.0；课程线 37405.0；工作坊 3960.0；医疗线 2819.9</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>142133.35</v>
+        <v>142731.35</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 67182.0；考证 39588.0；营地 27800.0；课程线 5053.0；医疗线 2510.35</t>
+          <t>咨询线 67580.0；考证 39588.0；营地 27800.0；课程线 5053.0；医疗线 2710.35</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>261576.14</v>
+        <v>285737.9</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>48.6</v>
+        <v>48</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 127192.0；工作坊 57420.0；菌群线 45600.0；课程线 28334.0；医疗线 3030.14</t>
+          <t>咨询线 137192.0；工作坊 57420.0；菌群线 45600.0；课程线 42351.0；医疗线 3174.9</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>184230.94</v>
+        <v>210491.94</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>91.3</v>
+        <v>92.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 168184.0；医疗线 8050.94；课程线 7996.0；菌群线 0.0</t>
+          <t>咨询线 194378.0；医疗线 8079.94；课程线 8034.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>150178</v>
+        <v>201094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -934,11 +934,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>97.09999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>咨询线 145800.0；课程线 2398.0；工作坊 1980.0</t>
+          <t>咨询线 196198.0；课程线 2916.0；工作坊 1980.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>192514.4</v>
+        <v>192525.4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 182676.0；医疗线 8971.4；课程线 867.0</t>
+          <t>咨询线 182676.0；医疗线 8971.4；课程线 878.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110985.08</v>
+        <v>114093.06</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>81.5</v>
+        <v>82</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 90486.0；医疗线 20408.08；课程线 91.0</t>
+          <t>咨询线 93586.0；医疗线 20416.06；课程线 91.0</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101087.2</v>
+        <v>123464.2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1003,11 +1003,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>84.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>咨询线 85680.0；工作坊 7920.0；医疗线 7276.2；课程线 211.0；菌群线 0.0</t>
+          <t>咨询线 106078.0；工作坊 7920.0；医疗线 7276.2；课程线 2190.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59051</v>
+        <v>59070</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 49592.0；课程线 9459.0</t>
+          <t>咨询线 49592.0；课程线 9478.0</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>106279</v>
+        <v>107075</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1049,11 +1049,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>62.7</v>
+        <v>62.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>咨询线 66586.0；考证 39588.0；课程线 105.0</t>
+          <t>咨询线 67382.0；考证 39588.0；课程线 105.0</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>54400</v>
+        <v>59380</v>
       </c>
     </row>
     <row r="3">
@@ -1140,11 +1140,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>肖伟</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>41460</v>
+        <v>47800</v>
       </c>
     </row>
     <row r="5">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>唐歌</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37840</v>
+        <v>44820</v>
       </c>
     </row>
     <row r="6">
@@ -1176,11 +1176,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>刘士明</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31560</v>
+        <v>44700</v>
       </c>
     </row>
     <row r="7">
@@ -1194,11 +1194,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>74196</v>
+        <v>84414</v>
       </c>
     </row>
     <row r="8">
@@ -1212,11 +1212,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>73418</v>
+        <v>79196</v>
       </c>
     </row>
     <row r="9">
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>68390</v>
+        <v>74584</v>
       </c>
     </row>
     <row r="10">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>郑巨光</t>
+          <t>蔡清霞</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>65592</v>
+        <v>69208</v>
       </c>
     </row>
     <row r="11">
@@ -1266,11 +1266,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>郑巨光</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>63292</v>
+        <v>65592</v>
       </c>
     </row>
     <row r="12">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>99945</v>
+        <v>102137</v>
       </c>
     </row>
     <row r="15">
@@ -1356,11 +1356,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>94497</v>
+        <v>94884</v>
       </c>
     </row>
     <row r="17">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>何媛媛</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>何媛媛</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>曾妍妍</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>曾妍妍</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1518,11 +1518,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>丁蕾</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3800</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="26">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>卢忠慧</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1590,11 +1590,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>冯岚</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>29800</v>
+        <v>34100</v>
       </c>
     </row>
     <row r="30">
@@ -1608,11 +1608,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>冯岚</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>27800</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="31">
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>822596.5600000001</v>
+        <v>991544.5600000001</v>
       </c>
       <c r="C2" t="n">
-        <v>200694.9</v>
+        <v>241446.06</v>
       </c>
       <c r="D2" t="n">
-        <v>14728</v>
+        <v>16871</v>
       </c>
       <c r="E2" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="F2" t="n">
-        <v>185966.9</v>
+        <v>224575.06</v>
       </c>
       <c r="G2" t="n">
-        <v>22.61</v>
+        <v>22.65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>少年说陪伴计划 85800.0；青少年同行者计划领航营 35820.0；少年说 陪伴计划 13200.0</t>
+          <t>少年说陪伴计划 92400.0；青少年同行者计划领航营 51740.0；青少年同行者计划护航营（6月） 16846.0</t>
         </is>
       </c>
     </row>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1562632</v>
+        <v>1727320</v>
       </c>
       <c r="C3" t="n">
-        <v>199797.98</v>
+        <v>228418.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1828,14 +1828,14 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>199797.98</v>
+        <v>228418.98</v>
       </c>
       <c r="G3" t="n">
-        <v>12.79</v>
+        <v>13.22</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>儿童青少年 108499.98；精神心理 43398.0；睡眠障碍 10000.0</t>
+          <t>儿童青少年 110499.98；精神心理 52398.0；家庭守护计划2.0一阶（4980补差价产品） 10621.0</t>
         </is>
       </c>
     </row>
@@ -1846,22 +1846,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1058465.01</v>
+        <v>1062538.75</v>
       </c>
       <c r="C4" t="n">
-        <v>399973.42</v>
+        <v>401822.42</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>399973.42</v>
+        <v>401773.42</v>
       </c>
       <c r="G4" t="n">
-        <v>37.79</v>
+        <v>37.81</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>176691.9</v>
+        <v>182391.9</v>
       </c>
       <c r="C6" t="n">
         <v>95125.89999999999</v>
@@ -1915,13 +1915,13 @@
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="F6" t="n">
         <v>93108</v>
       </c>
       <c r="G6" t="n">
-        <v>52.7</v>
+        <v>51.05</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>257080</v>
+        <v>263380</v>
       </c>
       <c r="C7" t="n">
-        <v>119866.67</v>
+        <v>149666.67</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1948,14 +1948,14 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>119866.67</v>
+        <v>149666.67</v>
       </c>
       <c r="G7" t="n">
-        <v>46.63</v>
+        <v>56.83</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>蛋壳跳动身心复能营21天（一阶） 98866.67；青少年【未来之翼】身心节律复能7日营 16800.0；青少年营地食宿费补差价 4200.0</t>
+          <t>蛋壳跳动身心复能营21天（一阶） 128666.67；青少年【未来之翼】身心节律复能7日营 16800.0；青少年营地食宿费补差价 4200.0</t>
         </is>
       </c>
     </row>

--- a/产品分析_导出.xlsx
+++ b/产品分析_导出.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1727320</v>
+        <v>1722320</v>
       </c>
       <c r="D5" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E5" t="n">
         <v>377474</v>
       </c>
       <c r="F5" t="n">
-        <v>1349846</v>
+        <v>1344846</v>
       </c>
     </row>
     <row r="6">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1062538.75</v>
+        <v>560585.09</v>
       </c>
       <c r="D8" t="n">
-        <v>918</v>
+        <v>828</v>
       </c>
       <c r="E8" t="n">
         <v>11206.74</v>
       </c>
       <c r="F8" t="n">
-        <v>1051332.01</v>
+        <v>549378.35</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>634447.3</v>
+        <v>325152.72</v>
       </c>
       <c r="D9" t="n">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="E9" t="n">
         <v>2661.37</v>
       </c>
       <c r="F9" t="n">
-        <v>631785.9300000001</v>
+        <v>322491.35</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>426540.85</v>
+        <v>235432.37</v>
       </c>
       <c r="D10" t="n">
-        <v>514</v>
+        <v>434</v>
       </c>
       <c r="E10" t="n">
         <v>8545.370000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>417995.48</v>
+        <v>226887</v>
       </c>
     </row>
     <row r="11">
@@ -761,6 +761,30 @@
       </c>
       <c r="F14" t="n">
         <v>81180</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>（合计）</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>25871.6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>55</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6536.36</v>
+      </c>
+      <c r="F15" t="n">
+        <v>19335.24</v>
       </c>
     </row>
   </sheetData>
@@ -811,7 +835,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>915652.6</v>
+        <v>517170.6</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -819,11 +843,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>97.7</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医疗线 894681.6；咨询线 10398.0；工作坊 9900.0；课程线 673.0；菌群线 0.0</t>
+          <t>医疗线 496129.6；咨询线 10398.0；工作坊 9900.0；课程线 673.0；其他 70.0；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -857,7 +881,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>142731.35</v>
+        <v>143231.35</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -865,11 +889,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>咨询线 67580.0；考证 39588.0；营地 27800.0；课程线 5053.0；医疗线 2710.35</t>
+          <t>咨询线 67580.0；考证 39588.0；营地 27800.0；课程线 5053.0；医疗线 2710.35；其他 500.0</t>
         </is>
       </c>
     </row>
@@ -892,7 +916,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>咨询线 137192.0；工作坊 57420.0；菌群线 45600.0；课程线 42351.0；医疗线 3174.9</t>
+          <t>咨询线 137192.0；工作坊 57420.0；菌群线 45600.0；课程线 42351.0；医疗线 3174.9；其他 0.0</t>
         </is>
       </c>
     </row>
@@ -903,7 +927,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>210491.94</v>
+        <v>211257.18</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -911,11 +935,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>92.3</v>
+        <v>92</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>咨询线 194378.0；医疗线 8079.94；课程线 8034.0；菌群线 0.0</t>
+          <t>咨询线 194378.0；医疗线 8079.94；课程线 8034.0；其他 765.24；菌群线 0.0</t>
         </is>
       </c>
     </row>
@@ -961,7 +985,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>咨询线 182676.0；医疗线 8971.4；课程线 878.0</t>
+          <t>咨询线 182676.0；医疗线 8971.4；课程线 878.0；其他 0.0</t>
         </is>
       </c>
     </row>
@@ -972,7 +996,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>114093.06</v>
+        <v>113893.06</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -980,11 +1004,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>82</v>
+        <v>82.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>咨询线 93586.0；医疗线 20416.06；课程线 91.0</t>
+          <t>咨询线 93586.0；医疗线 20216.06；课程线 91.0</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59070</v>
+        <v>77070</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1026,11 +1050,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>84</v>
+        <v>64.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>咨询线 49592.0；课程线 9478.0</t>
+          <t>咨询线 49592.0；其他 18000.0；课程线 9478.0</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1284,11 +1308,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>144981.5</v>
+        <v>95807</v>
       </c>
     </row>
     <row r="13">
@@ -1302,11 +1326,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>143291</v>
+        <v>91504</v>
       </c>
     </row>
     <row r="14">
@@ -1320,11 +1344,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>李浩然</t>
+          <t>余佼</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>102137</v>
+        <v>88298</v>
       </c>
     </row>
     <row r="15">
@@ -1338,11 +1362,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>余佼</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>95070</v>
+        <v>64497</v>
       </c>
     </row>
     <row r="16">
@@ -1356,11 +1380,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>94884</v>
+        <v>35106.1</v>
       </c>
     </row>
     <row r="17">
@@ -1721,6 +1745,96 @@
       </c>
       <c r="D36" t="n">
         <v>3960</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>田婉丽</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>姜玮</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>765.24</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>陈洁</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>刘俊彤</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>吴群</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1734,7 +1848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1816,7 +1930,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1727320</v>
+        <v>1722320</v>
       </c>
       <c r="C3" t="n">
         <v>228418.98</v>
@@ -1831,7 +1945,7 @@
         <v>228418.98</v>
       </c>
       <c r="G3" t="n">
-        <v>13.22</v>
+        <v>13.26</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1846,26 +1960,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1062538.75</v>
+        <v>560585.09</v>
       </c>
       <c r="C4" t="n">
-        <v>401822.42</v>
+        <v>2849</v>
       </c>
       <c r="D4" t="n">
         <v>49</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F4" t="n">
-        <v>401773.42</v>
+        <v>2800</v>
       </c>
       <c r="G4" t="n">
-        <v>37.81</v>
+        <v>0.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>日间中心 Ⅱ 115000.0；日间中心 Ⅰ 96000.0；治疗I（个体1000） 81000.0</t>
+          <t>50分钟问诊（诸秉根） -线下 1800.0；医师50分钟问诊-线上 1000.0；AI测评V9.0-多维父母教养行为测评 49.0</t>
         </is>
       </c>
     </row>
@@ -1984,6 +2098,32 @@
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>25871.6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
